--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 13:46</t>
+          <t>2026-09-27 13:49</t>
         </is>
       </c>
     </row>

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04 13:05</t>
+          <t>2026-10-04 13:42</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
         <v>0.134</v>
@@ -2622,20 +2622,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Above-average</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15" t="n">
-        <v>0.147</v>
+        <v>0.144</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="H15" t="n">
         <v>54</v>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E18" t="n">
         <v>0.16</v>
@@ -2901,13 +2901,13 @@
         <v>15</v>
       </c>
       <c r="E21" t="n">
-        <v>0.199</v>
+        <v>0.19</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H21" t="n">
         <v>57</v>
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E28" t="n">
         <v>0.128</v>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E34" t="n">
         <v>0.128</v>
@@ -3785,13 +3785,13 @@
         <v>7</v>
       </c>
       <c r="E41" t="n">
-        <v>0.368</v>
+        <v>0.366</v>
       </c>
       <c r="F41" t="n">
         <v>2</v>
       </c>
       <c r="G41" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="H41" t="n">
         <v>51</v>
@@ -4940,20 +4940,20 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Above-average</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E67" t="n">
-        <v>0.122</v>
+        <v>0.169</v>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.8</v>
+        <v>2</v>
       </c>
       <c r="H67" t="n">
         <v>50</v>
@@ -5354,7 +5354,7 @@
         <v>77</v>
       </c>
       <c r="H3" t="n">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
       <c r="I3" t="n">
         <v>66.7</v>
@@ -5810,14 +5810,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0-1-0</t>
+          <t>0-2-0</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
         <v>22.6</v>
@@ -5826,13 +5826,13 @@
         <v>77.09999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>45.4</v>
+        <v>54.3</v>
       </c>
       <c r="I11" t="n">
         <v>50</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>1.024</v>
       </c>
       <c r="K11" t="n">
         <v>48.6</v>
@@ -6357,13 +6357,13 @@
         <v>79.90000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>50.5</v>
+        <v>50.9</v>
       </c>
       <c r="I20" t="n">
         <v>80</v>
       </c>
       <c r="J20" t="n">
-        <v>0.995</v>
+        <v>0.994</v>
       </c>
       <c r="K20" t="n">
         <v>48.4</v>
@@ -6770,13 +6770,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>53.8</v>
+        <v>53.4</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.96</v>
+        <v>0.962</v>
       </c>
       <c r="K27" t="n">
         <v>53.9</v>
@@ -7049,14 +7049,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0-0-1</t>
+          <t>1-0-1</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>33.3</v>
+        <v>57.1</v>
       </c>
       <c r="E32" t="n">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="F32" t="n">
         <v>18.5</v>
@@ -7065,13 +7065,13 @@
         <v>77.59999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>40.3</v>
+        <v>39.9</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J32" t="n">
-        <v>1.003</v>
+        <v>0.984</v>
       </c>
       <c r="K32" t="n">
         <v>47.8</v>
@@ -35521,7 +35521,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Ryan Ufko</t>
+          <t>Nicolas Hague</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -35536,27 +35536,23 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Top-6 F</t>
-        </is>
-      </c>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Top-4 D</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
           <t>last season</t>
         </is>
       </c>
       <c r="G357" t="n">
-        <v>13.9</v>
+        <v>19.6</v>
       </c>
       <c r="H357" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="I357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J357" t="n">
         <v>0</v>
@@ -35568,16 +35564,16 @@
         <v>0</v>
       </c>
       <c r="M357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N357" t="n">
-        <v>15.4</v>
+        <v>18.2</v>
       </c>
       <c r="O357" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q357" t="n">
         <v>0</v>
@@ -35586,7 +35582,7 @@
         <v>0</v>
       </c>
       <c r="S357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T357" t="inlineStr">
         <is>
@@ -35595,16 +35591,16 @@
       </c>
       <c r="U357" t="inlineStr"/>
       <c r="V357" t="n">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="W357" t="n">
-        <v>13.9</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Nicolas Hague</t>
+          <t>Nick Perbix</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -35629,7 +35625,7 @@
         </is>
       </c>
       <c r="G358" t="n">
-        <v>19.6</v>
+        <v>19.1</v>
       </c>
       <c r="H358" t="n">
         <v>0.1</v>
@@ -35647,13 +35643,13 @@
         <v>0</v>
       </c>
       <c r="M358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N358" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="O358" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P358" t="n">
         <v>2</v>
@@ -35665,7 +35661,7 @@
         <v>0</v>
       </c>
       <c r="S358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T358" t="inlineStr">
         <is>
@@ -35674,16 +35670,16 @@
       </c>
       <c r="U358" t="inlineStr"/>
       <c r="V358" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="W358" t="n">
-        <v>19.6</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Nick Perbix</t>
+          <t>Alexander Kerfoot</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -35693,12 +35689,12 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Top-4 D</t>
+          <t>Depth F</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
@@ -35708,10 +35704,10 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>19.1</v>
+        <v>12.8</v>
       </c>
       <c r="H359" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="I359" t="n">
         <v>2</v>
@@ -35720,19 +35716,19 @@
         <v>0</v>
       </c>
       <c r="K359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M359" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N359" t="n">
-        <v>18.4</v>
+        <v>14.9</v>
       </c>
       <c r="O359" t="n">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="P359" t="n">
         <v>2</v>
@@ -35741,10 +35737,10 @@
         <v>0</v>
       </c>
       <c r="R359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S359" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T359" t="inlineStr">
         <is>
@@ -35753,16 +35749,16 @@
       </c>
       <c r="U359" t="inlineStr"/>
       <c r="V359" t="n">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="W359" t="n">
-        <v>19.1</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Alexander Kerfoot</t>
+          <t>Ross Colton</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -35787,10 +35783,10 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="H360" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I360" t="n">
         <v>2</v>
@@ -35799,19 +35795,19 @@
         <v>0</v>
       </c>
       <c r="K360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M360" t="n">
         <v>2</v>
       </c>
       <c r="N360" t="n">
-        <v>14.9</v>
+        <v>13.8</v>
       </c>
       <c r="O360" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="P360" t="n">
         <v>2</v>
@@ -35820,7 +35816,7 @@
         <v>0</v>
       </c>
       <c r="R360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S360" t="n">
         <v>2</v>
@@ -35832,16 +35828,16 @@
       </c>
       <c r="U360" t="inlineStr"/>
       <c r="V360" t="n">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="W360" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Ross Colton</t>
+          <t>Matthew Wood</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -35851,7 +35847,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -35866,10 +35862,10 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="H361" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="I361" t="n">
         <v>2</v>
@@ -35884,13 +35880,13 @@
         <v>0</v>
       </c>
       <c r="M361" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N361" t="n">
-        <v>13.8</v>
+        <v>16.7</v>
       </c>
       <c r="O361" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="P361" t="n">
         <v>2</v>
@@ -35902,7 +35898,7 @@
         <v>0</v>
       </c>
       <c r="S361" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T361" t="inlineStr">
         <is>
@@ -35911,16 +35907,16 @@
       </c>
       <c r="U361" t="inlineStr"/>
       <c r="V361" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="W361" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Matthew Wood</t>
+          <t>Nils Hoglander</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -35930,7 +35926,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -35945,43 +35941,43 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="H362" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="I362" t="n">
         <v>2</v>
       </c>
       <c r="J362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K362" t="n">
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N362" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="O362" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="P362" t="n">
         <v>2</v>
       </c>
       <c r="Q362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T362" t="inlineStr">
         <is>
@@ -35990,16 +35986,16 @@
       </c>
       <c r="U362" t="inlineStr"/>
       <c r="V362" t="n">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="W362" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Nils Hoglander</t>
+          <t>Reid Schaefer</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -36024,43 +36020,43 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="H363" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I363" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
       </c>
       <c r="L363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M363" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N363" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="O363" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P363" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S363" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T363" t="inlineStr">
         <is>
@@ -36069,16 +36065,16 @@
       </c>
       <c r="U363" t="inlineStr"/>
       <c r="V363" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="W363" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Reid Schaefer</t>
+          <t>Adam Edstrom</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -36088,7 +36084,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -36103,13 +36099,13 @@
         </is>
       </c>
       <c r="G364" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
       </c>
       <c r="I364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J364" t="n">
         <v>0</v>
@@ -36121,16 +36117,16 @@
         <v>0</v>
       </c>
       <c r="M364" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N364" t="n">
-        <v>11.6</v>
+        <v>12.4</v>
       </c>
       <c r="O364" t="n">
         <v>0</v>
       </c>
       <c r="P364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q364" t="n">
         <v>0</v>
@@ -36139,7 +36135,7 @@
         <v>0</v>
       </c>
       <c r="S364" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T364" t="inlineStr">
         <is>
@@ -36148,16 +36144,16 @@
       </c>
       <c r="U364" t="inlineStr"/>
       <c r="V364" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="W364" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Adam Edstrom</t>
+          <t>Adam Wilsby</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -36167,12 +36163,12 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Depth F</t>
+          <t>Depth D</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
@@ -36182,7 +36178,7 @@
         </is>
       </c>
       <c r="G365" t="n">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -36200,10 +36196,10 @@
         <v>0</v>
       </c>
       <c r="M365" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N365" t="n">
-        <v>12.4</v>
+        <v>15.3</v>
       </c>
       <c r="O365" t="n">
         <v>0</v>
@@ -36218,7 +36214,7 @@
         <v>0</v>
       </c>
       <c r="S365" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T365" t="inlineStr">
         <is>
@@ -36227,16 +36223,16 @@
       </c>
       <c r="U365" t="inlineStr"/>
       <c r="V365" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="W365" t="n">
-        <v>9.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Adam Wilsby</t>
+          <t>Ilya Lyubushkin</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -36261,13 +36257,13 @@
         </is>
       </c>
       <c r="G366" t="n">
-        <v>17</v>
+        <v>15.7</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
       </c>
       <c r="I366" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J366" t="n">
         <v>0</v>
@@ -36279,16 +36275,12 @@
         <v>0</v>
       </c>
       <c r="M366" t="n">
-        <v>1</v>
-      </c>
-      <c r="N366" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="O366" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N366" t="inlineStr"/>
+      <c r="O366" t="inlineStr"/>
       <c r="P366" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q366" t="n">
         <v>0</v>
@@ -36297,7 +36289,7 @@
         <v>0</v>
       </c>
       <c r="S366" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T366" t="inlineStr">
         <is>
@@ -36306,16 +36298,16 @@
       </c>
       <c r="U366" t="inlineStr"/>
       <c r="V366" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="W366" t="n">
-        <v>17</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Ilya Lyubushkin</t>
+          <t>Ryan Ufko</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -36340,13 +36332,13 @@
         </is>
       </c>
       <c r="G367" t="n">
-        <v>15.7</v>
+        <v>13.9</v>
       </c>
       <c r="H367" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J367" t="n">
         <v>0</v>
@@ -36358,12 +36350,16 @@
         <v>0</v>
       </c>
       <c r="M367" t="n">
-        <v>0</v>
-      </c>
-      <c r="N367" t="inlineStr"/>
-      <c r="O367" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N367" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="O367" t="n">
+        <v>2.9</v>
+      </c>
       <c r="P367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q367" t="n">
         <v>0</v>
@@ -36372,7 +36368,7 @@
         <v>0</v>
       </c>
       <c r="S367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T367" t="inlineStr">
         <is>
@@ -36381,10 +36377,10 @@
       </c>
       <c r="U367" t="inlineStr"/>
       <c r="V367" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="W367" t="n">
-        <v>15.7</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="368">

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05 07:34</t>
+          <t>2026-10-05 08:32</t>
         </is>
       </c>
     </row>
@@ -23643,7 +23643,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Michael Rasmussen</t>
+          <t>Michael Brandsegg-Nygård</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -23653,7 +23653,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -23668,10 +23668,10 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="H209" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="I209" t="n">
         <v>2</v>
@@ -23680,16 +23680,16 @@
         <v>0</v>
       </c>
       <c r="K209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M209" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N209" t="n">
-        <v>15.5</v>
+        <v>14.6</v>
       </c>
       <c r="O209" t="n">
         <v>1.8</v>
@@ -23701,10 +23701,10 @@
         <v>0</v>
       </c>
       <c r="R209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S209" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -23713,16 +23713,16 @@
       </c>
       <c r="U209" t="inlineStr"/>
       <c r="V209" t="n">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="W209" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Michael Brandsegg-Nygård</t>
+          <t>Keegan Kolesar</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -23747,10 +23747,10 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="H210" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="I210" t="n">
         <v>2</v>
@@ -23759,19 +23759,19 @@
         <v>0</v>
       </c>
       <c r="K210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>14.6</v>
+        <v>10.6</v>
       </c>
       <c r="O210" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="P210" t="n">
         <v>2</v>
@@ -23780,10 +23780,10 @@
         <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S210" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23792,16 +23792,16 @@
       </c>
       <c r="U210" t="inlineStr"/>
       <c r="V210" t="n">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="W210" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Keegan Kolesar</t>
+          <t>Nate Danielson</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -23811,7 +23811,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -23826,10 +23826,10 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>11.5</v>
+        <v>11.1</v>
       </c>
       <c r="H211" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="I211" t="n">
         <v>2</v>
@@ -23844,13 +23844,13 @@
         <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N211" t="n">
-        <v>10.6</v>
+        <v>8.9</v>
       </c>
       <c r="O211" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="P211" t="n">
         <v>2</v>
@@ -23862,7 +23862,7 @@
         <v>0</v>
       </c>
       <c r="S211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23871,16 +23871,16 @@
       </c>
       <c r="U211" t="inlineStr"/>
       <c r="V211" t="n">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="W211" t="n">
-        <v>11.5</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Nate Danielson</t>
+          <t>Carter Mazur</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -23890,7 +23890,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -23905,13 +23905,13 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="H212" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="I212" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -23923,16 +23923,12 @@
         <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>1</v>
-      </c>
-      <c r="N212" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="O212" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
       <c r="P212" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q212" t="n">
         <v>0</v>
@@ -23941,7 +23937,7 @@
         <v>0</v>
       </c>
       <c r="S212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -23950,16 +23946,16 @@
       </c>
       <c r="U212" t="inlineStr"/>
       <c r="V212" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="W212" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Carter Mazur</t>
+          <t>Albert Johansson</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -23969,12 +23965,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Depth F</t>
+          <t>Depth D</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -23984,13 +23980,13 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>10.7</v>
+        <v>15.9</v>
       </c>
       <c r="H213" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -24002,12 +23998,16 @@
         <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
-      </c>
-      <c r="N213" t="inlineStr"/>
-      <c r="O213" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N213" t="n">
+        <v>15</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
       <c r="P213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q213" t="n">
         <v>0</v>
@@ -24016,7 +24016,7 @@
         <v>0</v>
       </c>
       <c r="S213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -24025,16 +24025,16 @@
       </c>
       <c r="U213" t="inlineStr"/>
       <c r="V213" t="n">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="W213" t="n">
-        <v>10.7</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Albert Johansson</t>
+          <t>Jacob Bernard-Docker</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -24059,13 +24059,13 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>15.9</v>
+        <v>14.8</v>
       </c>
       <c r="H214" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -24077,16 +24077,12 @@
         <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>1</v>
-      </c>
-      <c r="N214" t="n">
-        <v>15</v>
-      </c>
-      <c r="O214" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
       <c r="P214" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q214" t="n">
         <v>0</v>
@@ -24095,7 +24091,7 @@
         <v>0</v>
       </c>
       <c r="S214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -24104,16 +24100,16 @@
       </c>
       <c r="U214" t="inlineStr"/>
       <c r="V214" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="W214" t="n">
-        <v>15.9</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Jacob Bernard-Docker</t>
+          <t>Michael Rasmussen</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -24123,7 +24119,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -24138,13 +24134,13 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>14.8</v>
+        <v>12.6</v>
       </c>
       <c r="H215" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -24156,12 +24152,16 @@
         <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
-      </c>
-      <c r="N215" t="inlineStr"/>
-      <c r="O215" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="N215" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="O215" t="n">
+        <v>1.8</v>
+      </c>
       <c r="P215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q215" t="n">
         <v>0</v>
@@ -24170,7 +24170,7 @@
         <v>0</v>
       </c>
       <c r="S215" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -24179,10 +24179,10 @@
       </c>
       <c r="U215" t="inlineStr"/>
       <c r="V215" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W215" t="n">
-        <v>14.8</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="216">

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 07:31</t>
+          <t>2026-10-06 08:29</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
         <v>17</v>
       </c>
       <c r="P22" t="n">
-        <v>32.5</v>
+        <v>32.8</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>6</v>
       </c>
       <c r="P27" t="n">
-        <v>60.4</v>
+        <v>60</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Michael Brandsegg-Nygård</t>
+          <t>Michael Rasmussen</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -24083,7 +24083,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -24098,10 +24098,10 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="H209" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="I209" t="n">
         <v>2</v>
@@ -24110,16 +24110,16 @@
         <v>0</v>
       </c>
       <c r="K209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N209" t="n">
-        <v>14.6</v>
+        <v>15.5</v>
       </c>
       <c r="O209" t="n">
         <v>1.8</v>
@@ -24131,10 +24131,10 @@
         <v>0</v>
       </c>
       <c r="R209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S209" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -24143,16 +24143,16 @@
       </c>
       <c r="U209" t="inlineStr"/>
       <c r="V209" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="W209" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Keegan Kolesar</t>
+          <t>Michael Brandsegg-Nygård</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="H210" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I210" t="n">
         <v>2</v>
@@ -24189,19 +24189,19 @@
         <v>0</v>
       </c>
       <c r="K210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N210" t="n">
-        <v>10.6</v>
+        <v>14.6</v>
       </c>
       <c r="O210" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="P210" t="n">
         <v>2</v>
@@ -24210,10 +24210,10 @@
         <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S210" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -24222,16 +24222,16 @@
       </c>
       <c r="U210" t="inlineStr"/>
       <c r="V210" t="n">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="W210" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Nate Danielson</t>
+          <t>Keegan Kolesar</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -24241,7 +24241,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -24256,10 +24256,10 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="H211" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="I211" t="n">
         <v>2</v>
@@ -24274,13 +24274,13 @@
         <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>8.9</v>
+        <v>10.6</v>
       </c>
       <c r="O211" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="P211" t="n">
         <v>2</v>
@@ -24292,7 +24292,7 @@
         <v>0</v>
       </c>
       <c r="S211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -24301,16 +24301,16 @@
       </c>
       <c r="U211" t="inlineStr"/>
       <c r="V211" t="n">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="W211" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Carter Mazur</t>
+          <t>Nate Danielson</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -24320,7 +24320,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -24335,13 +24335,13 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="H212" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="I212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -24353,12 +24353,16 @@
         <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
-      </c>
-      <c r="N212" t="inlineStr"/>
-      <c r="O212" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N212" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0.5</v>
+      </c>
       <c r="P212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q212" t="n">
         <v>0</v>
@@ -24367,7 +24371,7 @@
         <v>0</v>
       </c>
       <c r="S212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -24376,16 +24380,16 @@
       </c>
       <c r="U212" t="inlineStr"/>
       <c r="V212" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="W212" t="n">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Albert Johansson</t>
+          <t>Carter Mazur</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -24395,12 +24399,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Depth D</t>
+          <t>Depth F</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -24410,13 +24414,13 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>15.9</v>
+        <v>10.7</v>
       </c>
       <c r="H213" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I213" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -24428,16 +24432,12 @@
         <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>1</v>
-      </c>
-      <c r="N213" t="n">
-        <v>15</v>
-      </c>
-      <c r="O213" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
       <c r="P213" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q213" t="n">
         <v>0</v>
@@ -24446,7 +24446,7 @@
         <v>0</v>
       </c>
       <c r="S213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -24455,16 +24455,16 @@
       </c>
       <c r="U213" t="inlineStr"/>
       <c r="V213" t="n">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="W213" t="n">
-        <v>15.9</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Jacob Bernard-Docker</t>
+          <t>Albert Johansson</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -24489,13 +24489,13 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>14.8</v>
+        <v>15.9</v>
       </c>
       <c r="H214" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I214" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -24507,12 +24507,16 @@
         <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
-      </c>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N214" t="n">
+        <v>15</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
       <c r="P214" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q214" t="n">
         <v>0</v>
@@ -24521,7 +24525,7 @@
         <v>0</v>
       </c>
       <c r="S214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -24530,16 +24534,16 @@
       </c>
       <c r="U214" t="inlineStr"/>
       <c r="V214" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="W214" t="n">
-        <v>14.8</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Michael Rasmussen</t>
+          <t>Jacob Bernard-Docker</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -24549,7 +24553,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -24564,13 +24568,13 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>12.6</v>
+        <v>14.8</v>
       </c>
       <c r="H215" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I215" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -24582,16 +24586,12 @@
         <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>4</v>
-      </c>
-      <c r="N215" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="O215" t="n">
-        <v>1.8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
       <c r="P215" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q215" t="n">
         <v>0</v>
@@ -24600,7 +24600,7 @@
         <v>0</v>
       </c>
       <c r="S215" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -24609,10 +24609,10 @@
       </c>
       <c r="U215" t="inlineStr"/>
       <c r="V215" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="W215" t="n">
-        <v>12.6</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="216">
@@ -35829,7 +35829,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Nicolas Hague</t>
+          <t>Ryan Ufko</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -35844,23 +35844,27 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Top-4 D</t>
-        </is>
-      </c>
-      <c r="E357" t="inlineStr"/>
+          <t>Top-6 F</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F357" t="inlineStr">
         <is>
           <t>last season</t>
         </is>
       </c>
       <c r="G357" t="n">
-        <v>19.6</v>
+        <v>13.9</v>
       </c>
       <c r="H357" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="I357" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J357" t="n">
         <v>0</v>
@@ -35872,16 +35876,16 @@
         <v>0</v>
       </c>
       <c r="M357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N357" t="n">
-        <v>18.2</v>
+        <v>15.4</v>
       </c>
       <c r="O357" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P357" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q357" t="n">
         <v>0</v>
@@ -35890,7 +35894,7 @@
         <v>0</v>
       </c>
       <c r="S357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T357" t="inlineStr">
         <is>
@@ -35899,16 +35903,16 @@
       </c>
       <c r="U357" t="inlineStr"/>
       <c r="V357" t="n">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="W357" t="n">
-        <v>19.6</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Nick Perbix</t>
+          <t>Nicolas Hague</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -35933,7 +35937,7 @@
         </is>
       </c>
       <c r="G358" t="n">
-        <v>19.1</v>
+        <v>19.6</v>
       </c>
       <c r="H358" t="n">
         <v>0.1</v>
@@ -35951,13 +35955,13 @@
         <v>0</v>
       </c>
       <c r="M358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N358" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="O358" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P358" t="n">
         <v>2</v>
@@ -35969,7 +35973,7 @@
         <v>0</v>
       </c>
       <c r="S358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T358" t="inlineStr">
         <is>
@@ -35978,16 +35982,16 @@
       </c>
       <c r="U358" t="inlineStr"/>
       <c r="V358" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="W358" t="n">
-        <v>19.1</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Alexander Kerfoot</t>
+          <t>Nick Perbix</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -35997,12 +36001,12 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Depth F</t>
+          <t>Top-4 D</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
@@ -36012,10 +36016,10 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>12.8</v>
+        <v>19.1</v>
       </c>
       <c r="H359" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="I359" t="n">
         <v>2</v>
@@ -36024,19 +36028,19 @@
         <v>0</v>
       </c>
       <c r="K359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M359" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N359" t="n">
-        <v>14.9</v>
+        <v>18.4</v>
       </c>
       <c r="O359" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="P359" t="n">
         <v>2</v>
@@ -36045,10 +36049,10 @@
         <v>0</v>
       </c>
       <c r="R359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S359" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T359" t="inlineStr">
         <is>
@@ -36057,16 +36061,16 @@
       </c>
       <c r="U359" t="inlineStr"/>
       <c r="V359" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="W359" t="n">
-        <v>12.8</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Ross Colton</t>
+          <t>Alexander Kerfoot</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -36091,10 +36095,10 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="H360" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="I360" t="n">
         <v>2</v>
@@ -36103,19 +36107,19 @@
         <v>0</v>
       </c>
       <c r="K360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M360" t="n">
         <v>2</v>
       </c>
       <c r="N360" t="n">
-        <v>13.8</v>
+        <v>14.9</v>
       </c>
       <c r="O360" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="P360" t="n">
         <v>2</v>
@@ -36124,7 +36128,7 @@
         <v>0</v>
       </c>
       <c r="R360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S360" t="n">
         <v>2</v>
@@ -36136,16 +36140,16 @@
       </c>
       <c r="U360" t="inlineStr"/>
       <c r="V360" t="n">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="W360" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Matthew Wood</t>
+          <t>Ross Colton</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -36155,7 +36159,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -36170,10 +36174,10 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="H361" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="I361" t="n">
         <v>2</v>
@@ -36188,13 +36192,13 @@
         <v>0</v>
       </c>
       <c r="M361" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N361" t="n">
-        <v>16.7</v>
+        <v>13.8</v>
       </c>
       <c r="O361" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="P361" t="n">
         <v>2</v>
@@ -36206,7 +36210,7 @@
         <v>0</v>
       </c>
       <c r="S361" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T361" t="inlineStr">
         <is>
@@ -36215,16 +36219,16 @@
       </c>
       <c r="U361" t="inlineStr"/>
       <c r="V361" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="W361" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Nils Hoglander</t>
+          <t>Matthew Wood</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -36234,7 +36238,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -36249,43 +36253,43 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="H362" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="I362" t="n">
         <v>2</v>
       </c>
       <c r="J362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K362" t="n">
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M362" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N362" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="O362" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="P362" t="n">
         <v>2</v>
       </c>
       <c r="Q362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S362" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T362" t="inlineStr">
         <is>
@@ -36294,16 +36298,16 @@
       </c>
       <c r="U362" t="inlineStr"/>
       <c r="V362" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="W362" t="n">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Reid Schaefer</t>
+          <t>Nils Hoglander</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -36328,43 +36332,43 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="H363" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I363" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
       </c>
       <c r="L363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M363" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N363" t="n">
-        <v>11.6</v>
+        <v>11.1</v>
       </c>
       <c r="O363" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P363" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S363" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T363" t="inlineStr">
         <is>
@@ -36373,16 +36377,16 @@
       </c>
       <c r="U363" t="inlineStr"/>
       <c r="V363" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="W363" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Adam Edstrom</t>
+          <t>Reid Schaefer</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -36392,7 +36396,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -36407,13 +36411,13 @@
         </is>
       </c>
       <c r="G364" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
       </c>
       <c r="I364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J364" t="n">
         <v>0</v>
@@ -36425,16 +36429,16 @@
         <v>0</v>
       </c>
       <c r="M364" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N364" t="n">
-        <v>12.4</v>
+        <v>11.6</v>
       </c>
       <c r="O364" t="n">
         <v>0</v>
       </c>
       <c r="P364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q364" t="n">
         <v>0</v>
@@ -36443,7 +36447,7 @@
         <v>0</v>
       </c>
       <c r="S364" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T364" t="inlineStr">
         <is>
@@ -36452,16 +36456,16 @@
       </c>
       <c r="U364" t="inlineStr"/>
       <c r="V364" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="W364" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Adam Wilsby</t>
+          <t>Adam Edstrom</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -36471,12 +36475,12 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Depth D</t>
+          <t>Depth F</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
@@ -36486,7 +36490,7 @@
         </is>
       </c>
       <c r="G365" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -36504,10 +36508,10 @@
         <v>0</v>
       </c>
       <c r="M365" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N365" t="n">
-        <v>15.3</v>
+        <v>12.4</v>
       </c>
       <c r="O365" t="n">
         <v>0</v>
@@ -36522,7 +36526,7 @@
         <v>0</v>
       </c>
       <c r="S365" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T365" t="inlineStr">
         <is>
@@ -36531,16 +36535,16 @@
       </c>
       <c r="U365" t="inlineStr"/>
       <c r="V365" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="W365" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Ilya Lyubushkin</t>
+          <t>Adam Wilsby</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -36565,13 +36569,13 @@
         </is>
       </c>
       <c r="G366" t="n">
-        <v>15.7</v>
+        <v>17</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
       </c>
       <c r="I366" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J366" t="n">
         <v>0</v>
@@ -36583,12 +36587,16 @@
         <v>0</v>
       </c>
       <c r="M366" t="n">
-        <v>0</v>
-      </c>
-      <c r="N366" t="inlineStr"/>
-      <c r="O366" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N366" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="O366" t="n">
+        <v>0</v>
+      </c>
       <c r="P366" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q366" t="n">
         <v>0</v>
@@ -36597,7 +36605,7 @@
         <v>0</v>
       </c>
       <c r="S366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T366" t="inlineStr">
         <is>
@@ -36606,16 +36614,16 @@
       </c>
       <c r="U366" t="inlineStr"/>
       <c r="V366" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="W366" t="n">
-        <v>15.7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Ryan Ufko</t>
+          <t>Ilya Lyubushkin</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -36640,13 +36648,13 @@
         </is>
       </c>
       <c r="G367" t="n">
-        <v>13.9</v>
+        <v>15.7</v>
       </c>
       <c r="H367" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J367" t="n">
         <v>0</v>
@@ -36658,16 +36666,12 @@
         <v>0</v>
       </c>
       <c r="M367" t="n">
-        <v>1</v>
-      </c>
-      <c r="N367" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="O367" t="n">
-        <v>2.9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N367" t="inlineStr"/>
+      <c r="O367" t="inlineStr"/>
       <c r="P367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q367" t="n">
         <v>0</v>
@@ -36676,7 +36680,7 @@
         <v>0</v>
       </c>
       <c r="S367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T367" t="inlineStr">
         <is>
@@ -36685,10 +36689,10 @@
       </c>
       <c r="U367" t="inlineStr"/>
       <c r="V367" t="n">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="W367" t="n">
-        <v>13.9</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="368">
@@ -42212,7 +42216,7 @@
         <v>2</v>
       </c>
       <c r="M437" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N437" t="n">
         <v>24.5</v>
@@ -42230,7 +42234,7 @@
         <v>2</v>
       </c>
       <c r="S437" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T437" t="inlineStr">
         <is>

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 07:31</t>
+          <t>2026-10-07 08:39</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
         <v>12</v>
       </c>
       <c r="P5" t="n">
-        <v>58.9</v>
+        <v>58.7</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>14</v>
       </c>
       <c r="P16" t="n">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>2</v>
       </c>
       <c r="M75" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N75" t="n">
         <v>17</v>
@@ -13233,7 +13233,7 @@
         <v>2</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -16603,7 +16603,11 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr">
         <is>
           <t>last season</t>
@@ -27563,7 +27567,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Lars Eller</t>
+          <t>Uvis Balinskis</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -27573,7 +27577,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -27588,43 +27592,43 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>12.7</v>
+        <v>13.9</v>
       </c>
       <c r="H256" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="I256" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
       </c>
       <c r="K256" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L256" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N256" t="n">
-        <v>12.7</v>
+        <v>13.9</v>
       </c>
       <c r="O256" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="P256" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q256" t="n">
         <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S256" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -27633,16 +27637,16 @@
       </c>
       <c r="U256" t="inlineStr"/>
       <c r="V256" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="W256" t="n">
-        <v>11.4</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Sandis Vilmanis</t>
+          <t>Lars Eller</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -27652,7 +27656,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -27667,10 +27671,10 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="H257" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="I257" t="n">
         <v>4</v>
@@ -27679,19 +27683,19 @@
         <v>0</v>
       </c>
       <c r="K257" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L257" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M257" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N257" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="O257" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="P257" t="n">
         <v>4</v>
@@ -27700,10 +27704,10 @@
         <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S257" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -27712,16 +27716,16 @@
       </c>
       <c r="U257" t="inlineStr"/>
       <c r="V257" t="n">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="W257" t="n">
-        <v>10.4</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Garnet Hathaway</t>
+          <t>Sandis Vilmanis</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -27731,7 +27735,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -27746,10 +27750,10 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>8.300000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="H258" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I258" t="n">
         <v>4</v>
@@ -27764,13 +27768,13 @@
         <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N258" t="n">
-        <v>8.300000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="O258" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P258" t="n">
         <v>4</v>
@@ -27782,7 +27786,7 @@
         <v>0</v>
       </c>
       <c r="S258" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -27791,7 +27795,7 @@
       </c>
       <c r="U258" t="inlineStr"/>
       <c r="V258" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="W258" t="n">
         <v>10.4</v>
@@ -27800,7 +27804,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Jonah Gadjovich</t>
+          <t>Garnet Hathaway</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -27810,7 +27814,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -27821,17 +27825,17 @@
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G259" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
       </c>
       <c r="I259" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -27843,12 +27847,16 @@
         <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>0</v>
-      </c>
-      <c r="N259" t="inlineStr"/>
-      <c r="O259" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N259" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
       <c r="P259" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q259" t="n">
         <v>0</v>
@@ -27857,7 +27865,7 @@
         <v>0</v>
       </c>
       <c r="S259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -27866,16 +27874,16 @@
       </c>
       <c r="U259" t="inlineStr"/>
       <c r="V259" t="n">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="W259" t="n">
-        <v>7.9</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Bokondji Imama</t>
+          <t>Jonah Gadjovich</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -27896,17 +27904,17 @@
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G260" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
       </c>
       <c r="I260" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -27918,16 +27926,12 @@
         <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>1</v>
-      </c>
-      <c r="N260" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O260" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr"/>
       <c r="P260" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q260" t="n">
         <v>0</v>
@@ -27936,7 +27940,7 @@
         <v>0</v>
       </c>
       <c r="S260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -27945,16 +27949,16 @@
       </c>
       <c r="U260" t="inlineStr"/>
       <c r="V260" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="W260" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Dmitry Kulikov</t>
+          <t>Bokondji Imama</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -27964,12 +27968,12 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Depth D</t>
+          <t>Depth F</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -27979,7 +27983,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>16.4</v>
+        <v>6.3</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -27991,16 +27995,16 @@
         <v>0</v>
       </c>
       <c r="K261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M261" t="n">
         <v>1</v>
       </c>
       <c r="N261" t="n">
-        <v>16.4</v>
+        <v>6.3</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -28012,7 +28016,7 @@
         <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S261" t="n">
         <v>1</v>
@@ -28024,16 +28028,16 @@
       </c>
       <c r="U261" t="inlineStr"/>
       <c r="V261" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="W261" t="n">
-        <v>18</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Uvis Balinskis</t>
+          <t>Dmitry Kulikov</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -28058,43 +28062,43 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>13.9</v>
+        <v>16.4</v>
       </c>
       <c r="H262" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="I262" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
       </c>
       <c r="K262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N262" t="n">
-        <v>13.9</v>
+        <v>16.4</v>
       </c>
       <c r="O262" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P262" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q262" t="n">
         <v>0</v>
       </c>
       <c r="R262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -28103,10 +28107,10 @@
       </c>
       <c r="U262" t="inlineStr"/>
       <c r="V262" t="n">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="W262" t="n">
-        <v>16.4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="263">
@@ -34983,7 +34987,7 @@
         </is>
       </c>
       <c r="G349" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="H349" t="n">
         <v>3.2</v>
@@ -35004,7 +35008,7 @@
         <v>6</v>
       </c>
       <c r="N349" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="O349" t="n">
         <v>3.2</v>
@@ -35066,7 +35070,7 @@
         </is>
       </c>
       <c r="G350" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="H350" t="n">
         <v>3.4</v>
@@ -35087,7 +35091,7 @@
         <v>4</v>
       </c>
       <c r="N350" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="O350" t="n">
         <v>3.4</v>
@@ -35390,7 +35394,7 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="H354" t="n">
         <v>1.5</v>
@@ -35411,7 +35415,7 @@
         <v>7</v>
       </c>
       <c r="N354" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="O354" t="n">
         <v>1.5</v>
@@ -35951,7 +35955,7 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -35972,7 +35976,7 @@
         <v>1</v>
       </c>
       <c r="N361" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="O361" t="n">
         <v>0</v>
@@ -36109,7 +36113,7 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -36130,7 +36134,7 @@
         <v>8</v>
       </c>
       <c r="N363" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="O363" t="n">
         <v>0</v>
@@ -36675,7 +36679,7 @@
         <v>2</v>
       </c>
       <c r="N370" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="O370" t="n">
         <v>0</v>

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 07:33</t>
+          <t>2026-10-08 08:32</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" t="n">
         <v>-0.058</v>
@@ -2784,7 +2784,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" t="n">
         <v>-0.089</v>
@@ -2902,7 +2902,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ukko-Pekka Luukkonen</t>
+          <t>Alex Lyon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2916,39 +2916,35 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.134</v>
+        <v>0.292</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I6" t="n">
-        <v>10.5</v>
+        <v>12.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>67</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alex Lyon</t>
+          <t>Ukko-Pekka Luukkonen</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2958,34 +2954,38 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Above-average</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>0.292</v>
+        <v>0.134</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I7" t="n">
-        <v>12.6</v>
+        <v>10.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
         <v>0.067</v>
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E9" t="n">
         <v>-0.016</v>
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
         <v>0.21</v>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E14" t="n">
         <v>-0.128</v>
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15" t="n">
         <v>0.153</v>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E16" t="n">
         <v>-0.173</v>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E18" t="n">
         <v>0.124</v>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>0.259</v>
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E20" t="n">
         <v>0.12</v>
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
         <v>0.172</v>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22" t="n">
         <v>-0.042</v>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E23" t="n">
         <v>-0.074</v>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E24" t="n">
         <v>-0.205</v>
@@ -3798,7 +3798,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jacob Markstrom</t>
+          <t>Akira Schmid</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3812,39 +3812,39 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.122</v>
+        <v>-0.033</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>3.1</v>
+        <v>-0.4</v>
       </c>
       <c r="H26" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="I26" t="n">
-        <v>-11.9</v>
+        <v>-1</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K26" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Akira Schmid</t>
+          <t>Jacob Markstrom</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3854,36 +3854,36 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Replacement-level</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.033</v>
+        <v>-0.122</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4</v>
+        <v>3.1</v>
       </c>
       <c r="H27" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="I27" t="n">
-        <v>-1</v>
+        <v>-11.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E28" t="n">
         <v>0.128</v>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E29" t="n">
         <v>-0.17</v>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E30" t="n">
         <v>0.212</v>
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E31" t="n">
         <v>-0.145</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E32" t="n">
         <v>0.19</v>
@@ -4116,7 +4116,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Samuel Montembeault</t>
+          <t>Jacob Fowler</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4126,14 +4126,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Replacement-level</t>
+          <t>Above-average</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.146</v>
+        <v>0.265</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4142,10 +4142,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I33" t="n">
-        <v>-4.9</v>
+        <v>7.1</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4158,53 +4158,49 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jake Allen</t>
+          <t>Samuel Montembeault</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NJD</t>
+          <t>MTL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Replacement-level</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="E34" t="n">
-        <v>0.102</v>
+        <v>-0.146</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="I34" t="n">
-        <v>6.3</v>
+        <v>-4.9</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>67</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nico Daws</t>
+          <t>Jake Allen</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4214,41 +4210,43 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Replacement-level (small sample)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>27</v>
+      </c>
       <c r="E35" t="n">
-        <v>-0.142</v>
+        <v>0.102</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35" t="n">
-        <v>-2.4</v>
+        <v>-0.9</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>6.3</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K35" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rémi Poirier</t>
+          <t>Nico Daws</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4258,54 +4256,56 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Replacement-level (no NHL data)</t>
+          <t>Replacement-level (small sample)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>-0.142</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Justus Annunen</t>
+          <t>Rémi Poirier</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NSH</t>
+          <t>NJD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Above-average</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>12</v>
-      </c>
+          <t>Replacement-level (no NHL data)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>0.237</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -4314,10 +4314,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
@@ -4330,7 +4330,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Juuse Saros</t>
+          <t>Justus Annunen</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4340,43 +4340,39 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Above-average</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.101</v>
+        <v>0.237</v>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="I38" t="n">
-        <v>-9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>100</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Matt Murray</t>
+          <t>Juuse Saros</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4386,83 +4382,83 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Replacement-level (no NHL data)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>41</v>
+      </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>-0.101</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ilya Sorokin</t>
+          <t>Matt Murray</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NYI</t>
+          <t>NSH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>2</v>
-      </c>
+          <t>Replacement-level (no NHL data)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>0.451</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>25.3</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>67</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Semyon Varlamov</t>
+          <t>Ilya Sorokin</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4472,76 +4468,76 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Average (small sample)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
       <c r="E41" t="n">
-        <v>0.073</v>
+        <v>0.451</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>55</v>
+      </c>
+      <c r="I41" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="J41" t="n">
         <v>0.8</v>
       </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.9</v>
-      </c>
       <c r="K41" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Igor Shesterkin</t>
+          <t>Semyon Varlamov</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NYR</t>
+          <t>NYI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Above-average</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>7</v>
-      </c>
+          <t>Average (small sample)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>0.381</v>
+        <v>0.073</v>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="H42" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>21.2</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K42" t="n">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -4552,7 +4548,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Joonas Korpisalo</t>
+          <t>Igor Shesterkin</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4562,39 +4558,43 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Above-average</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.025</v>
+        <v>0.381</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="H43" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="I43" t="n">
-        <v>-1</v>
+        <v>21.2</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dylan Garand</t>
+          <t>Joonas Korpisalo</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4604,87 +4604,83 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Average (small sample)</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>33</v>
+      </c>
       <c r="E44" t="n">
-        <v>0.378</v>
+        <v>-0.025</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="I44" t="n">
-        <v>3.9</v>
+        <v>-1</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>20</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Linus Ullmark</t>
+          <t>Dylan Garand</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OTT</t>
+          <t>NYR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Replacement-level</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>48</v>
-      </c>
+          <t>Average (small sample)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>-0.15</v>
+        <v>0.378</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="H45" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>-12.8</v>
+        <v>3.9</v>
       </c>
       <c r="J45" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K45" t="n">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Samuel Ersson</t>
+          <t>Linus Ullmark</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4698,39 +4694,39 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.395</v>
+        <v>-0.15</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.6</v>
+        <v>2.7</v>
       </c>
       <c r="H46" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I46" t="n">
-        <v>-16.5</v>
+        <v>-12.8</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K46" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Jonas Johansson</t>
+          <t>Samuel Ersson</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4744,30 +4740,34 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.309</v>
+        <v>-0.395</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="H47" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I47" t="n">
-        <v>-10.4</v>
+        <v>-16.5</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E48" t="n">
         <v>0.182</v>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E49" t="n">
         <v>-0.049</v>
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E50" t="n">
         <v>-0.244</v>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E52" t="n">
         <v>0.187</v>
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E53" t="n">
         <v>-0.081</v>
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E54" t="n">
         <v>-0.024</v>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E55" t="n">
         <v>-0.3</v>
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E56" t="n">
         <v>0.257</v>
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E60" t="n">
         <v>-0.166</v>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E61" t="n">
         <v>-0.124</v>
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E62" t="n">
         <v>0.113</v>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E64" t="n">
         <v>0.06900000000000001</v>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E67" t="n">
         <v>-0.148</v>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E69" t="n">
         <v>0.183</v>
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E70" t="n">
         <v>0.083</v>
@@ -5914,7 +5914,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E73" t="n">
         <v>-0.122</v>

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11 07:28</t>
+          <t>2026-10-11 08:28</t>
         </is>
       </c>
     </row>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Top-4 D</t>
+          <t>Depth F</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -18947,7 +18947,11 @@
           <t>Top-pair D</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr">
         <is>
           <t>last season</t>
@@ -40265,7 +40269,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Alexis Lafrenière</t>
+          <t>J.T. Miller</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -40275,7 +40279,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -40294,43 +40298,43 @@
         </is>
       </c>
       <c r="G405" t="n">
-        <v>19.1</v>
+        <v>17.8</v>
       </c>
       <c r="H405" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="I405" t="n">
         <v>6</v>
       </c>
       <c r="J405" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K405" t="n">
         <v>2</v>
       </c>
       <c r="L405" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M405" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N405" t="n">
-        <v>19.1</v>
+        <v>17.8</v>
       </c>
       <c r="O405" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="P405" t="n">
         <v>6</v>
       </c>
       <c r="Q405" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R405" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S405" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T405" t="inlineStr">
         <is>
@@ -40339,16 +40343,16 @@
       </c>
       <c r="U405" t="inlineStr"/>
       <c r="V405" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="W405" t="n">
-        <v>17.6</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>J.T. Miller</t>
+          <t>Pavel Dorofeyev</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -40358,7 +40362,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -40377,10 +40381,10 @@
         </is>
       </c>
       <c r="G406" t="n">
-        <v>17.8</v>
+        <v>16.8</v>
       </c>
       <c r="H406" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="I406" t="n">
         <v>6</v>
@@ -40395,13 +40399,13 @@
         <v>3</v>
       </c>
       <c r="M406" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="N406" t="n">
-        <v>17.8</v>
+        <v>16.8</v>
       </c>
       <c r="O406" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="P406" t="n">
         <v>6</v>
@@ -40413,7 +40417,7 @@
         <v>3</v>
       </c>
       <c r="S406" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="T406" t="inlineStr">
         <is>
@@ -40422,16 +40426,16 @@
       </c>
       <c r="U406" t="inlineStr"/>
       <c r="V406" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="W406" t="n">
-        <v>20.1</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Pavel Dorofeyev</t>
+          <t>Will Cuylle</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -40441,7 +40445,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -40449,54 +40453,50 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E407" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E407" t="inlineStr"/>
       <c r="F407" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G407" t="n">
-        <v>16.8</v>
+        <v>15.4</v>
       </c>
       <c r="H407" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="I407" t="n">
         <v>6</v>
       </c>
       <c r="J407" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K407" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L407" t="n">
         <v>3</v>
       </c>
       <c r="M407" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N407" t="n">
-        <v>16.8</v>
+        <v>15.4</v>
       </c>
       <c r="O407" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="P407" t="n">
         <v>6</v>
       </c>
       <c r="Q407" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R407" t="n">
         <v>3</v>
       </c>
       <c r="S407" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="T407" t="inlineStr">
         <is>
@@ -40508,13 +40508,13 @@
         <v>82</v>
       </c>
       <c r="W407" t="n">
-        <v>17.6</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Will Cuylle</t>
+          <t>Gabe Perreault</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -40524,7 +40524,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -40539,43 +40539,43 @@
         </is>
       </c>
       <c r="G408" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="H408" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="I408" t="n">
         <v>6</v>
       </c>
       <c r="J408" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K408" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L408" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M408" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N408" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="O408" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="P408" t="n">
         <v>6</v>
       </c>
       <c r="Q408" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R408" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S408" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T408" t="inlineStr">
         <is>
@@ -40584,16 +40584,16 @@
       </c>
       <c r="U408" t="inlineStr"/>
       <c r="V408" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="W408" t="n">
-        <v>16.9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Gabe Perreault</t>
+          <t>Sean Durzi</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -40603,12 +40603,12 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Top-6 F</t>
+          <t>Top-4 D</t>
         </is>
       </c>
       <c r="E409" t="inlineStr"/>
@@ -40618,43 +40618,43 @@
         </is>
       </c>
       <c r="G409" t="n">
-        <v>15.2</v>
+        <v>20.5</v>
       </c>
       <c r="H409" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I409" t="n">
         <v>6</v>
       </c>
       <c r="J409" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K409" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L409" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M409" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N409" t="n">
-        <v>15.2</v>
+        <v>20.5</v>
       </c>
       <c r="O409" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="P409" t="n">
         <v>6</v>
       </c>
       <c r="Q409" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R409" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S409" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T409" t="inlineStr">
         <is>
@@ -40663,16 +40663,16 @@
       </c>
       <c r="U409" t="inlineStr"/>
       <c r="V409" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="W409" t="n">
-        <v>16</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Sean Durzi</t>
+          <t>Marcus Pettersson</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -40697,43 +40697,43 @@
         </is>
       </c>
       <c r="G410" t="n">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="H410" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="I410" t="n">
         <v>6</v>
       </c>
       <c r="J410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L410" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M410" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N410" t="n">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="O410" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="P410" t="n">
         <v>6</v>
       </c>
       <c r="Q410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R410" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S410" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T410" t="inlineStr">
         <is>
@@ -40742,16 +40742,16 @@
       </c>
       <c r="U410" t="inlineStr"/>
       <c r="V410" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="W410" t="n">
-        <v>19.3</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Marcus Pettersson</t>
+          <t>Tye Kartye</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -40761,12 +40761,12 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Top-4 D</t>
+          <t>Depth F</t>
         </is>
       </c>
       <c r="E411" t="inlineStr"/>
@@ -40776,10 +40776,10 @@
         </is>
       </c>
       <c r="G411" t="n">
-        <v>20.2</v>
+        <v>14.9</v>
       </c>
       <c r="H411" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I411" t="n">
         <v>6</v>
@@ -40788,19 +40788,19 @@
         <v>0</v>
       </c>
       <c r="K411" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L411" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M411" t="n">
         <v>5</v>
       </c>
       <c r="N411" t="n">
-        <v>20.2</v>
+        <v>14.9</v>
       </c>
       <c r="O411" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P411" t="n">
         <v>6</v>
@@ -40809,7 +40809,7 @@
         <v>0</v>
       </c>
       <c r="R411" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S411" t="n">
         <v>5</v>
@@ -40821,16 +40821,16 @@
       </c>
       <c r="U411" t="inlineStr"/>
       <c r="V411" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="W411" t="n">
-        <v>21.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Tye Kartye</t>
+          <t>Noah Laba</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -40840,7 +40840,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -40855,10 +40855,10 @@
         </is>
       </c>
       <c r="G412" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="H412" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I412" t="n">
         <v>6</v>
@@ -40867,19 +40867,19 @@
         <v>0</v>
       </c>
       <c r="K412" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L412" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M412" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N412" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="O412" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P412" t="n">
         <v>6</v>
@@ -40888,10 +40888,10 @@
         <v>0</v>
       </c>
       <c r="R412" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S412" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T412" t="inlineStr">
         <is>
@@ -40900,16 +40900,16 @@
       </c>
       <c r="U412" t="inlineStr"/>
       <c r="V412" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="W412" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Noah Laba</t>
+          <t>Eeli Tolvanen</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -40919,7 +40919,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -40934,43 +40934,43 @@
         </is>
       </c>
       <c r="G413" t="n">
-        <v>14.6</v>
+        <v>13.3</v>
       </c>
       <c r="H413" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="I413" t="n">
         <v>6</v>
       </c>
       <c r="J413" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K413" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L413" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M413" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N413" t="n">
-        <v>14.6</v>
+        <v>13.3</v>
       </c>
       <c r="O413" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="P413" t="n">
         <v>6</v>
       </c>
       <c r="Q413" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R413" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S413" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T413" t="inlineStr">
         <is>
@@ -40979,16 +40979,16 @@
       </c>
       <c r="U413" t="inlineStr"/>
       <c r="V413" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="W413" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Eeli Tolvanen</t>
+          <t>Joseph Veleno</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -40998,7 +40998,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -41013,43 +41013,43 @@
         </is>
       </c>
       <c r="G414" t="n">
-        <v>13.3</v>
+        <v>11.6</v>
       </c>
       <c r="H414" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I414" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J414" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K414" t="n">
         <v>0</v>
       </c>
       <c r="L414" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M414" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N414" t="n">
-        <v>13.3</v>
+        <v>11.6</v>
       </c>
       <c r="O414" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P414" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q414" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R414" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S414" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T414" t="inlineStr">
         <is>
@@ -41058,16 +41058,16 @@
       </c>
       <c r="U414" t="inlineStr"/>
       <c r="V414" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="W414" t="n">
-        <v>16</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Joseph Veleno</t>
+          <t>Adam Sykora</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -41077,7 +41077,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -41088,17 +41088,17 @@
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G415" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="H415" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I415" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J415" t="n">
         <v>0</v>
@@ -41110,16 +41110,12 @@
         <v>0</v>
       </c>
       <c r="M415" t="n">
-        <v>2</v>
-      </c>
-      <c r="N415" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="O415" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N415" t="inlineStr"/>
+      <c r="O415" t="inlineStr"/>
       <c r="P415" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q415" t="n">
         <v>0</v>
@@ -41128,7 +41124,7 @@
         <v>0</v>
       </c>
       <c r="S415" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T415" t="inlineStr">
         <is>
@@ -41137,16 +41133,16 @@
       </c>
       <c r="U415" t="inlineStr"/>
       <c r="V415" t="n">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="W415" t="n">
-        <v>12.1</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Adam Sykora</t>
+          <t>Oliver Bjorkstrand</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -41156,7 +41152,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -41167,43 +41163,47 @@
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G416" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="H416" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I416" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J416" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K416" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L416" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M416" t="n">
-        <v>0</v>
-      </c>
-      <c r="N416" t="inlineStr"/>
-      <c r="O416" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="N416" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O416" t="n">
+        <v>1</v>
+      </c>
       <c r="P416" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q416" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R416" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S416" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T416" t="inlineStr">
         <is>
@@ -41212,16 +41212,16 @@
       </c>
       <c r="U416" t="inlineStr"/>
       <c r="V416" t="n">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="W416" t="n">
-        <v>11.2</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Oliver Bjorkstrand</t>
+          <t>Matt Rempe</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -41231,7 +41231,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -41242,47 +41242,47 @@
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G417" t="n">
-        <v>11.1</v>
+        <v>8.6</v>
       </c>
       <c r="H417" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I417" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J417" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K417" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L417" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M417" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N417" t="n">
-        <v>11.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O417" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P417" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q417" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R417" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S417" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T417" t="inlineStr">
         <is>
@@ -41291,16 +41291,16 @@
       </c>
       <c r="U417" t="inlineStr"/>
       <c r="V417" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="W417" t="n">
-        <v>13.6</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Matt Rempe</t>
+          <t>Jaroslav Chmelar</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -41310,7 +41310,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -41321,17 +41321,17 @@
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G418" t="n">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="H418" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I418" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J418" t="n">
         <v>0</v>
@@ -41343,16 +41343,16 @@
         <v>0</v>
       </c>
       <c r="M418" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N418" t="n">
-        <v>9.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="O418" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P418" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q418" t="n">
         <v>0</v>
@@ -41361,7 +41361,7 @@
         <v>0</v>
       </c>
       <c r="S418" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T418" t="inlineStr">
         <is>
@@ -41370,16 +41370,16 @@
       </c>
       <c r="U418" t="inlineStr"/>
       <c r="V418" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="W418" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Jaroslav Chmelar</t>
+          <t>Alexis Lafrenière</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -41389,58 +41389,62 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Depth F</t>
-        </is>
-      </c>
-      <c r="E419" t="inlineStr"/>
+          <t>Depth D</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F419" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G419" t="n">
-        <v>7.9</v>
+        <v>19.1</v>
       </c>
       <c r="H419" t="n">
-        <v>0.1</v>
+        <v>3.2</v>
       </c>
       <c r="I419" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J419" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K419" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L419" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M419" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N419" t="n">
-        <v>7.9</v>
+        <v>19.1</v>
       </c>
       <c r="O419" t="n">
-        <v>0.1</v>
+        <v>3.2</v>
       </c>
       <c r="P419" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q419" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R419" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S419" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T419" t="inlineStr">
         <is>
@@ -41449,10 +41453,10 @@
       </c>
       <c r="U419" t="inlineStr"/>
       <c r="V419" t="n">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="W419" t="n">
-        <v>9.199999999999999</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="420">
@@ -43542,7 +43546,11 @@
           <t>Depth (no NHL data)</t>
         </is>
       </c>
-      <c r="E446" t="inlineStr"/>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F446" t="inlineStr">
         <is>
           <t>no NHL data</t>

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 07:36</t>
+          <t>2026-10-12 08:32</t>
         </is>
       </c>
     </row>
@@ -13606,7 +13606,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Jackson Blake</t>
+          <t>Logan Stankoven</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -13624,54 +13624,50 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>18.2</v>
+        <v>17.7</v>
       </c>
       <c r="H71" t="n">
-        <v>5.4</v>
+        <v>2</v>
       </c>
       <c r="I71" t="n">
         <v>7</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K71" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M71" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N71" t="n">
-        <v>18.2</v>
+        <v>17.7</v>
       </c>
       <c r="O71" t="n">
-        <v>5.4</v>
+        <v>2</v>
       </c>
       <c r="P71" t="n">
         <v>7</v>
       </c>
       <c r="Q71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R71" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -13683,13 +13679,13 @@
         <v>81</v>
       </c>
       <c r="W71" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Logan Stankoven</t>
+          <t>Andrei Svechnikov</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -13699,7 +13695,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -13707,17 +13703,21 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>17.7</v>
+        <v>17</v>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="I72" t="n">
         <v>7</v>
@@ -13726,19 +13726,19 @@
         <v>4</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L72" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M72" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N72" t="n">
-        <v>17.7</v>
+        <v>17</v>
       </c>
       <c r="O72" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="P72" t="n">
         <v>7</v>
@@ -13747,10 +13747,10 @@
         <v>4</v>
       </c>
       <c r="R72" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S72" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -13759,16 +13759,16 @@
       </c>
       <c r="U72" t="inlineStr"/>
       <c r="V72" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="W72" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Andrei Svechnikov</t>
+          <t>Nikolaj Ehlers</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -13778,7 +13778,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -13797,43 +13797,43 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>17</v>
+        <v>15.7</v>
       </c>
       <c r="H73" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="I73" t="n">
         <v>7</v>
       </c>
       <c r="J73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L73" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M73" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="N73" t="n">
-        <v>17</v>
+        <v>15.7</v>
       </c>
       <c r="O73" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="P73" t="n">
         <v>7</v>
       </c>
       <c r="Q73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S73" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -13842,16 +13842,16 @@
       </c>
       <c r="U73" t="inlineStr"/>
       <c r="V73" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="W73" t="n">
-        <v>17</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Nikolaj Ehlers</t>
+          <t>Jordan Staal</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -13869,54 +13869,50 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="H74" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="I74" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N74" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="O74" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="P74" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -13925,16 +13921,16 @@
       </c>
       <c r="U74" t="inlineStr"/>
       <c r="V74" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="W74" t="n">
-        <v>16.6</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Jordan Staal</t>
+          <t>Charles Alexis Legault</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -13944,7 +13940,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -13955,17 +13951,17 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>15.6</v>
+        <v>14.3</v>
       </c>
       <c r="H75" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -13977,16 +13973,16 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N75" t="n">
-        <v>15.6</v>
+        <v>11.9</v>
       </c>
       <c r="O75" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -13995,7 +13991,7 @@
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -14004,16 +14000,16 @@
       </c>
       <c r="U75" t="inlineStr"/>
       <c r="V75" t="n">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="W75" t="n">
-        <v>16.2</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Charles Alexis Legault</t>
+          <t>Jaccob Slavin</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -14028,53 +14024,53 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Top-6 F</t>
+          <t>Top-4 D</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>14.3</v>
+        <v>20.9</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M76" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N76" t="n">
-        <v>11.9</v>
+        <v>20.9</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S76" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -14083,16 +14079,16 @@
       </c>
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="W76" t="n">
-        <v>14.3</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Jaccob Slavin</t>
+          <t>Jalen Chatfield</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -14117,10 +14113,10 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I77" t="n">
         <v>7</v>
@@ -14135,13 +14131,13 @@
         <v>2</v>
       </c>
       <c r="M77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N77" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P77" t="n">
         <v>7</v>
@@ -14153,7 +14149,7 @@
         <v>2</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -14162,16 +14158,16 @@
       </c>
       <c r="U77" t="inlineStr"/>
       <c r="V77" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="W77" t="n">
-        <v>21.3</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Jalen Chatfield</t>
+          <t>Jackson Blake</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -14181,58 +14177,62 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Top-4 D</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>Depth F</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>20.4</v>
+        <v>18.2</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1</v>
+        <v>5.4</v>
       </c>
       <c r="I78" t="n">
         <v>7</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L78" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M78" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="N78" t="n">
-        <v>20.4</v>
+        <v>18.2</v>
       </c>
       <c r="O78" t="n">
-        <v>0.1</v>
+        <v>5.4</v>
       </c>
       <c r="P78" t="n">
         <v>7</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -14241,10 +14241,10 @@
       </c>
       <c r="U78" t="inlineStr"/>
       <c r="V78" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="W78" t="n">
-        <v>20.1</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="79">
@@ -15782,7 +15782,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Depth F</t>
+          <t>Top-4 D</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -18860,7 +18860,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Dominic Toninato</t>
+          <t>Patrick Kane</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -18870,12 +18870,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Top-pair D</t>
+          <t>Top-6 F</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -18885,47 +18885,47 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>9.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M137" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N137" t="n">
-        <v>9.1</v>
+        <v>19.5</v>
       </c>
       <c r="O137" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P137" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S137" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -18934,16 +18934,16 @@
       </c>
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="n">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="W137" t="n">
-        <v>9.199999999999999</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Patrick Kane</t>
+          <t>Frank Nazar</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -18953,7 +18953,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18961,54 +18961,50 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>19.5</v>
+        <v>18.8</v>
       </c>
       <c r="H138" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="I138" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K138" t="n">
         <v>1</v>
       </c>
       <c r="L138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M138" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N138" t="n">
-        <v>19.5</v>
+        <v>18.8</v>
       </c>
       <c r="O138" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="P138" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S138" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -19017,16 +19013,16 @@
       </c>
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="W138" t="n">
-        <v>17.7</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Frank Nazar</t>
+          <t>Roman Kantserov</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -19036,7 +19032,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19044,50 +19040,54 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="H139" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="I139" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N139" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="O139" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="P139" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S139" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -19096,16 +19096,16 @@
       </c>
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="W139" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Roman Kantserov</t>
+          <t>Anton Frondell</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -19115,7 +19115,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -19123,21 +19123,17 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="H140" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="I140" t="n">
         <v>6</v>
@@ -19146,19 +19142,19 @@
         <v>1</v>
       </c>
       <c r="K140" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L140" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M140" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N140" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="O140" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="P140" t="n">
         <v>6</v>
@@ -19167,10 +19163,10 @@
         <v>1</v>
       </c>
       <c r="R140" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S140" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -19179,16 +19175,16 @@
       </c>
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W140" t="n">
-        <v>0</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Anton Frondell</t>
+          <t>Tyler Bertuzzi</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -19198,7 +19194,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -19206,17 +19202,21 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>18.2</v>
+        <v>17.9</v>
       </c>
       <c r="H141" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="I141" t="n">
         <v>6</v>
@@ -19225,19 +19225,19 @@
         <v>1</v>
       </c>
       <c r="K141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L141" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M141" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N141" t="n">
-        <v>18.2</v>
+        <v>17.9</v>
       </c>
       <c r="O141" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="P141" t="n">
         <v>6</v>
@@ -19246,10 +19246,10 @@
         <v>1</v>
       </c>
       <c r="R141" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -19258,16 +19258,16 @@
       </c>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="n">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="W141" t="n">
-        <v>17.7</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Tyler Bertuzzi</t>
+          <t>Alex Vlasic</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -19277,62 +19277,58 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Top-6 F</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Top-4 D</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>17.9</v>
+        <v>19.5</v>
       </c>
       <c r="H142" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I142" t="n">
         <v>6</v>
       </c>
       <c r="J142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L142" t="n">
         <v>2</v>
       </c>
       <c r="M142" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N142" t="n">
-        <v>17.9</v>
+        <v>19.5</v>
       </c>
       <c r="O142" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P142" t="n">
         <v>6</v>
       </c>
       <c r="Q142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
         <v>2</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -19341,16 +19337,16 @@
       </c>
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="W142" t="n">
-        <v>18.4</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Alex Vlasic</t>
+          <t>Wyatt Kaiser</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -19375,10 +19371,10 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I143" t="n">
         <v>6</v>
@@ -19396,10 +19392,10 @@
         <v>4</v>
       </c>
       <c r="N143" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P143" t="n">
         <v>6</v>
@@ -19420,16 +19416,16 @@
       </c>
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="W143" t="n">
-        <v>21.1</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Wyatt Kaiser</t>
+          <t>Ryan Greene</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -19439,12 +19435,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Top-4 D</t>
+          <t>Depth F</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -19454,10 +19450,10 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>19.2</v>
+        <v>16</v>
       </c>
       <c r="H144" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="I144" t="n">
         <v>6</v>
@@ -19466,19 +19462,19 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M144" t="n">
         <v>4</v>
       </c>
       <c r="N144" t="n">
-        <v>19.2</v>
+        <v>16</v>
       </c>
       <c r="O144" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="P144" t="n">
         <v>6</v>
@@ -19487,7 +19483,7 @@
         <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S144" t="n">
         <v>4</v>
@@ -19499,16 +19495,16 @@
       </c>
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="W144" t="n">
-        <v>19.6</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Ryan Greene</t>
+          <t>Cole Smith</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -19518,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19533,43 +19529,43 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>16</v>
+        <v>14.9</v>
       </c>
       <c r="H145" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I145" t="n">
         <v>6</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L145" t="n">
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N145" t="n">
-        <v>16</v>
+        <v>14.9</v>
       </c>
       <c r="O145" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="P145" t="n">
         <v>6</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R145" t="n">
         <v>1</v>
       </c>
       <c r="S145" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -19578,16 +19574,16 @@
       </c>
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="W145" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Cole Smith</t>
+          <t>Jordan Greenway</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -19597,7 +19593,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19612,10 +19608,10 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="H146" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I146" t="n">
         <v>6</v>
@@ -19630,13 +19626,13 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="N146" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="O146" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P146" t="n">
         <v>6</v>
@@ -19648,7 +19644,7 @@
         <v>1</v>
       </c>
       <c r="S146" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -19657,16 +19653,16 @@
       </c>
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="W146" t="n">
-        <v>13.3</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Jordan Greenway</t>
+          <t>Teuvo Teravainen</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -19676,7 +19672,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19691,43 +19687,43 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>14.5</v>
+        <v>12.7</v>
       </c>
       <c r="H147" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M147" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="N147" t="n">
-        <v>14.5</v>
+        <v>12.7</v>
       </c>
       <c r="O147" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P147" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S147" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -19736,16 +19732,16 @@
       </c>
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="W147" t="n">
-        <v>12.4</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Teuvo Teravainen</t>
+          <t>Andrew Mangiapane</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -19755,7 +19751,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19766,47 +19762,47 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="H148" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I148" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N148" t="n">
-        <v>12.7</v>
+        <v>5.4</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
       </c>
       <c r="P148" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q148" t="n">
         <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -19815,16 +19811,16 @@
       </c>
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="W148" t="n">
-        <v>17.8</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Andrew Mangiapane</t>
+          <t>Oliver Moore</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -19834,7 +19830,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19845,47 +19841,47 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="H149" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M149" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N149" t="n">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="O149" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P149" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S149" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -19894,16 +19890,16 @@
       </c>
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="W149" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Oliver Moore</t>
+          <t>Ryan Donato</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -19928,7 +19924,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H150" t="n">
         <v>1.2</v>
@@ -19937,19 +19933,19 @@
         <v>6</v>
       </c>
       <c r="J150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L150" t="n">
         <v>2</v>
       </c>
       <c r="M150" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N150" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O150" t="n">
         <v>1.2</v>
@@ -19958,13 +19954,13 @@
         <v>6</v>
       </c>
       <c r="Q150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R150" t="n">
         <v>2</v>
       </c>
       <c r="S150" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -19973,16 +19969,16 @@
       </c>
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="n">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="W150" t="n">
-        <v>12.8</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Ryan Donato</t>
+          <t>Nick Lardis</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -19992,7 +19988,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20010,40 +20006,40 @@
         <v>11</v>
       </c>
       <c r="H151" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I151" t="n">
         <v>6</v>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L151" t="n">
         <v>2</v>
       </c>
       <c r="M151" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N151" t="n">
         <v>11</v>
       </c>
       <c r="O151" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="P151" t="n">
         <v>6</v>
       </c>
       <c r="Q151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
         <v>2</v>
       </c>
       <c r="S151" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -20052,16 +20048,16 @@
       </c>
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="W151" t="n">
-        <v>14.7</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Nick Lardis</t>
+          <t>Dominic Toninato</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -20071,7 +20067,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20079,50 +20075,54 @@
           <t>Depth F</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H152" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N152" t="n">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="O152" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="P152" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q152" t="n">
         <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -20131,10 +20131,10 @@
       </c>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="W152" t="n">
-        <v>12.7</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="153">
@@ -40200,7 +40200,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>J.T. Miller</t>
+          <t>Alexis Lafrenière</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -40210,7 +40210,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -40229,43 +40229,43 @@
         </is>
       </c>
       <c r="G405" t="n">
-        <v>17.9</v>
+        <v>19.1</v>
       </c>
       <c r="H405" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="I405" t="n">
         <v>7</v>
       </c>
       <c r="J405" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K405" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L405" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M405" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N405" t="n">
-        <v>17.9</v>
+        <v>19.1</v>
       </c>
       <c r="O405" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="P405" t="n">
         <v>7</v>
       </c>
       <c r="Q405" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R405" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S405" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T405" t="inlineStr">
         <is>
@@ -40274,16 +40274,16 @@
       </c>
       <c r="U405" t="inlineStr"/>
       <c r="V405" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="W405" t="n">
-        <v>20.1</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Pavel Dorofeyev</t>
+          <t>J.T. Miller</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -40293,7 +40293,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -40312,10 +40312,10 @@
         </is>
       </c>
       <c r="G406" t="n">
-        <v>17</v>
+        <v>17.9</v>
       </c>
       <c r="H406" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="I406" t="n">
         <v>7</v>
@@ -40324,19 +40324,19 @@
         <v>1</v>
       </c>
       <c r="K406" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L406" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M406" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="N406" t="n">
-        <v>17</v>
+        <v>17.9</v>
       </c>
       <c r="O406" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P406" t="n">
         <v>7</v>
@@ -40345,10 +40345,10 @@
         <v>1</v>
       </c>
       <c r="R406" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S406" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="T406" t="inlineStr">
         <is>
@@ -40357,16 +40357,16 @@
       </c>
       <c r="U406" t="inlineStr"/>
       <c r="V406" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="W406" t="n">
-        <v>17.6</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Gabe Perreault</t>
+          <t>Pavel Dorofeyev</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -40384,50 +40384,54 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E407" t="inlineStr"/>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F407" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G407" t="n">
-        <v>15.7</v>
+        <v>17</v>
       </c>
       <c r="H407" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="I407" t="n">
         <v>7</v>
       </c>
       <c r="J407" t="n">
+        <v>1</v>
+      </c>
+      <c r="K407" t="n">
+        <v>2</v>
+      </c>
+      <c r="L407" t="n">
         <v>3</v>
       </c>
-      <c r="K407" t="n">
-        <v>3</v>
-      </c>
-      <c r="L407" t="n">
-        <v>6</v>
-      </c>
       <c r="M407" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="N407" t="n">
-        <v>15.7</v>
+        <v>17</v>
       </c>
       <c r="O407" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="P407" t="n">
         <v>7</v>
       </c>
       <c r="Q407" t="n">
+        <v>1</v>
+      </c>
+      <c r="R407" t="n">
         <v>3</v>
       </c>
-      <c r="R407" t="n">
-        <v>6</v>
-      </c>
       <c r="S407" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T407" t="inlineStr">
         <is>
@@ -40436,16 +40440,16 @@
       </c>
       <c r="U407" t="inlineStr"/>
       <c r="V407" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="W407" t="n">
-        <v>16</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Will Cuylle</t>
+          <t>Gabe Perreault</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -40455,7 +40459,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -40470,43 +40474,43 @@
         </is>
       </c>
       <c r="G408" t="n">
-        <v>15.4</v>
+        <v>15.7</v>
       </c>
       <c r="H408" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="I408" t="n">
         <v>7</v>
       </c>
       <c r="J408" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K408" t="n">
         <v>3</v>
       </c>
       <c r="L408" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M408" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N408" t="n">
-        <v>15.4</v>
+        <v>15.7</v>
       </c>
       <c r="O408" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="P408" t="n">
         <v>7</v>
       </c>
       <c r="Q408" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R408" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S408" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T408" t="inlineStr">
         <is>
@@ -40515,16 +40519,16 @@
       </c>
       <c r="U408" t="inlineStr"/>
       <c r="V408" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="W408" t="n">
-        <v>16.9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Marcus Pettersson</t>
+          <t>Will Cuylle</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -40534,12 +40538,12 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Top-4 D</t>
+          <t>Top-6 F</t>
         </is>
       </c>
       <c r="E409" t="inlineStr"/>
@@ -40549,43 +40553,43 @@
         </is>
       </c>
       <c r="G409" t="n">
-        <v>20.4</v>
+        <v>15.4</v>
       </c>
       <c r="H409" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="I409" t="n">
         <v>7</v>
       </c>
       <c r="J409" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K409" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L409" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M409" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="N409" t="n">
-        <v>20.4</v>
+        <v>15.4</v>
       </c>
       <c r="O409" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="P409" t="n">
         <v>7</v>
       </c>
       <c r="Q409" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R409" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S409" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T409" t="inlineStr">
         <is>
@@ -40597,13 +40601,13 @@
         <v>82</v>
       </c>
       <c r="W409" t="n">
-        <v>21.5</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Sean Durzi</t>
+          <t>Marcus Pettersson</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -40628,43 +40632,43 @@
         </is>
       </c>
       <c r="G410" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="H410" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="I410" t="n">
         <v>7</v>
       </c>
       <c r="J410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L410" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M410" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N410" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="O410" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="P410" t="n">
         <v>7</v>
       </c>
       <c r="Q410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R410" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S410" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T410" t="inlineStr">
         <is>
@@ -40673,16 +40677,16 @@
       </c>
       <c r="U410" t="inlineStr"/>
       <c r="V410" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="W410" t="n">
-        <v>19.3</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Tye Kartye</t>
+          <t>Sean Durzi</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -40692,12 +40696,12 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Depth F</t>
+          <t>Top-4 D</t>
         </is>
       </c>
       <c r="E411" t="inlineStr"/>
@@ -40707,43 +40711,43 @@
         </is>
       </c>
       <c r="G411" t="n">
-        <v>15</v>
+        <v>20.3</v>
       </c>
       <c r="H411" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I411" t="n">
         <v>7</v>
       </c>
       <c r="J411" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K411" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L411" t="n">
+        <v>2</v>
+      </c>
+      <c r="M411" t="n">
         <v>4</v>
       </c>
-      <c r="M411" t="n">
-        <v>8</v>
-      </c>
       <c r="N411" t="n">
-        <v>15</v>
+        <v>20.3</v>
       </c>
       <c r="O411" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="P411" t="n">
         <v>7</v>
       </c>
       <c r="Q411" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R411" t="n">
+        <v>2</v>
+      </c>
+      <c r="S411" t="n">
         <v>4</v>
-      </c>
-      <c r="S411" t="n">
-        <v>8</v>
       </c>
       <c r="T411" t="inlineStr">
         <is>
@@ -40752,16 +40756,16 @@
       </c>
       <c r="U411" t="inlineStr"/>
       <c r="V411" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="W411" t="n">
-        <v>12</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Noah Laba</t>
+          <t>Tye Kartye</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -40771,7 +40775,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -40786,43 +40790,43 @@
         </is>
       </c>
       <c r="G412" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="H412" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I412" t="n">
         <v>7</v>
       </c>
       <c r="J412" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K412" t="n">
         <v>2</v>
       </c>
       <c r="L412" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M412" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N412" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="O412" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P412" t="n">
         <v>7</v>
       </c>
       <c r="Q412" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R412" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S412" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T412" t="inlineStr">
         <is>
@@ -40831,16 +40835,16 @@
       </c>
       <c r="U412" t="inlineStr"/>
       <c r="V412" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="W412" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Eeli Tolvanen</t>
+          <t>Noah Laba</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -40850,7 +40854,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -40865,43 +40869,43 @@
         </is>
       </c>
       <c r="G413" t="n">
-        <v>13.1</v>
+        <v>14.4</v>
       </c>
       <c r="H413" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="I413" t="n">
         <v>7</v>
       </c>
       <c r="J413" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L413" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M413" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N413" t="n">
-        <v>13.1</v>
+        <v>14.4</v>
       </c>
       <c r="O413" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="P413" t="n">
         <v>7</v>
       </c>
       <c r="Q413" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R413" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S413" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T413" t="inlineStr">
         <is>
@@ -40910,16 +40914,16 @@
       </c>
       <c r="U413" t="inlineStr"/>
       <c r="V413" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="W413" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Joseph Veleno</t>
+          <t>Eeli Tolvanen</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -40929,7 +40933,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -40944,43 +40948,43 @@
         </is>
       </c>
       <c r="G414" t="n">
-        <v>11.6</v>
+        <v>13.1</v>
       </c>
       <c r="H414" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I414" t="n">
+        <v>7</v>
+      </c>
+      <c r="J414" t="n">
+        <v>3</v>
+      </c>
+      <c r="K414" t="n">
+        <v>1</v>
+      </c>
+      <c r="L414" t="n">
         <v>4</v>
       </c>
-      <c r="J414" t="n">
-        <v>0</v>
-      </c>
-      <c r="K414" t="n">
-        <v>0</v>
-      </c>
-      <c r="L414" t="n">
-        <v>0</v>
-      </c>
       <c r="M414" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N414" t="n">
-        <v>11.6</v>
+        <v>13.1</v>
       </c>
       <c r="O414" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="P414" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q414" t="n">
+        <v>3</v>
+      </c>
+      <c r="R414" t="n">
         <v>4</v>
       </c>
-      <c r="Q414" t="n">
-        <v>0</v>
-      </c>
-      <c r="R414" t="n">
-        <v>0</v>
-      </c>
       <c r="S414" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T414" t="inlineStr">
         <is>
@@ -40989,16 +40993,16 @@
       </c>
       <c r="U414" t="inlineStr"/>
       <c r="V414" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="W414" t="n">
-        <v>12.1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Adam Sykora</t>
+          <t>Joseph Veleno</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -41008,7 +41012,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -41019,17 +41023,17 @@
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G415" t="n">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="H415" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I415" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J415" t="n">
         <v>0</v>
@@ -41041,12 +41045,16 @@
         <v>0</v>
       </c>
       <c r="M415" t="n">
-        <v>0</v>
-      </c>
-      <c r="N415" t="inlineStr"/>
-      <c r="O415" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N415" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="O415" t="n">
+        <v>0</v>
+      </c>
       <c r="P415" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q415" t="n">
         <v>0</v>
@@ -41055,7 +41063,7 @@
         <v>0</v>
       </c>
       <c r="S415" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T415" t="inlineStr">
         <is>
@@ -41064,16 +41072,16 @@
       </c>
       <c r="U415" t="inlineStr"/>
       <c r="V415" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="W415" t="n">
-        <v>11.2</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Oliver Bjorkstrand</t>
+          <t>Adam Sykora</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -41083,7 +41091,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -41094,47 +41102,43 @@
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G416" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="H416" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="I416" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J416" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K416" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L416" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M416" t="n">
-        <v>10</v>
-      </c>
-      <c r="N416" t="n">
-        <v>11</v>
-      </c>
-      <c r="O416" t="n">
-        <v>0.9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N416" t="inlineStr"/>
+      <c r="O416" t="inlineStr"/>
       <c r="P416" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q416" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R416" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S416" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T416" t="inlineStr">
         <is>
@@ -41143,16 +41147,16 @@
       </c>
       <c r="U416" t="inlineStr"/>
       <c r="V416" t="n">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="W416" t="n">
-        <v>13.6</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Cole Beaudoin</t>
+          <t>Oliver Bjorkstrand</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -41162,7 +41166,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -41177,43 +41181,43 @@
         </is>
       </c>
       <c r="G417" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="H417" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="I417" t="n">
+        <v>7</v>
+      </c>
+      <c r="J417" t="n">
+        <v>2</v>
+      </c>
+      <c r="K417" t="n">
+        <v>1</v>
+      </c>
+      <c r="L417" t="n">
         <v>3</v>
       </c>
-      <c r="J417" t="n">
-        <v>0</v>
-      </c>
-      <c r="K417" t="n">
-        <v>0</v>
-      </c>
-      <c r="L417" t="n">
-        <v>0</v>
-      </c>
       <c r="M417" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N417" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="O417" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="P417" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>2</v>
+      </c>
+      <c r="R417" t="n">
         <v>3</v>
       </c>
-      <c r="Q417" t="n">
-        <v>0</v>
-      </c>
-      <c r="R417" t="n">
-        <v>0</v>
-      </c>
       <c r="S417" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T417" t="inlineStr">
         <is>
@@ -41222,16 +41226,16 @@
       </c>
       <c r="U417" t="inlineStr"/>
       <c r="V417" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="W417" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Matt Rempe</t>
+          <t>Cole Beaudoin</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -41252,17 +41256,17 @@
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G418" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="H418" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I418" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J418" t="n">
         <v>0</v>
@@ -41277,13 +41281,13 @@
         <v>1</v>
       </c>
       <c r="N418" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="O418" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P418" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q418" t="n">
         <v>0</v>
@@ -41301,16 +41305,16 @@
       </c>
       <c r="U418" t="inlineStr"/>
       <c r="V418" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="W418" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Jaroslav Chmelar</t>
+          <t>Matt Rempe</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -41320,7 +41324,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -41331,17 +41335,17 @@
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G419" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="H419" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I419" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J419" t="n">
         <v>0</v>
@@ -41353,16 +41357,16 @@
         <v>0</v>
       </c>
       <c r="M419" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N419" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O419" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P419" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q419" t="n">
         <v>0</v>
@@ -41371,7 +41375,7 @@
         <v>0</v>
       </c>
       <c r="S419" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T419" t="inlineStr">
         <is>
@@ -41380,16 +41384,16 @@
       </c>
       <c r="U419" t="inlineStr"/>
       <c r="V419" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="W419" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Alexis Lafrenière</t>
+          <t>Jaroslav Chmelar</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -41399,62 +41403,58 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Depth D</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Depth F</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr"/>
       <c r="F420" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G420" t="n">
-        <v>19.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H420" t="n">
-        <v>3.2</v>
+        <v>0.1</v>
       </c>
       <c r="I420" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J420" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K420" t="n">
+        <v>0</v>
+      </c>
+      <c r="L420" t="n">
+        <v>0</v>
+      </c>
+      <c r="M420" t="n">
         <v>3</v>
       </c>
-      <c r="L420" t="n">
-        <v>8</v>
-      </c>
-      <c r="M420" t="n">
-        <v>14</v>
-      </c>
       <c r="N420" t="n">
-        <v>19.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O420" t="n">
-        <v>3.2</v>
+        <v>0.1</v>
       </c>
       <c r="P420" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q420" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R420" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S420" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T420" t="inlineStr">
         <is>
@@ -41463,10 +41463,10 @@
       </c>
       <c r="U420" t="inlineStr"/>
       <c r="V420" t="n">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="W420" t="n">
-        <v>17.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="421">
@@ -43477,11 +43477,7 @@
           <t>Depth (no NHL data)</t>
         </is>
       </c>
-      <c r="E446" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr">
         <is>
           <t>no NHL data</t>

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 07:35</t>
+          <t>2026-10-13 08:34</t>
         </is>
       </c>
     </row>
@@ -10892,7 +10892,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Morgan Geekie</t>
+          <t>JJ Peterka</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -10921,43 +10921,43 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>17.4</v>
+        <v>16.6</v>
       </c>
       <c r="H29" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
         <v>6</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L29" t="n">
         <v>4</v>
       </c>
       <c r="M29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N29" t="n">
-        <v>17.4</v>
+        <v>16.6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="P29" t="n">
         <v>6</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
         <v>4</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -10966,16 +10966,16 @@
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W29" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JJ Peterka</t>
+          <t>Elias Lindholm</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -10993,30 +10993,26 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>16.6</v>
+        <v>16.1</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="I30" t="n">
         <v>6</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L30" t="n">
         <v>4</v>
@@ -11025,16 +11021,16 @@
         <v>10</v>
       </c>
       <c r="N30" t="n">
-        <v>16.6</v>
+        <v>16.1</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="P30" t="n">
         <v>6</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>4</v>
@@ -11049,16 +11045,16 @@
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="W30" t="n">
-        <v>16</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Elias Lindholm</t>
+          <t>Fraser Minten</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11083,43 +11079,43 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>16.1</v>
+        <v>15.4</v>
       </c>
       <c r="H31" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>6</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N31" t="n">
-        <v>16.1</v>
+        <v>15.4</v>
       </c>
       <c r="O31" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="P31" t="n">
         <v>6</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -11128,16 +11124,16 @@
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="W31" t="n">
-        <v>17.9</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Fraser Minten</t>
+          <t>Nikita Zadorov</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -11147,12 +11143,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Top-6 F</t>
+          <t>Top-4 D</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -11162,43 +11158,43 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>15.4</v>
+        <v>20.5</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I32" t="n">
         <v>6</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N32" t="n">
-        <v>15.4</v>
+        <v>20.5</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="P32" t="n">
         <v>6</v>
       </c>
       <c r="Q32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -11207,16 +11203,16 @@
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="W32" t="n">
-        <v>15.6</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nikita Zadorov</t>
+          <t>Hampus Lindholm</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -11241,43 +11237,43 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>20.5</v>
+        <v>19.7</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="I33" t="n">
         <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N33" t="n">
-        <v>20.5</v>
+        <v>19.7</v>
       </c>
       <c r="O33" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="P33" t="n">
         <v>6</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -11286,16 +11282,16 @@
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="W33" t="n">
-        <v>20.9</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Hampus Lindholm</t>
+          <t>Morgan Geekie</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -11305,7 +11301,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -11313,17 +11309,21 @@
           <t>Top-4 D</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>19.7</v>
+        <v>17.4</v>
       </c>
       <c r="H34" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="I34" t="n">
         <v>6</v>
@@ -11338,13 +11338,13 @@
         <v>4</v>
       </c>
       <c r="M34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N34" t="n">
-        <v>19.7</v>
+        <v>17.4</v>
       </c>
       <c r="O34" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="P34" t="n">
         <v>6</v>
@@ -11356,7 +11356,7 @@
         <v>4</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -11365,10 +11365,10 @@
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="W34" t="n">
-        <v>21.6</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="35">
@@ -14072,7 +14072,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>K'Andre Miller</t>
+          <t>Sebastian Aho</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -14082,58 +14082,62 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Top-pair D</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
+          <t>Top-line C</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>22.4</v>
+        <v>19.4</v>
       </c>
       <c r="H69" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="I69" t="n">
         <v>7</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L69" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M69" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="N69" t="n">
-        <v>22.4</v>
+        <v>19.4</v>
       </c>
       <c r="O69" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="P69" t="n">
         <v>7</v>
       </c>
       <c r="Q69" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R69" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -14142,16 +14146,16 @@
       </c>
       <c r="U69" t="inlineStr"/>
       <c r="V69" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="W69" t="n">
-        <v>22.4</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sean Walker</t>
+          <t>K'Andre Miller</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -14176,43 +14180,43 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>21.4</v>
+        <v>22.4</v>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="I70" t="n">
         <v>7</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N70" t="n">
-        <v>21.4</v>
+        <v>22.4</v>
       </c>
       <c r="O70" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="P70" t="n">
         <v>7</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -14221,16 +14225,16 @@
       </c>
       <c r="U70" t="inlineStr"/>
       <c r="V70" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="W70" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Jackson Blake</t>
+          <t>Sean Walker</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -14240,62 +14244,58 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Top-6 F</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Top-pair D</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>18.2</v>
+        <v>21.4</v>
       </c>
       <c r="H71" t="n">
-        <v>5.4</v>
+        <v>1</v>
       </c>
       <c r="I71" t="n">
         <v>7</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L71" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N71" t="n">
-        <v>18.2</v>
+        <v>21.4</v>
       </c>
       <c r="O71" t="n">
-        <v>5.4</v>
+        <v>1</v>
       </c>
       <c r="P71" t="n">
         <v>7</v>
       </c>
       <c r="Q71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -14307,13 +14307,13 @@
         <v>81</v>
       </c>
       <c r="W71" t="n">
-        <v>16.5</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Logan Stankoven</t>
+          <t>Jackson Blake</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14331,50 +14331,54 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>17.7</v>
+        <v>18.2</v>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
+        <v>5.4</v>
       </c>
       <c r="I72" t="n">
         <v>7</v>
       </c>
       <c r="J72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L72" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M72" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N72" t="n">
-        <v>17.7</v>
+        <v>18.2</v>
       </c>
       <c r="O72" t="n">
-        <v>2</v>
+        <v>5.4</v>
       </c>
       <c r="P72" t="n">
         <v>7</v>
       </c>
       <c r="Q72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S72" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -14386,13 +14390,13 @@
         <v>81</v>
       </c>
       <c r="W72" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Andrei Svechnikov</t>
+          <t>Logan Stankoven</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -14402,7 +14406,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14410,21 +14414,17 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>17</v>
+        <v>17.7</v>
       </c>
       <c r="H73" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="I73" t="n">
         <v>7</v>
@@ -14433,19 +14433,19 @@
         <v>4</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M73" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N73" t="n">
-        <v>17</v>
+        <v>17.7</v>
       </c>
       <c r="O73" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="P73" t="n">
         <v>7</v>
@@ -14454,10 +14454,10 @@
         <v>4</v>
       </c>
       <c r="R73" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S73" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -14466,16 +14466,16 @@
       </c>
       <c r="U73" t="inlineStr"/>
       <c r="V73" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="W73" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Nikolaj Ehlers</t>
+          <t>Andrei Svechnikov</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -14485,7 +14485,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14504,43 +14504,43 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>15.7</v>
+        <v>17</v>
       </c>
       <c r="H74" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I74" t="n">
         <v>7</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L74" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M74" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="N74" t="n">
-        <v>15.7</v>
+        <v>17</v>
       </c>
       <c r="O74" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="P74" t="n">
         <v>7</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R74" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S74" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -14549,16 +14549,16 @@
       </c>
       <c r="U74" t="inlineStr"/>
       <c r="V74" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="W74" t="n">
-        <v>16.6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Jordan Staal</t>
+          <t>Nikolaj Ehlers</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -14568,7 +14568,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -14576,50 +14576,54 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="H75" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="I75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M75" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N75" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="O75" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="P75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -14628,16 +14632,16 @@
       </c>
       <c r="U75" t="inlineStr"/>
       <c r="V75" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="W75" t="n">
-        <v>16.2</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Jaccob Slavin</t>
+          <t>Jordan Staal</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -14647,12 +14651,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Top-4 D</t>
+          <t>Top-6 F</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -14662,43 +14666,43 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>20.9</v>
+        <v>15.6</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="I76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N76" t="n">
-        <v>20.9</v>
+        <v>15.6</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -14707,16 +14711,16 @@
       </c>
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="W76" t="n">
-        <v>21.3</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Jalen Chatfield</t>
+          <t>Jaccob Slavin</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -14741,10 +14745,10 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>20.4</v>
+        <v>20.9</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
         <v>7</v>
@@ -14759,13 +14763,13 @@
         <v>2</v>
       </c>
       <c r="M77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N77" t="n">
-        <v>20.4</v>
+        <v>20.9</v>
       </c>
       <c r="O77" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
         <v>7</v>
@@ -14777,7 +14781,7 @@
         <v>2</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -14786,16 +14790,16 @@
       </c>
       <c r="U77" t="inlineStr"/>
       <c r="V77" t="n">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="W77" t="n">
-        <v>20.1</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sebastian Aho</t>
+          <t>Jalen Chatfield</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -14805,62 +14809,58 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Depth F</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Top-4 D</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>19.4</v>
+        <v>20.4</v>
       </c>
       <c r="H78" t="n">
-        <v>4.8</v>
+        <v>0.1</v>
       </c>
       <c r="I78" t="n">
         <v>7</v>
       </c>
       <c r="J78" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L78" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M78" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="N78" t="n">
-        <v>19.4</v>
+        <v>20.4</v>
       </c>
       <c r="O78" t="n">
-        <v>4.8</v>
+        <v>0.1</v>
       </c>
       <c r="P78" t="n">
         <v>7</v>
       </c>
       <c r="Q78" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="S78" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -14869,10 +14869,10 @@
       </c>
       <c r="U78" t="inlineStr"/>
       <c r="V78" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="W78" t="n">
-        <v>19.6</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="79">
@@ -15992,7 +15992,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Damon Severson</t>
+          <t>Charlie Coyle</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -16002,12 +16002,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Top-pair D</t>
+          <t>Top-6 F</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -16017,47 +16017,47 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>21.1</v>
+        <v>18.6</v>
       </c>
       <c r="H93" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M93" t="n">
+        <v>9</v>
+      </c>
+      <c r="N93" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="O93" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P93" t="n">
         <v>4</v>
       </c>
-      <c r="N93" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P93" t="n">
-        <v>2</v>
-      </c>
       <c r="Q93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -16066,16 +16066,16 @@
       </c>
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="W93" t="n">
-        <v>21.1</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Charlie Coyle</t>
+          <t>Matthew Knies</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -16085,7 +16085,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -16104,43 +16104,43 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>18.6</v>
+        <v>17.3</v>
       </c>
       <c r="H94" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="I94" t="n">
         <v>4</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K94" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L94" t="n">
         <v>4</v>
       </c>
       <c r="M94" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N94" t="n">
-        <v>18.6</v>
+        <v>17.3</v>
       </c>
       <c r="O94" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P94" t="n">
         <v>4</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R94" t="n">
         <v>4</v>
       </c>
       <c r="S94" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -16149,16 +16149,16 @@
       </c>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="W94" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Matthew Knies</t>
+          <t>Kent Johnson</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -16168,7 +16168,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -16187,10 +16187,10 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>17.3</v>
+        <v>16.8</v>
       </c>
       <c r="H95" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="I95" t="n">
         <v>4</v>
@@ -16199,19 +16199,19 @@
         <v>2</v>
       </c>
       <c r="K95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M95" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N95" t="n">
-        <v>17.3</v>
+        <v>16.8</v>
       </c>
       <c r="O95" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P95" t="n">
         <v>4</v>
@@ -16220,10 +16220,10 @@
         <v>2</v>
       </c>
       <c r="R95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S95" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -16232,16 +16232,16 @@
       </c>
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="W95" t="n">
-        <v>18.8</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Kent Johnson</t>
+          <t>Sean Monahan</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -16259,11 +16259,7 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>last games</t>
@@ -16273,40 +16269,40 @@
         <v>16.8</v>
       </c>
       <c r="H96" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="I96" t="n">
         <v>4</v>
       </c>
       <c r="J96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
         <v>1</v>
       </c>
       <c r="L96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M96" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N96" t="n">
         <v>16.8</v>
       </c>
       <c r="O96" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="P96" t="n">
         <v>4</v>
       </c>
       <c r="Q96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S96" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -16315,16 +16311,16 @@
       </c>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="W96" t="n">
-        <v>13.2</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sean Monahan</t>
+          <t>Valeri Nichushkin</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -16334,7 +16330,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16349,10 +16345,10 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>16.8</v>
+        <v>16.3</v>
       </c>
       <c r="H97" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="I97" t="n">
         <v>4</v>
@@ -16367,13 +16363,13 @@
         <v>2</v>
       </c>
       <c r="M97" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N97" t="n">
-        <v>16.8</v>
+        <v>16.3</v>
       </c>
       <c r="O97" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="P97" t="n">
         <v>4</v>
@@ -16385,7 +16381,7 @@
         <v>2</v>
       </c>
       <c r="S97" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -16394,16 +16390,16 @@
       </c>
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="W97" t="n">
-        <v>17.1</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Valeri Nichushkin</t>
+          <t>Ivan Provorov</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -16413,58 +16409,54 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Top-6 F</t>
+          <t>Top-4 D</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>16.3</v>
+        <v>24.8</v>
       </c>
       <c r="H98" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>7</v>
-      </c>
-      <c r="N98" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="O98" t="n">
-        <v>1.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
       <c r="P98" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -16473,16 +16465,16 @@
       </c>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="W98" t="n">
-        <v>17.7</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ivan Provorov</t>
+          <t>Damon Severson</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -16500,46 +16492,54 @@
           <t>Top-4 D</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr">
         <is>
           <t>last season</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>24.8</v>
+        <v>21.1</v>
       </c>
       <c r="H99" t="n">
         <v>1.1</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="N99" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.2</v>
+      </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -16548,10 +16548,10 @@
       </c>
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="W99" t="n">
-        <v>24.8</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="100">
@@ -20786,11 +20786,7 @@
           <t>Depth F</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>last season</t>
@@ -31513,7 +31509,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Jared Wright</t>
+          <t>Andre Lee</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -31523,7 +31519,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -31538,13 +31534,13 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
       </c>
       <c r="I288" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -31556,16 +31552,16 @@
         <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N288" t="n">
-        <v>10.4</v>
+        <v>9.4</v>
       </c>
       <c r="O288" t="n">
         <v>0</v>
       </c>
       <c r="P288" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q288" t="n">
         <v>0</v>
@@ -31574,7 +31570,7 @@
         <v>0</v>
       </c>
       <c r="S288" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -31583,16 +31579,16 @@
       </c>
       <c r="U288" t="inlineStr"/>
       <c r="V288" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="W288" t="n">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Andre Lee</t>
+          <t>Samuel Helenius</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -31602,7 +31598,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -31617,7 +31613,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>10.3</v>
+        <v>8</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -31635,10 +31631,10 @@
         <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N289" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="O289" t="n">
         <v>0</v>
@@ -31653,7 +31649,7 @@
         <v>0</v>
       </c>
       <c r="S289" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -31662,16 +31658,16 @@
       </c>
       <c r="U289" t="inlineStr"/>
       <c r="V289" t="n">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="W289" t="n">
-        <v>10.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Samuel Helenius</t>
+          <t>Mikey Anderson</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -31681,58 +31677,58 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Depth F</t>
+          <t>Depth D</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G290" t="n">
-        <v>8</v>
+        <v>18.5</v>
       </c>
       <c r="H290" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I290" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
       </c>
       <c r="K290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M290" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N290" t="n">
-        <v>8</v>
+        <v>18.5</v>
       </c>
       <c r="O290" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P290" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q290" t="n">
         <v>0</v>
       </c>
       <c r="R290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S290" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T290" t="inlineStr">
         <is>
@@ -31741,16 +31737,16 @@
       </c>
       <c r="U290" t="inlineStr"/>
       <c r="V290" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="W290" t="n">
-        <v>8</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Mikey Anderson</t>
+          <t>Brian Dumoulin</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -31775,7 +31771,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>18.5</v>
+        <v>16.3</v>
       </c>
       <c r="H291" t="n">
         <v>0.1</v>
@@ -31784,19 +31780,19 @@
         <v>4</v>
       </c>
       <c r="J291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K291" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L291" t="n">
         <v>1</v>
       </c>
       <c r="M291" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N291" t="n">
-        <v>18.5</v>
+        <v>16.3</v>
       </c>
       <c r="O291" t="n">
         <v>0.1</v>
@@ -31805,13 +31801,13 @@
         <v>4</v>
       </c>
       <c r="Q291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R291" t="n">
         <v>1</v>
       </c>
       <c r="S291" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T291" t="inlineStr">
         <is>
@@ -31820,16 +31816,16 @@
       </c>
       <c r="U291" t="inlineStr"/>
       <c r="V291" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="W291" t="n">
-        <v>20.6</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Brian Dumoulin</t>
+          <t>Joel Edmundson</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -31854,40 +31850,40 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>16.3</v>
+        <v>14.4</v>
       </c>
       <c r="H292" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I292" t="n">
         <v>4</v>
       </c>
       <c r="J292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M292" t="n">
         <v>4</v>
       </c>
       <c r="N292" t="n">
-        <v>16.3</v>
+        <v>14.4</v>
       </c>
       <c r="O292" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P292" t="n">
         <v>4</v>
       </c>
       <c r="Q292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S292" t="n">
         <v>4</v>
@@ -31902,13 +31898,13 @@
         <v>82</v>
       </c>
       <c r="W292" t="n">
-        <v>17.8</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Joel Edmundson</t>
+          <t>Jared Wright</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -31918,7 +31914,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -31929,17 +31925,17 @@
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G293" t="n">
-        <v>14.4</v>
+        <v>11.4</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
       </c>
       <c r="I293" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J293" t="n">
         <v>0</v>
@@ -31951,16 +31947,16 @@
         <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N293" t="n">
-        <v>14.4</v>
+        <v>10.4</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
       </c>
       <c r="P293" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q293" t="n">
         <v>0</v>
@@ -31969,7 +31965,7 @@
         <v>0</v>
       </c>
       <c r="S293" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T293" t="inlineStr">
         <is>
@@ -31978,10 +31974,10 @@
       </c>
       <c r="U293" t="inlineStr"/>
       <c r="V293" t="n">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="W293" t="n">
-        <v>18.5</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="294">

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 07:44</t>
+          <t>2026-10-15 08:45</t>
         </is>
       </c>
     </row>
@@ -27564,7 +27564,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Matt Savoie</t>
+          <t>Owen Michaels</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -27574,7 +27574,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -27585,43 +27585,47 @@
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G239" t="n">
-        <v>14.8</v>
+        <v>13.4</v>
       </c>
       <c r="H239" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="I239" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
-      </c>
-      <c r="N239" t="inlineStr"/>
-      <c r="O239" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="N239" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="O239" t="n">
+        <v>0.1</v>
+      </c>
       <c r="P239" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S239" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -27630,16 +27634,16 @@
       </c>
       <c r="U239" t="inlineStr"/>
       <c r="V239" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="W239" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Owen Michaels</t>
+          <t>Colton Dach</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -27649,7 +27653,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -27667,40 +27671,40 @@
         <v>13.4</v>
       </c>
       <c r="H240" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I240" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J240" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K240" t="n">
         <v>0</v>
       </c>
       <c r="L240" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N240" t="n">
         <v>13.4</v>
       </c>
       <c r="O240" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="P240" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q240" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R240" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S240" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -27709,16 +27713,16 @@
       </c>
       <c r="U240" t="inlineStr"/>
       <c r="V240" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="W240" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Colton Dach</t>
+          <t>Jason Dickinson</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -27743,10 +27747,10 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>13.4</v>
+        <v>12.2</v>
       </c>
       <c r="H241" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="I241" t="n">
         <v>3</v>
@@ -27755,19 +27759,19 @@
         <v>0</v>
       </c>
       <c r="K241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M241" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N241" t="n">
-        <v>13.4</v>
+        <v>12.2</v>
       </c>
       <c r="O241" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="P241" t="n">
         <v>3</v>
@@ -27776,10 +27780,10 @@
         <v>0</v>
       </c>
       <c r="R241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S241" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -27788,16 +27792,16 @@
       </c>
       <c r="U241" t="inlineStr"/>
       <c r="V241" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="W241" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Jason Dickinson</t>
+          <t>Mattias Janmark</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -27818,47 +27822,43 @@
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G242" t="n">
-        <v>12.2</v>
+        <v>11.9</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
       </c>
       <c r="I242" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
       </c>
       <c r="K242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>2</v>
-      </c>
-      <c r="N242" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="O242" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr"/>
       <c r="P242" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q242" t="n">
         <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S242" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -27867,16 +27867,16 @@
       </c>
       <c r="U242" t="inlineStr"/>
       <c r="V242" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="W242" t="n">
-        <v>15.5</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Mattias Janmark</t>
+          <t>Filip Hallander</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -27897,43 +27897,47 @@
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G243" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="H243" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I243" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K243" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M243" t="n">
-        <v>0</v>
-      </c>
-      <c r="N243" t="inlineStr"/>
-      <c r="O243" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="N243" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0.4</v>
+      </c>
       <c r="P243" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R243" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S243" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -27942,16 +27946,16 @@
       </c>
       <c r="U243" t="inlineStr"/>
       <c r="V243" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="W243" t="n">
-        <v>11.9</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Filip Hallander</t>
+          <t>Max Jones</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -27961,7 +27965,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -27976,40 +27980,40 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
       <c r="H244" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I244" t="n">
         <v>4</v>
       </c>
       <c r="J244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K244" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L244" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M244" t="n">
         <v>4</v>
       </c>
       <c r="N244" t="n">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
       <c r="O244" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="P244" t="n">
         <v>4</v>
       </c>
       <c r="Q244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S244" t="n">
         <v>4</v>
@@ -28021,16 +28025,16 @@
       </c>
       <c r="U244" t="inlineStr"/>
       <c r="V244" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="W244" t="n">
-        <v>13.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Max Jones</t>
+          <t>Trent Frederic</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -28040,7 +28044,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -28055,43 +28059,43 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>10.3</v>
+        <v>9.6</v>
       </c>
       <c r="H245" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="I245" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K245" t="n">
         <v>0</v>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M245" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N245" t="n">
-        <v>10.3</v>
+        <v>9.6</v>
       </c>
       <c r="O245" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="P245" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S245" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -28100,16 +28104,16 @@
       </c>
       <c r="U245" t="inlineStr"/>
       <c r="V245" t="n">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="W245" t="n">
-        <v>8.300000000000001</v>
+        <v>11</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Trent Frederic</t>
+          <t>Isaac Howard</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -28119,7 +28123,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -28134,7 +28138,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="H246" t="n">
         <v>1.6</v>
@@ -28143,19 +28147,19 @@
         <v>6</v>
       </c>
       <c r="J246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K246" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M246" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N246" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="O246" t="n">
         <v>1.6</v>
@@ -28164,13 +28168,13 @@
         <v>6</v>
       </c>
       <c r="Q246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S246" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -28179,16 +28183,16 @@
       </c>
       <c r="U246" t="inlineStr"/>
       <c r="V246" t="n">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="W246" t="n">
-        <v>11</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Isaac Howard</t>
+          <t>Josh Samanski</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -28198,7 +28202,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -28213,43 +28217,43 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="H247" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="I247" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
       </c>
       <c r="K247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M247" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="O247" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="P247" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q247" t="n">
         <v>0</v>
       </c>
       <c r="R247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S247" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -28258,16 +28262,16 @@
       </c>
       <c r="U247" t="inlineStr"/>
       <c r="V247" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="W247" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Josh Samanski</t>
+          <t>Jake Walman</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -28277,12 +28281,12 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Depth F</t>
+          <t>Depth D</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -28292,43 +28296,43 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>7.5</v>
+        <v>14.8</v>
       </c>
       <c r="H248" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="I248" t="n">
+        <v>4</v>
+      </c>
+      <c r="J248" t="n">
+        <v>0</v>
+      </c>
+      <c r="K248" t="n">
+        <v>0</v>
+      </c>
+      <c r="L248" t="n">
+        <v>0</v>
+      </c>
+      <c r="M248" t="n">
         <v>5</v>
       </c>
-      <c r="J248" t="n">
-        <v>0</v>
-      </c>
-      <c r="K248" t="n">
-        <v>1</v>
-      </c>
-      <c r="L248" t="n">
-        <v>1</v>
-      </c>
-      <c r="M248" t="n">
-        <v>0</v>
-      </c>
       <c r="N248" t="n">
-        <v>7.5</v>
+        <v>14.8</v>
       </c>
       <c r="O248" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="P248" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>0</v>
+      </c>
+      <c r="R248" t="n">
+        <v>0</v>
+      </c>
+      <c r="S248" t="n">
         <v>5</v>
-      </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
-      <c r="R248" t="n">
-        <v>1</v>
-      </c>
-      <c r="S248" t="n">
-        <v>0</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -28337,16 +28341,16 @@
       </c>
       <c r="U248" t="inlineStr"/>
       <c r="V248" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="W248" t="n">
-        <v>10.6</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Jake Walman</t>
+          <t>Matt Savoie</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -28356,7 +28360,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -28367,17 +28371,17 @@
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G249" t="n">
         <v>14.8</v>
       </c>
       <c r="H249" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="I249" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -28389,16 +28393,12 @@
         <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>5</v>
-      </c>
-      <c r="N249" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="O249" t="n">
-        <v>2.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr"/>
       <c r="P249" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q249" t="n">
         <v>0</v>
@@ -28407,7 +28407,7 @@
         <v>0</v>
       </c>
       <c r="S249" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -28416,10 +28416,10 @@
       </c>
       <c r="U249" t="inlineStr"/>
       <c r="V249" t="n">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="W249" t="n">
-        <v>18.8</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="250">
@@ -31297,7 +31297,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Jared Wright</t>
+          <t>Trevor Moore</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -31307,58 +31307,58 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Top-4 D</t>
+          <t>Depth F</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G286" t="n">
-        <v>11.4</v>
+        <v>16.4</v>
       </c>
       <c r="H286" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I286" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M286" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N286" t="n">
-        <v>10.4</v>
+        <v>16.4</v>
       </c>
       <c r="O286" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P286" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R286" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S286" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T286" t="inlineStr">
         <is>
@@ -31367,16 +31367,16 @@
       </c>
       <c r="U286" t="inlineStr"/>
       <c r="V286" t="n">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="W286" t="n">
-        <v>11.4</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Trevor Moore</t>
+          <t>Erik Haula</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -31401,10 +31401,10 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>16.4</v>
+        <v>15.9</v>
       </c>
       <c r="H287" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="I287" t="n">
         <v>5</v>
@@ -31413,19 +31413,19 @@
         <v>1</v>
       </c>
       <c r="K287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L287" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M287" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N287" t="n">
-        <v>16.4</v>
+        <v>15.9</v>
       </c>
       <c r="O287" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="P287" t="n">
         <v>5</v>
@@ -31434,10 +31434,10 @@
         <v>1</v>
       </c>
       <c r="R287" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S287" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T287" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
       </c>
       <c r="U287" t="inlineStr"/>
       <c r="V287" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="W287" t="n">
         <v>16.7</v>
@@ -31455,7 +31455,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Erik Haula</t>
+          <t>Alex Turcotte</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -31465,7 +31465,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -31480,43 +31480,43 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>15.9</v>
+        <v>14.1</v>
       </c>
       <c r="H288" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="I288" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K288" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L288" t="n">
+        <v>1</v>
+      </c>
+      <c r="M288" t="n">
+        <v>1</v>
+      </c>
+      <c r="N288" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="O288" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P288" t="n">
         <v>3</v>
       </c>
-      <c r="M288" t="n">
-        <v>14</v>
-      </c>
-      <c r="N288" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="O288" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P288" t="n">
-        <v>5</v>
-      </c>
       <c r="Q288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R288" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S288" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -31525,16 +31525,16 @@
       </c>
       <c r="U288" t="inlineStr"/>
       <c r="V288" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="W288" t="n">
-        <v>16.7</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Alex Turcotte</t>
+          <t>Joel Armia</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -31544,7 +31544,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -31559,43 +31559,43 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>14.1</v>
+        <v>13.4</v>
       </c>
       <c r="H289" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="I289" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L289" t="n">
         <v>1</v>
       </c>
       <c r="M289" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N289" t="n">
-        <v>14.1</v>
+        <v>13.4</v>
       </c>
       <c r="O289" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="P289" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R289" t="n">
         <v>1</v>
       </c>
       <c r="S289" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -31604,16 +31604,16 @@
       </c>
       <c r="U289" t="inlineStr"/>
       <c r="V289" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="W289" t="n">
-        <v>10.8</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Joel Armia</t>
+          <t>Corey Perry</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -31638,40 +31638,40 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>13.4</v>
+        <v>12.3</v>
       </c>
       <c r="H290" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="I290" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
       </c>
       <c r="L290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M290" t="n">
         <v>6</v>
       </c>
       <c r="N290" t="n">
-        <v>13.4</v>
+        <v>12.3</v>
       </c>
       <c r="O290" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="P290" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S290" t="n">
         <v>6</v>
@@ -31683,16 +31683,16 @@
       </c>
       <c r="U290" t="inlineStr"/>
       <c r="V290" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="W290" t="n">
-        <v>14.1</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Corey Perry</t>
+          <t>Jared Wright</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -31713,17 +31713,17 @@
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G291" t="n">
-        <v>12.3</v>
+        <v>11.4</v>
       </c>
       <c r="H291" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="I291" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J291" t="n">
         <v>0</v>
@@ -31735,16 +31735,16 @@
         <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N291" t="n">
-        <v>12.3</v>
+        <v>10.4</v>
       </c>
       <c r="O291" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P291" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q291" t="n">
         <v>0</v>
@@ -31753,7 +31753,7 @@
         <v>0</v>
       </c>
       <c r="S291" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T291" t="inlineStr">
         <is>
@@ -31762,10 +31762,10 @@
       </c>
       <c r="U291" t="inlineStr"/>
       <c r="V291" t="n">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="W291" t="n">
-        <v>13.7</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="292">
@@ -65589,7 +65589,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>Justin Holl</t>
+          <t>Alex Ovechkin</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -65599,7 +65599,7 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -65607,50 +65607,54 @@
           <t>Depth F</t>
         </is>
       </c>
-      <c r="E714" t="inlineStr"/>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G714" t="n">
-        <v>15.7</v>
+        <v>13.9</v>
       </c>
       <c r="H714" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="I714" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J714" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K714" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L714" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M714" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N714" t="n">
-        <v>12.6</v>
+        <v>13.9</v>
       </c>
       <c r="O714" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P714" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q714" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R714" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S714" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T714" t="inlineStr">
         <is>
@@ -65659,16 +65663,16 @@
       </c>
       <c r="U714" t="inlineStr"/>
       <c r="V714" t="n">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="W714" t="n">
-        <v>15.7</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>Alex Ovechkin</t>
+          <t>Ryan Leonard</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -65678,7 +65682,7 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -65686,11 +65690,7 @@
           <t>Depth F</t>
         </is>
       </c>
-      <c r="E715" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E715" t="inlineStr"/>
       <c r="F715" t="inlineStr">
         <is>
           <t>last games</t>
@@ -65700,40 +65700,40 @@
         <v>13.9</v>
       </c>
       <c r="H715" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="I715" t="n">
         <v>7</v>
       </c>
       <c r="J715" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K715" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L715" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M715" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="N715" t="n">
         <v>13.9</v>
       </c>
       <c r="O715" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="P715" t="n">
         <v>7</v>
       </c>
       <c r="Q715" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R715" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S715" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T715" t="inlineStr">
         <is>
@@ -65742,16 +65742,16 @@
       </c>
       <c r="U715" t="inlineStr"/>
       <c r="V715" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="W715" t="n">
-        <v>17.4</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>Ryan Leonard</t>
+          <t>Justin Sourdif</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -65761,7 +65761,7 @@
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -65776,43 +65776,43 @@
         </is>
       </c>
       <c r="G716" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="H716" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I716" t="n">
         <v>7</v>
       </c>
       <c r="J716" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K716" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L716" t="n">
+        <v>1</v>
+      </c>
+      <c r="M716" t="n">
         <v>6</v>
       </c>
-      <c r="M716" t="n">
-        <v>17</v>
-      </c>
       <c r="N716" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="O716" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P716" t="n">
         <v>7</v>
       </c>
       <c r="Q716" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R716" t="n">
+        <v>1</v>
+      </c>
+      <c r="S716" t="n">
         <v>6</v>
-      </c>
-      <c r="S716" t="n">
-        <v>17</v>
       </c>
       <c r="T716" t="inlineStr">
         <is>
@@ -65821,16 +65821,16 @@
       </c>
       <c r="U716" t="inlineStr"/>
       <c r="V716" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W716" t="n">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>Justin Sourdif</t>
+          <t>Jordan Kyrou</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -65840,7 +65840,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
@@ -65855,43 +65855,43 @@
         </is>
       </c>
       <c r="G717" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="H717" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I717" t="n">
         <v>7</v>
       </c>
       <c r="J717" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K717" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L717" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M717" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N717" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="O717" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P717" t="n">
         <v>7</v>
       </c>
       <c r="Q717" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R717" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S717" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T717" t="inlineStr">
         <is>
@@ -65900,16 +65900,16 @@
       </c>
       <c r="U717" t="inlineStr"/>
       <c r="V717" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="W717" t="n">
-        <v>14.7</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>Jordan Kyrou</t>
+          <t>Ethen Frank</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -65930,47 +65930,47 @@
       <c r="E718" t="inlineStr"/>
       <c r="F718" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G718" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="H718" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I718" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J718" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K718" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L718" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M718" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N718" t="n">
-        <v>13.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O718" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="P718" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q718" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R718" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S718" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T718" t="inlineStr">
         <is>
@@ -65979,16 +65979,16 @@
       </c>
       <c r="U718" t="inlineStr"/>
       <c r="V718" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="W718" t="n">
-        <v>15.7</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>Ethen Frank</t>
+          <t>Ilya Protas</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -65998,7 +65998,7 @@
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -66009,47 +66009,47 @@
       <c r="E719" t="inlineStr"/>
       <c r="F719" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G719" t="n">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
       <c r="H719" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="I719" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J719" t="n">
         <v>0</v>
       </c>
       <c r="K719" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L719" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M719" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N719" t="n">
-        <v>9.699999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="O719" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="P719" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q719" t="n">
         <v>0</v>
       </c>
       <c r="R719" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S719" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T719" t="inlineStr">
         <is>
@@ -66058,16 +66058,16 @@
       </c>
       <c r="U719" t="inlineStr"/>
       <c r="V719" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="W719" t="n">
-        <v>12.2</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>Ilya Protas</t>
+          <t>Anthony Beauvillier</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
@@ -66077,7 +66077,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -66092,43 +66092,43 @@
         </is>
       </c>
       <c r="G720" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="H720" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="I720" t="n">
         <v>7</v>
       </c>
       <c r="J720" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K720" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L720" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M720" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N720" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="O720" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="P720" t="n">
         <v>7</v>
       </c>
       <c r="Q720" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R720" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S720" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T720" t="inlineStr">
         <is>
@@ -66137,16 +66137,16 @@
       </c>
       <c r="U720" t="inlineStr"/>
       <c r="V720" t="n">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="W720" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>Anthony Beauvillier</t>
+          <t>Ivan Miroshnichenko</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -66156,7 +66156,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
@@ -66167,17 +66167,17 @@
       <c r="E721" t="inlineStr"/>
       <c r="F721" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G721" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="H721" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I721" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J721" t="n">
         <v>1</v>
@@ -66189,16 +66189,16 @@
         <v>1</v>
       </c>
       <c r="M721" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N721" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="O721" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="P721" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q721" t="n">
         <v>1</v>
@@ -66207,7 +66207,7 @@
         <v>1</v>
       </c>
       <c r="S721" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T721" t="inlineStr">
         <is>
@@ -66216,16 +66216,16 @@
       </c>
       <c r="U721" t="inlineStr"/>
       <c r="V721" t="n">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="W721" t="n">
-        <v>15.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>Ivan Miroshnichenko</t>
+          <t>Timothy Liljegren</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
@@ -66235,28 +66235,28 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Depth F</t>
+          <t>Depth D</t>
         </is>
       </c>
       <c r="E722" t="inlineStr"/>
       <c r="F722" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G722" t="n">
-        <v>9.6</v>
+        <v>18.5</v>
       </c>
       <c r="H722" t="n">
         <v>0</v>
       </c>
       <c r="I722" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J722" t="n">
         <v>1</v>
@@ -66268,16 +66268,16 @@
         <v>1</v>
       </c>
       <c r="M722" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N722" t="n">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="O722" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="P722" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q722" t="n">
         <v>1</v>
@@ -66286,7 +66286,7 @@
         <v>1</v>
       </c>
       <c r="S722" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T722" t="inlineStr">
         <is>
@@ -66295,16 +66295,16 @@
       </c>
       <c r="U722" t="inlineStr"/>
       <c r="V722" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="W722" t="n">
-        <v>9.6</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>Timothy Liljegren</t>
+          <t>Cole Hutson</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
@@ -66332,7 +66332,7 @@
         <v>18.5</v>
       </c>
       <c r="H723" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I723" t="n">
         <v>7</v>
@@ -66341,19 +66341,19 @@
         <v>1</v>
       </c>
       <c r="K723" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L723" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M723" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="N723" t="n">
         <v>18.5</v>
       </c>
       <c r="O723" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P723" t="n">
         <v>7</v>
@@ -66362,10 +66362,10 @@
         <v>1</v>
       </c>
       <c r="R723" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S723" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="T723" t="inlineStr">
         <is>
@@ -66374,16 +66374,16 @@
       </c>
       <c r="U723" t="inlineStr"/>
       <c r="V723" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="W723" t="n">
-        <v>19.9</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>Cole Hutson</t>
+          <t>Justin Holl</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
@@ -66404,47 +66404,47 @@
       <c r="E724" t="inlineStr"/>
       <c r="F724" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G724" t="n">
-        <v>18.5</v>
+        <v>15.7</v>
       </c>
       <c r="H724" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I724" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J724" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K724" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L724" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M724" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="N724" t="n">
-        <v>18.5</v>
+        <v>12.6</v>
       </c>
       <c r="O724" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P724" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q724" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R724" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S724" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="T724" t="inlineStr">
         <is>
@@ -66453,10 +66453,10 @@
       </c>
       <c r="U724" t="inlineStr"/>
       <c r="V724" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W724" t="n">
-        <v>17.5</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="725">

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 07:37</t>
+          <t>2026-10-17 08:37</t>
         </is>
       </c>
     </row>
@@ -43578,7 +43578,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Jorian Donovan</t>
+          <t>Jordan Spence</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -43593,71 +43593,75 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Top-6 F</t>
+          <t>Top-4 D</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
       <c r="F442" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G442" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="H442" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I442" t="n">
+        <v>8</v>
+      </c>
+      <c r="J442" t="n">
+        <v>0</v>
+      </c>
+      <c r="K442" t="n">
+        <v>1</v>
+      </c>
+      <c r="L442" t="n">
+        <v>1</v>
+      </c>
+      <c r="M442" t="n">
         <v>7</v>
       </c>
-      <c r="H442" t="n">
-        <v>0</v>
-      </c>
-      <c r="I442" t="n">
-        <v>1</v>
-      </c>
-      <c r="J442" t="n">
-        <v>0</v>
-      </c>
-      <c r="K442" t="n">
-        <v>0</v>
-      </c>
-      <c r="L442" t="n">
-        <v>0</v>
-      </c>
-      <c r="M442" t="n">
-        <v>0</v>
-      </c>
       <c r="N442" t="n">
-        <v>9.199999999999999</v>
+        <v>22.7</v>
       </c>
       <c r="O442" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="P442" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q442" t="n">
         <v>0</v>
       </c>
       <c r="R442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S442" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T442" t="inlineStr">
         <is>
-          <t>Not enough games</t>
-        </is>
-      </c>
-      <c r="U442" t="inlineStr"/>
+          <t>Cold – usage down</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>1 pts vs 4.1 expected in last 8; TOI +3.9 min/gm; PP -1.0 min/gm; shots rate x0.49; goals vs shooting% -0.5</t>
+        </is>
+      </c>
       <c r="V442" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="W442" t="n">
-        <v>7</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Jordan Spence</t>
+          <t>Tyler Kleven</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -43682,65 +43686,65 @@
         </is>
       </c>
       <c r="G443" t="n">
-        <v>22.7</v>
+        <v>21</v>
       </c>
       <c r="H443" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I443" t="n">
         <v>8</v>
       </c>
       <c r="J443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K443" t="n">
         <v>1</v>
       </c>
       <c r="L443" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M443" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N443" t="n">
-        <v>22.7</v>
+        <v>21</v>
       </c>
       <c r="O443" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="P443" t="n">
         <v>8</v>
       </c>
       <c r="Q443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R443" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S443" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T443" t="inlineStr">
         <is>
-          <t>Cold – usage down</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="U443" t="inlineStr">
         <is>
-          <t>1 pts vs 4.1 expected in last 8; TOI +3.9 min/gm; PP -1.0 min/gm; shots rate x0.49; goals vs shooting% -0.5</t>
+          <t>2 pts vs 2.5 expected in last 8; TOI +3.7 min/gm; PP -0.0 min/gm; shots rate x0.64; goals vs shooting% +0.7</t>
         </is>
       </c>
       <c r="V443" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="W443" t="n">
-        <v>18.7</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Tyler Kleven</t>
+          <t>Michael Amadio</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -43750,12 +43754,12 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Top-4 D</t>
+          <t>Depth F</t>
         </is>
       </c>
       <c r="E444" t="inlineStr"/>
@@ -43765,43 +43769,43 @@
         </is>
       </c>
       <c r="G444" t="n">
-        <v>21</v>
+        <v>16.2</v>
       </c>
       <c r="H444" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I444" t="n">
         <v>8</v>
       </c>
       <c r="J444" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K444" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L444" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M444" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N444" t="n">
-        <v>21</v>
+        <v>16.2</v>
       </c>
       <c r="O444" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P444" t="n">
         <v>8</v>
       </c>
       <c r="Q444" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R444" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S444" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T444" t="inlineStr">
         <is>
@@ -43810,20 +43814,20 @@
       </c>
       <c r="U444" t="inlineStr">
         <is>
-          <t>2 pts vs 2.5 expected in last 8; TOI +3.7 min/gm; PP -0.0 min/gm; shots rate x0.64; goals vs shooting% +0.7</t>
+          <t>4 pts vs 3.5 expected in last 8; TOI +0.1 min/gm; PP -0.1 min/gm; shots rate x0.94; goals vs shooting% +0.6</t>
         </is>
       </c>
       <c r="V444" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="W444" t="n">
-        <v>17.3</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Michael Amadio</t>
+          <t>William Eklund</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -43833,7 +43837,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -43848,65 +43852,61 @@
         </is>
       </c>
       <c r="G445" t="n">
-        <v>16.2</v>
+        <v>13.9</v>
       </c>
       <c r="H445" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I445" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J445" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K445" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L445" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M445" t="n">
         <v>9</v>
       </c>
       <c r="N445" t="n">
-        <v>16.2</v>
+        <v>13.9</v>
       </c>
       <c r="O445" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P445" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q445" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R445" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S445" t="n">
         <v>9</v>
       </c>
       <c r="T445" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="U445" t="inlineStr">
-        <is>
-          <t>4 pts vs 3.5 expected in last 8; TOI +0.1 min/gm; PP -0.1 min/gm; shots rate x0.94; goals vs shooting% +0.6</t>
-        </is>
-      </c>
+          <t>Not enough games</t>
+        </is>
+      </c>
+      <c r="U445" t="inlineStr"/>
       <c r="V445" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="W445" t="n">
-        <v>16.1</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>William Eklund</t>
+          <t>Andre Burakovsky</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -43931,43 +43931,43 @@
         </is>
       </c>
       <c r="G446" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="H446" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="I446" t="n">
         <v>4</v>
       </c>
       <c r="J446" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K446" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L446" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M446" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N446" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="O446" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P446" t="n">
         <v>4</v>
       </c>
       <c r="Q446" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R446" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S446" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T446" t="inlineStr">
         <is>
@@ -43976,16 +43976,16 @@
       </c>
       <c r="U446" t="inlineStr"/>
       <c r="V446" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="W446" t="n">
-        <v>18.5</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Andre Burakovsky</t>
+          <t>Fabian Zetterlund</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -44010,61 +44010,65 @@
         </is>
       </c>
       <c r="G447" t="n">
-        <v>13.7</v>
+        <v>12.9</v>
       </c>
       <c r="H447" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="I447" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K447" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L447" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M447" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="N447" t="n">
-        <v>13.7</v>
+        <v>12.9</v>
       </c>
       <c r="O447" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="P447" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R447" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S447" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T447" t="inlineStr">
         <is>
-          <t>Not enough games</t>
-        </is>
-      </c>
-      <c r="U447" t="inlineStr"/>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>3 pts vs 3.2 expected in last 8; TOI +0.0 min/gm; PP +1.1 min/gm; shots rate x1.16; goals vs shooting% -0.9</t>
+        </is>
+      </c>
       <c r="V447" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="W447" t="n">
-        <v>16.4</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Fabian Zetterlund</t>
+          <t>Warren Foegele</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -44089,43 +44093,43 @@
         </is>
       </c>
       <c r="G448" t="n">
-        <v>12.9</v>
+        <v>11.5</v>
       </c>
       <c r="H448" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="I448" t="n">
         <v>8</v>
       </c>
       <c r="J448" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K448" t="n">
         <v>2</v>
       </c>
       <c r="L448" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M448" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="N448" t="n">
-        <v>12.9</v>
+        <v>11.5</v>
       </c>
       <c r="O448" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P448" t="n">
         <v>8</v>
       </c>
       <c r="Q448" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R448" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S448" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T448" t="inlineStr">
         <is>
@@ -44134,20 +44138,20 @@
       </c>
       <c r="U448" t="inlineStr">
         <is>
-          <t>3 pts vs 3.2 expected in last 8; TOI +0.0 min/gm; PP +1.1 min/gm; shots rate x1.16; goals vs shooting% -0.9</t>
+          <t>2 pts vs 1.7 expected in last 8; TOI -2.2 min/gm; PP -0.6 min/gm; shots rate x0.39; goals vs shooting% -0.5</t>
         </is>
       </c>
       <c r="V448" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="W448" t="n">
-        <v>12.9</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Warren Foegele</t>
+          <t>Stephen Halliday</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -44157,7 +44161,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -44172,65 +44176,61 @@
         </is>
       </c>
       <c r="G449" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="H449" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I449" t="n">
         <v>8</v>
       </c>
       <c r="J449" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K449" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M449" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N449" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="O449" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P449" t="n">
         <v>8</v>
       </c>
       <c r="Q449" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S449" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T449" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="U449" t="inlineStr">
-        <is>
-          <t>2 pts vs 1.7 expected in last 8; TOI -2.2 min/gm; PP -0.6 min/gm; shots rate x0.39; goals vs shooting% -0.5</t>
-        </is>
-      </c>
+          <t>Not enough baseline</t>
+        </is>
+      </c>
+      <c r="U449" t="inlineStr"/>
       <c r="V449" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="W449" t="n">
-        <v>13.8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Stephen Halliday</t>
+          <t>Nick Cousins</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -44255,61 +44255,65 @@
         </is>
       </c>
       <c r="G450" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="H450" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I450" t="n">
         <v>8</v>
       </c>
       <c r="J450" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K450" t="n">
         <v>1</v>
       </c>
       <c r="L450" t="n">
+        <v>2</v>
+      </c>
+      <c r="M450" t="n">
         <v>3</v>
       </c>
-      <c r="M450" t="n">
-        <v>8</v>
-      </c>
       <c r="N450" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="O450" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P450" t="n">
         <v>8</v>
       </c>
       <c r="Q450" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R450" t="n">
+        <v>2</v>
+      </c>
+      <c r="S450" t="n">
         <v>3</v>
       </c>
-      <c r="S450" t="n">
-        <v>8</v>
-      </c>
       <c r="T450" t="inlineStr">
         <is>
-          <t>Not enough baseline</t>
-        </is>
-      </c>
-      <c r="U450" t="inlineStr"/>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>2 pts vs 1.9 expected in last 8; TOI -2.0 min/gm; PP -0.0 min/gm; shots rate x0.47; goals vs shooting% +0.7</t>
+        </is>
+      </c>
       <c r="V450" t="n">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="W450" t="n">
-        <v>8.5</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Nick Cousins</t>
+          <t>Hayden Hodgson</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -44319,7 +44323,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -44330,69 +44334,65 @@
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G451" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
       </c>
       <c r="I451" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J451" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K451" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L451" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M451" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N451" t="n">
-        <v>9.4</v>
+        <v>5.4</v>
       </c>
       <c r="O451" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P451" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q451" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R451" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S451" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T451" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="U451" t="inlineStr">
-        <is>
-          <t>2 pts vs 1.9 expected in last 8; TOI -2.0 min/gm; PP -0.0 min/gm; shots rate x0.47; goals vs shooting% +0.7</t>
-        </is>
-      </c>
+          <t>Not enough games</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr"/>
       <c r="V451" t="n">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="W451" t="n">
-        <v>11.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Hayden Hodgson</t>
+          <t>Artem Zub</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -44402,12 +44402,12 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Depth F</t>
+          <t>Depth D</t>
         </is>
       </c>
       <c r="E452" t="inlineStr"/>
@@ -44417,43 +44417,43 @@
         </is>
       </c>
       <c r="G452" t="n">
-        <v>7</v>
+        <v>20.8</v>
       </c>
       <c r="H452" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I452" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J452" t="n">
         <v>0</v>
       </c>
       <c r="K452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N452" t="n">
-        <v>5.4</v>
+        <v>18.5</v>
       </c>
       <c r="O452" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P452" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q452" t="n">
         <v>0</v>
       </c>
       <c r="R452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T452" t="inlineStr">
         <is>
@@ -44462,16 +44462,16 @@
       </c>
       <c r="U452" t="inlineStr"/>
       <c r="V452" t="n">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="W452" t="n">
-        <v>7</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Artem Zub</t>
+          <t>Carter Yakemchuk</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -44489,68 +44489,72 @@
           <t>Depth D</t>
         </is>
       </c>
-      <c r="E453" t="inlineStr"/>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G453" t="n">
-        <v>20.8</v>
+        <v>18.5</v>
       </c>
       <c r="H453" t="n">
-        <v>0.1</v>
+        <v>3.6</v>
       </c>
       <c r="I453" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J453" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K453" t="n">
         <v>1</v>
       </c>
       <c r="L453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M453" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N453" t="n">
         <v>18.5</v>
       </c>
       <c r="O453" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P453" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q453" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S453" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="T453" t="inlineStr">
         <is>
-          <t>Not enough games</t>
+          <t>Not enough baseline</t>
         </is>
       </c>
       <c r="U453" t="inlineStr"/>
       <c r="V453" t="n">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="W453" t="n">
-        <v>20.8</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Carter Yakemchuk</t>
+          <t>Nikolas Matinpalo</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -44568,72 +44572,68 @@
           <t>Depth D</t>
         </is>
       </c>
-      <c r="E454" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G454" t="n">
-        <v>18.5</v>
+        <v>15.2</v>
       </c>
       <c r="H454" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I454" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J454" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K454" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L454" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M454" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N454" t="n">
-        <v>18.5</v>
+        <v>15.2</v>
       </c>
       <c r="O454" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P454" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q454" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R454" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S454" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T454" t="inlineStr">
         <is>
-          <t>Not enough baseline</t>
+          <t>Not enough games</t>
         </is>
       </c>
       <c r="U454" t="inlineStr"/>
       <c r="V454" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="W454" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Nikolas Matinpalo</t>
+          <t>Cameron Crotty</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -44658,13 +44658,13 @@
         </is>
       </c>
       <c r="G455" t="n">
-        <v>15.2</v>
+        <v>11.2</v>
       </c>
       <c r="H455" t="n">
         <v>0</v>
       </c>
       <c r="I455" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J455" t="n">
         <v>0</v>
@@ -44676,16 +44676,16 @@
         <v>0</v>
       </c>
       <c r="M455" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N455" t="n">
-        <v>15.2</v>
+        <v>11.2</v>
       </c>
       <c r="O455" t="n">
         <v>0</v>
       </c>
       <c r="P455" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q455" t="n">
         <v>0</v>
@@ -44694,7 +44694,7 @@
         <v>0</v>
       </c>
       <c r="S455" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T455" t="inlineStr">
         <is>
@@ -44703,16 +44703,16 @@
       </c>
       <c r="U455" t="inlineStr"/>
       <c r="V455" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="W455" t="n">
-        <v>15.6</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Cameron Crotty</t>
+          <t>Hoyt Stanley</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -44737,13 +44737,13 @@
         </is>
       </c>
       <c r="G456" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="H456" t="n">
         <v>0</v>
       </c>
       <c r="I456" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J456" t="n">
         <v>0</v>
@@ -44755,16 +44755,16 @@
         <v>0</v>
       </c>
       <c r="M456" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N456" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="O456" t="n">
         <v>0</v>
       </c>
       <c r="P456" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q456" t="n">
         <v>0</v>
@@ -44773,7 +44773,7 @@
         <v>0</v>
       </c>
       <c r="S456" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T456" t="inlineStr">
         <is>
@@ -44782,16 +44782,16 @@
       </c>
       <c r="U456" t="inlineStr"/>
       <c r="V456" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W456" t="n">
-        <v>14.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Hoyt Stanley</t>
+          <t>Jorian Donovan</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -44812,17 +44812,17 @@
       <c r="E457" t="inlineStr"/>
       <c r="F457" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G457" t="n">
-        <v>10.9</v>
+        <v>7</v>
       </c>
       <c r="H457" t="n">
         <v>0</v>
       </c>
       <c r="I457" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J457" t="n">
         <v>0</v>
@@ -44834,16 +44834,16 @@
         <v>0</v>
       </c>
       <c r="M457" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N457" t="n">
-        <v>10.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O457" t="n">
         <v>0</v>
       </c>
       <c r="P457" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q457" t="n">
         <v>0</v>
@@ -44852,7 +44852,7 @@
         <v>0</v>
       </c>
       <c r="S457" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T457" t="inlineStr">
         <is>
@@ -44861,10 +44861,10 @@
       </c>
       <c r="U457" t="inlineStr"/>
       <c r="V457" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W457" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="458">

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:44</t>
+          <t>2026-10-20 08:42</t>
         </is>
       </c>
     </row>

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 07:44</t>
+          <t>2026-10-21 08:45</t>
         </is>
       </c>
     </row>
@@ -20988,7 +20988,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Cale Makar</t>
+          <t>Nathan MacKinnon</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -20998,12 +20998,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Top-pair D</t>
+          <t>Top-line C</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -21017,43 +21017,43 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>22.1</v>
+        <v>21.3</v>
       </c>
       <c r="H162" t="n">
         <v>4.1</v>
       </c>
       <c r="I162" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J162" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K162" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L162" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M162" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="N162" t="n">
-        <v>22.1</v>
+        <v>21.3</v>
       </c>
       <c r="O162" t="n">
         <v>4.1</v>
       </c>
       <c r="P162" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q162" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R162" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="S162" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -21062,20 +21062,20 @@
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>11 pts vs 8.4 expected in last 9; TOI -2.7 min/gm; PP -0.1 min/gm; shots rate x1.13; goals vs shooting% +0.6</t>
+          <t>16 pts vs 15.2 expected in last 10; TOI -1.0 min/gm; PP -0.2 min/gm; shots rate x1.05; goals vs shooting% -0.7</t>
         </is>
       </c>
       <c r="V162" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="W162" t="n">
-        <v>24.8</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Devon Toews</t>
+          <t>Cale Makar</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -21093,72 +21093,76 @@
           <t>Top-pair D</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F163" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>20.6</v>
+        <v>22.1</v>
       </c>
       <c r="H163" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="I163" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K163" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L163" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M163" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="N163" t="n">
-        <v>20.6</v>
+        <v>22.1</v>
       </c>
       <c r="O163" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="P163" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R163" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S163" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
-          <t>Hot – mixed</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>7 pts vs 3.3 expected in last 10; TOI -1.7 min/gm; PP +0.4 min/gm; shots rate x0.90; goals vs shooting% +1.6</t>
+          <t>11 pts vs 8.4 expected in last 9; TOI -2.7 min/gm; PP -0.1 min/gm; shots rate x1.13; goals vs shooting% +0.6</t>
         </is>
       </c>
       <c r="V163" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="W163" t="n">
-        <v>22.4</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Martin Necas</t>
+          <t>Devon Toews</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -21168,84 +21172,80 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Top-6 F</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Top-pair D</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="H164" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="I164" t="n">
         <v>10</v>
       </c>
       <c r="J164" t="n">
+        <v>2</v>
+      </c>
+      <c r="K164" t="n">
         <v>5</v>
       </c>
-      <c r="K164" t="n">
-        <v>6</v>
-      </c>
       <c r="L164" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M164" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="N164" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="O164" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="P164" t="n">
         <v>10</v>
       </c>
       <c r="Q164" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R164" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S164" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Hot – mixed</t>
         </is>
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>11 pts vs 12.2 expected in last 10; TOI -1.1 min/gm; PP -0.4 min/gm; shots rate x0.92; goals vs shooting% +0.8</t>
+          <t>7 pts vs 3.3 expected in last 10; TOI -1.7 min/gm; PP +0.4 min/gm; shots rate x0.90; goals vs shooting% +1.6</t>
         </is>
       </c>
       <c r="V164" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="W164" t="n">
-        <v>21.5</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Nazem Kadri</t>
+          <t>Martin Necas</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -21274,7 +21274,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="H165" t="n">
         <v>3.7</v>
@@ -21283,19 +21283,19 @@
         <v>10</v>
       </c>
       <c r="J165" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K165" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L165" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M165" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N165" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="O165" t="n">
         <v>3.7</v>
@@ -21304,13 +21304,13 @@
         <v>10</v>
       </c>
       <c r="Q165" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R165" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S165" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -21319,20 +21319,20 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>7 pts vs 6.9 expected in last 10; TOI +1.3 min/gm; PP +0.5 min/gm; shots rate x0.91; goals vs shooting% -2.0</t>
+          <t>11 pts vs 12.2 expected in last 10; TOI -1.1 min/gm; PP -0.4 min/gm; shots rate x0.92; goals vs shooting% +0.8</t>
         </is>
       </c>
       <c r="V165" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W165" t="n">
-        <v>19</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Artturi Lehkonen</t>
+          <t>Nazem Kadri</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -21342,7 +21342,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21350,72 +21350,76 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F166" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>19</v>
+        <v>20.3</v>
       </c>
       <c r="H166" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="I166" t="n">
         <v>10</v>
       </c>
       <c r="J166" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L166" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M166" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="N166" t="n">
-        <v>19</v>
+        <v>20.3</v>
       </c>
       <c r="O166" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="P166" t="n">
         <v>10</v>
       </c>
       <c r="Q166" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S166" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
-          <t>Hot – shooting luck</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="U166" t="inlineStr">
         <is>
-          <t>11 pts vs 7.0 expected in last 10; TOI +0.5 min/gm; PP -0.7 min/gm; shots rate x0.71; goals vs shooting% +5.8</t>
+          <t>7 pts vs 6.9 expected in last 10; TOI +1.3 min/gm; PP +0.5 min/gm; shots rate x0.91; goals vs shooting% -2.0</t>
         </is>
       </c>
       <c r="V166" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="W166" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Brock Nelson</t>
+          <t>Artturi Lehkonen</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -21425,7 +21429,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21440,65 +21444,65 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="H167" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="I167" t="n">
         <v>10</v>
       </c>
       <c r="J167" t="n">
+        <v>8</v>
+      </c>
+      <c r="K167" t="n">
         <v>3</v>
       </c>
-      <c r="K167" t="n">
-        <v>5</v>
-      </c>
       <c r="L167" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M167" t="n">
+        <v>16</v>
+      </c>
+      <c r="N167" t="n">
         <v>19</v>
       </c>
-      <c r="N167" t="n">
-        <v>18.5</v>
-      </c>
       <c r="O167" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="P167" t="n">
         <v>10</v>
       </c>
       <c r="Q167" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R167" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S167" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Hot – shooting luck</t>
         </is>
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>8 pts vs 7.6 expected in last 10; TOI -1.1 min/gm; PP -1.9 min/gm; shots rate x0.88; goals vs shooting% -0.4</t>
+          <t>11 pts vs 7.0 expected in last 10; TOI +0.5 min/gm; PP -0.7 min/gm; shots rate x0.71; goals vs shooting% +5.8</t>
         </is>
       </c>
       <c r="V167" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="W167" t="n">
-        <v>19.7</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Gabriel Landeskog</t>
+          <t>Brock Nelson</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -21508,7 +21512,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -21523,43 +21527,43 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="H168" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="I168" t="n">
         <v>10</v>
       </c>
       <c r="J168" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K168" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L168" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M168" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="N168" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="O168" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="P168" t="n">
         <v>10</v>
       </c>
       <c r="Q168" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R168" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S168" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -21568,20 +21572,20 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>6 pts vs 5.7 expected in last 10; TOI -0.5 min/gm; PP -0.4 min/gm; shots rate x0.65; goals vs shooting% +2.5</t>
+          <t>8 pts vs 7.6 expected in last 10; TOI -1.1 min/gm; PP -1.9 min/gm; shots rate x0.88; goals vs shooting% -0.4</t>
         </is>
       </c>
       <c r="V168" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="W168" t="n">
-        <v>16.4</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Brett Kulak</t>
+          <t>Gabriel Landeskog</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -21591,12 +21595,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Top-4 D</t>
+          <t>Top-6 F</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -21606,43 +21610,43 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>18.3</v>
+        <v>16</v>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="I169" t="n">
         <v>10</v>
       </c>
       <c r="J169" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K169" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L169" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M169" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N169" t="n">
-        <v>18.3</v>
+        <v>16</v>
       </c>
       <c r="O169" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P169" t="n">
         <v>10</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R169" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S169" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -21651,20 +21655,20 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>4 pts vs 1.4 expected in last 10; TOI -0.7 min/gm; PP -0.1 min/gm; shots rate x0.73; goals vs shooting% -0.1</t>
+          <t>6 pts vs 5.7 expected in last 10; TOI -0.5 min/gm; PP -0.4 min/gm; shots rate x0.65; goals vs shooting% +2.5</t>
         </is>
       </c>
       <c r="V169" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="W169" t="n">
-        <v>19</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Sam Malinski</t>
+          <t>Brett Kulak</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -21689,43 +21693,43 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>16.4</v>
+        <v>18.3</v>
       </c>
       <c r="H170" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I170" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L170" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M170" t="n">
+        <v>8</v>
+      </c>
+      <c r="N170" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
         <v>10</v>
       </c>
-      <c r="N170" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="O170" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P170" t="n">
-        <v>9</v>
-      </c>
       <c r="Q170" t="n">
         <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -21734,20 +21738,20 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>2 pts vs 4.1 expected in last 9; TOI -1.2 min/gm; PP -0.0 min/gm; shots rate x0.60; goals vs shooting% -0.5</t>
+          <t>4 pts vs 1.4 expected in last 10; TOI -0.7 min/gm; PP -0.1 min/gm; shots rate x0.73; goals vs shooting% -0.1</t>
         </is>
       </c>
       <c r="V170" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W170" t="n">
-        <v>17.6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Nathan MacKinnon</t>
+          <t>Sam Malinski</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -21757,63 +21761,59 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Depth F</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Top-4 D</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>21.3</v>
+        <v>16.4</v>
       </c>
       <c r="H171" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="I171" t="n">
+        <v>9</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>2</v>
+      </c>
+      <c r="L171" t="n">
+        <v>2</v>
+      </c>
+      <c r="M171" t="n">
         <v>10</v>
       </c>
-      <c r="J171" t="n">
-        <v>6</v>
-      </c>
-      <c r="K171" t="n">
+      <c r="N171" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P171" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>0</v>
+      </c>
+      <c r="R171" t="n">
+        <v>2</v>
+      </c>
+      <c r="S171" t="n">
         <v>10</v>
       </c>
-      <c r="L171" t="n">
-        <v>16</v>
-      </c>
-      <c r="M171" t="n">
-        <v>44</v>
-      </c>
-      <c r="N171" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="O171" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P171" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q171" t="n">
-        <v>6</v>
-      </c>
-      <c r="R171" t="n">
-        <v>16</v>
-      </c>
-      <c r="S171" t="n">
-        <v>44</v>
-      </c>
       <c r="T171" t="inlineStr">
         <is>
           <t>Neutral</t>
@@ -21821,14 +21821,14 @@
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>16 pts vs 15.2 expected in last 10; TOI -1.0 min/gm; PP -0.2 min/gm; shots rate x1.05; goals vs shooting% -0.7</t>
+          <t>2 pts vs 4.1 expected in last 9; TOI -1.2 min/gm; PP -0.0 min/gm; shots rate x0.60; goals vs shooting% -0.5</t>
         </is>
       </c>
       <c r="V171" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="W171" t="n">
-        <v>22.3</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="172">
@@ -34518,7 +34518,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Cole Caufield</t>
+          <t>David Reinbacher</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -34528,84 +34528,76 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Top-6 F</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Top-pair D</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>19.7</v>
+        <v>13.1</v>
       </c>
       <c r="H328" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I328" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J328" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K328" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L328" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="N328" t="n">
-        <v>19.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O328" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P328" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q328" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R328" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S328" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="U328" t="inlineStr">
-        <is>
-          <t>8 pts vs 10.6 expected in last 9; TOI +1.5 min/gm; PP +0.3 min/gm; shots rate x1.03; goals vs shooting% -0.3</t>
-        </is>
-      </c>
+          <t>Not enough games</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr"/>
       <c r="V328" t="n">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="W328" t="n">
-        <v>18.2</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Juraj Slafkovský</t>
+          <t>Cole Caufield</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -34615,7 +34607,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -34634,7 +34626,7 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>18.9</v>
+        <v>19.7</v>
       </c>
       <c r="H329" t="n">
         <v>3.7</v>
@@ -34643,19 +34635,19 @@
         <v>9</v>
       </c>
       <c r="J329" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K329" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L329" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M329" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="N329" t="n">
-        <v>18.9</v>
+        <v>19.7</v>
       </c>
       <c r="O329" t="n">
         <v>3.7</v>
@@ -34664,13 +34656,13 @@
         <v>9</v>
       </c>
       <c r="Q329" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R329" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S329" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="T329" t="inlineStr">
         <is>
@@ -34679,20 +34671,20 @@
       </c>
       <c r="U329" t="inlineStr">
         <is>
-          <t>7 pts vs 8.2 expected in last 9; TOI +0.3 min/gm; PP +0.4 min/gm; shots rate x1.19; goals vs shooting% -2.0</t>
+          <t>8 pts vs 10.6 expected in last 9; TOI +1.5 min/gm; PP +0.3 min/gm; shots rate x1.03; goals vs shooting% -0.3</t>
         </is>
       </c>
       <c r="V329" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="W329" t="n">
-        <v>18.5</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Alex Newhook</t>
+          <t>Juraj Slafkovský</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -34702,7 +34694,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -34710,50 +34702,54 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E330" t="inlineStr"/>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F330" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G330" t="n">
-        <v>16.3</v>
+        <v>18.9</v>
       </c>
       <c r="H330" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="I330" t="n">
         <v>9</v>
       </c>
       <c r="J330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K330" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L330" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M330" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="N330" t="n">
-        <v>16.3</v>
+        <v>18.9</v>
       </c>
       <c r="O330" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="P330" t="n">
         <v>9</v>
       </c>
       <c r="Q330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R330" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S330" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="T330" t="inlineStr">
         <is>
@@ -34762,20 +34758,20 @@
       </c>
       <c r="U330" t="inlineStr">
         <is>
-          <t>4 pts vs 6.0 expected in last 9; TOI +1.8 min/gm; PP +0.2 min/gm; shots rate x0.75; goals vs shooting% -1.3</t>
+          <t>7 pts vs 8.2 expected in last 9; TOI +0.3 min/gm; PP +0.4 min/gm; shots rate x1.19; goals vs shooting% -2.0</t>
         </is>
       </c>
       <c r="V330" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="W330" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Phillip Danault</t>
+          <t>Alex Newhook</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -34800,43 +34796,43 @@
         </is>
       </c>
       <c r="G331" t="n">
-        <v>15.9</v>
+        <v>16.3</v>
       </c>
       <c r="H331" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="I331" t="n">
         <v>9</v>
       </c>
       <c r="J331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K331" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L331" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M331" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N331" t="n">
-        <v>15.9</v>
+        <v>16.3</v>
       </c>
       <c r="O331" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="P331" t="n">
         <v>9</v>
       </c>
       <c r="Q331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R331" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S331" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -34845,20 +34841,20 @@
       </c>
       <c r="U331" t="inlineStr">
         <is>
-          <t>2 pts vs 2.1 expected in last 9; TOI +0.3 min/gm; PP -0.3 min/gm; shots rate x1.26; goals vs shooting% -0.9</t>
+          <t>4 pts vs 6.0 expected in last 9; TOI +1.8 min/gm; PP +0.2 min/gm; shots rate x0.75; goals vs shooting% -1.3</t>
         </is>
       </c>
       <c r="V331" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="W331" t="n">
-        <v>15.6</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Ivan Demidov</t>
+          <t>Phillip Danault</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -34868,7 +34864,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -34876,72 +34872,72 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>15.5</v>
+        <v>15.9</v>
       </c>
       <c r="H332" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="I332" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L332" t="n">
         <v>2</v>
       </c>
       <c r="M332" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="N332" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="O332" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P332" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>0</v>
+      </c>
+      <c r="R332" t="n">
+        <v>2</v>
+      </c>
+      <c r="S332" t="n">
+        <v>14</v>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>2 pts vs 2.1 expected in last 9; TOI +0.3 min/gm; PP -0.3 min/gm; shots rate x1.26; goals vs shooting% -0.9</t>
+        </is>
+      </c>
+      <c r="V332" t="n">
+        <v>75</v>
+      </c>
+      <c r="W332" t="n">
         <v>15.6</v>
-      </c>
-      <c r="O332" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P332" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q332" t="n">
-        <v>1</v>
-      </c>
-      <c r="R332" t="n">
-        <v>2</v>
-      </c>
-      <c r="S332" t="n">
-        <v>4</v>
-      </c>
-      <c r="T332" t="inlineStr">
-        <is>
-          <t>Not enough games</t>
-        </is>
-      </c>
-      <c r="U332" t="inlineStr"/>
-      <c r="V332" t="n">
-        <v>82</v>
-      </c>
-      <c r="W332" t="n">
-        <v>15.5</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Kaiden Guhle</t>
+          <t>Ivan Demidov</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -34951,58 +34947,62 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Top-4 D</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr"/>
+          <t>Top-6 F</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>21.9</v>
+        <v>15.5</v>
       </c>
       <c r="H333" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="I333" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K333" t="n">
         <v>1</v>
       </c>
       <c r="L333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M333" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N333" t="n">
-        <v>21.9</v>
+        <v>15.6</v>
       </c>
       <c r="O333" t="n">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
       <c r="P333" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S333" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -35011,16 +35011,16 @@
       </c>
       <c r="U333" t="inlineStr"/>
       <c r="V333" t="n">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="W333" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Noah Dobson</t>
+          <t>Kaiden Guhle</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -35045,65 +35045,61 @@
         </is>
       </c>
       <c r="G334" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="H334" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="I334" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J334" t="n">
         <v>0</v>
       </c>
       <c r="K334" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L334" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M334" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="N334" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="O334" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="P334" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q334" t="n">
         <v>0</v>
       </c>
       <c r="R334" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S334" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="T334" t="inlineStr">
         <is>
-          <t>Cold – shots steady</t>
-        </is>
-      </c>
-      <c r="U334" t="inlineStr">
-        <is>
-          <t>2 pts vs 5.1 expected in last 9; TOI -0.9 min/gm; PP -0.4 min/gm; shots rate x1.23; goals vs shooting% -1.6</t>
-        </is>
-      </c>
+          <t>Not enough games</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr"/>
       <c r="V334" t="n">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="W334" t="n">
-        <v>22.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Chris Kreider</t>
+          <t>Noah Dobson</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -35113,12 +35109,12 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Depth F</t>
+          <t>Top-4 D</t>
         </is>
       </c>
       <c r="E335" t="inlineStr"/>
@@ -35128,65 +35124,65 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>15</v>
+        <v>21.6</v>
       </c>
       <c r="H335" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="I335" t="n">
         <v>9</v>
       </c>
       <c r="J335" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K335" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L335" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M335" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="N335" t="n">
-        <v>15</v>
+        <v>21.6</v>
       </c>
       <c r="O335" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="P335" t="n">
         <v>9</v>
       </c>
       <c r="Q335" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R335" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S335" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="T335" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Cold – shots steady</t>
         </is>
       </c>
       <c r="U335" t="inlineStr">
         <is>
-          <t>4 pts vs 5.3 expected in last 9; TOI -2.0 min/gm; PP -0.4 min/gm; shots rate x0.54; goals vs shooting% -0.3</t>
+          <t>2 pts vs 5.1 expected in last 9; TOI -0.9 min/gm; PP -0.4 min/gm; shots rate x1.23; goals vs shooting% -1.6</t>
         </is>
       </c>
       <c r="V335" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="W335" t="n">
-        <v>17</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Oliver Kapanen</t>
+          <t>Chris Kreider</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -35196,7 +35192,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -35207,65 +35203,69 @@
       <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H336" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="I336" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K336" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L336" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M336" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N336" t="n">
-        <v>11.1</v>
+        <v>15</v>
       </c>
       <c r="O336" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="P336" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R336" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S336" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T336" t="inlineStr">
         <is>
-          <t>Not enough games</t>
-        </is>
-      </c>
-      <c r="U336" t="inlineStr"/>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>4 pts vs 5.3 expected in last 9; TOI -2.0 min/gm; PP -0.4 min/gm; shots rate x0.54; goals vs shooting% -0.3</t>
+        </is>
+      </c>
       <c r="V336" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="W336" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Josh Anderson</t>
+          <t>Oliver Kapanen</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -35275,7 +35275,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -35286,69 +35286,65 @@
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G337" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="H337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I337" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J337" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="N337" t="n">
-        <v>14</v>
+        <v>11.1</v>
       </c>
       <c r="O337" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P337" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Q337" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R337" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S337" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="T337" t="inlineStr">
         <is>
-          <t>Hot – usage-backed</t>
-        </is>
-      </c>
-      <c r="U337" t="inlineStr">
-        <is>
-          <t>6 pts vs 2.9 expected in last 9; TOI -0.1 min/gm; PP -0.1 min/gm; shots rate x1.72; goals vs shooting% +1.0</t>
-        </is>
-      </c>
+          <t>Not enough games</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr"/>
       <c r="V337" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="W337" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Zachary Bolduc</t>
+          <t>Josh Anderson</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -35376,7 +35372,7 @@
         <v>14</v>
       </c>
       <c r="H338" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I338" t="n">
         <v>9</v>
@@ -35391,13 +35387,13 @@
         <v>6</v>
       </c>
       <c r="M338" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N338" t="n">
         <v>14</v>
       </c>
       <c r="O338" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="P338" t="n">
         <v>9</v>
@@ -35409,29 +35405,29 @@
         <v>6</v>
       </c>
       <c r="S338" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Hot – usage-backed</t>
         </is>
       </c>
       <c r="U338" t="inlineStr">
         <is>
-          <t>6 pts vs 3.5 expected in last 9; TOI +0.3 min/gm; PP +0.0 min/gm; shots rate x1.34; goals vs shooting% +2.1</t>
+          <t>6 pts vs 2.9 expected in last 9; TOI -0.1 min/gm; PP -0.1 min/gm; shots rate x1.72; goals vs shooting% +1.0</t>
         </is>
       </c>
       <c r="V338" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="W338" t="n">
-        <v>13.6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Jake Evans</t>
+          <t>Zachary Bolduc</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -35441,7 +35437,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -35456,43 +35452,43 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>13.6</v>
+        <v>14</v>
       </c>
       <c r="H339" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I339" t="n">
         <v>9</v>
       </c>
       <c r="J339" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K339" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L339" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M339" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="N339" t="n">
-        <v>13.6</v>
+        <v>14</v>
       </c>
       <c r="O339" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P339" t="n">
         <v>9</v>
       </c>
       <c r="Q339" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R339" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S339" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="T339" t="inlineStr">
         <is>
@@ -35501,20 +35497,20 @@
       </c>
       <c r="U339" t="inlineStr">
         <is>
-          <t>0 pts vs 2.8 expected in last 9; TOI -1.8 min/gm; PP -0.0 min/gm; shots rate x0.80; goals vs shooting% -1.1</t>
+          <t>6 pts vs 3.5 expected in last 9; TOI +0.3 min/gm; PP +0.0 min/gm; shots rate x1.34; goals vs shooting% +2.1</t>
         </is>
       </c>
       <c r="V339" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="W339" t="n">
-        <v>15.4</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>David Reinbacher</t>
+          <t>Jake Evans</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -35524,7 +35520,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -35535,17 +35531,17 @@
       <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G340" t="n">
-        <v>13.1</v>
+        <v>13.6</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
       </c>
       <c r="I340" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J340" t="n">
         <v>0</v>
@@ -35557,16 +35553,16 @@
         <v>0</v>
       </c>
       <c r="M340" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N340" t="n">
-        <v>9.199999999999999</v>
+        <v>13.6</v>
       </c>
       <c r="O340" t="n">
         <v>0</v>
       </c>
       <c r="P340" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Q340" t="n">
         <v>0</v>
@@ -35575,19 +35571,23 @@
         <v>0</v>
       </c>
       <c r="S340" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T340" t="inlineStr">
         <is>
-          <t>Not enough games</t>
-        </is>
-      </c>
-      <c r="U340" t="inlineStr"/>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>0 pts vs 2.8 expected in last 9; TOI -1.8 min/gm; PP -0.0 min/gm; shots rate x0.80; goals vs shooting% -1.1</t>
+        </is>
+      </c>
       <c r="V340" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="W340" t="n">
-        <v>13.1</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="341">
@@ -67942,11 +67942,7 @@
           <t>Depth F</t>
         </is>
       </c>
-      <c r="E734" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E734" t="inlineStr"/>
       <c r="F734" t="inlineStr">
         <is>
           <t>last season</t>

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 07:39</t>
+          <t>2026-10-24 08:40</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Travis Mitchell</t>
+          <t>Alex Killorn</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8830,72 +8830,72 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>16.6</v>
+        <v>16.1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="N8" t="n">
-        <v>16.6</v>
+        <v>16.1</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Not enough games</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr"/>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>4 pts vs 3.9 expected in last 10; TOI -0.6 min/gm; PP -0.6 min/gm; shots rate x0.92; goals vs shooting% +0.4</t>
+        </is>
+      </c>
       <c r="V8" t="n">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="W8" t="n">
-        <v>11.5</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alex Killorn</t>
+          <t>Tim Washe</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8920,65 +8920,65 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>16.1</v>
+        <v>15.2</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="I9" t="n">
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
-        <v>16.1</v>
+        <v>15.2</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="P9" t="n">
         <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Hot – usage-backed</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>4 pts vs 3.9 expected in last 10; TOI -0.6 min/gm; PP -0.6 min/gm; shots rate x0.92; goals vs shooting% +0.4</t>
+          <t>5 pts vs 1.6 expected in last 10; TOI +3.1 min/gm; PP +0.3 min/gm; shots rate x0.94; goals vs shooting% +2.4</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="W9" t="n">
-        <v>16.7</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tim Washe</t>
+          <t>Drew Helleson</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Top-6 F</t>
+          <t>Top-4 D</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -9003,65 +9003,61 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>15.2</v>
+        <v>18.2</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N10" t="n">
-        <v>15.2</v>
+        <v>18.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Hot – usage-backed</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>5 pts vs 1.6 expected in last 10; TOI +3.1 min/gm; PP +0.3 min/gm; shots rate x0.94; goals vs shooting% +2.4</t>
-        </is>
-      </c>
+          <t>Not enough games</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="W10" t="n">
-        <v>12.1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Drew Helleson</t>
+          <t>Pavel Mintyukov</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -9086,61 +9082,65 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Not enough games</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr"/>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2 pts vs 2.7 expected in last 9; TOI -0.3 min/gm; PP -0.5 min/gm; shots rate x0.52; goals vs shooting% -0.5</t>
+        </is>
+      </c>
       <c r="V11" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="W11" t="n">
-        <v>17</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pavel Mintyukov</t>
+          <t>Travis Mitchell</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Top-4 D</t>
+          <t>Depth F</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -9165,59 +9165,55 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>18.1</v>
+        <v>16.6</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N12" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Not enough games</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
         <v>9</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P12" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>2 pts vs 2.7 expected in last 9; TOI -0.3 min/gm; PP -0.5 min/gm; shots rate x0.52; goals vs shooting% -0.5</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>73</v>
-      </c>
       <c r="W12" t="n">
-        <v>18.4</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="13">
@@ -28937,11 +28933,7 @@
           <t>Depth F</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
           <t>last games</t>
@@ -42682,7 +42674,11 @@
           <t>Top-pair D</t>
         </is>
       </c>
-      <c r="E420" t="inlineStr"/>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F420" t="inlineStr">
         <is>
           <t>last games</t>
@@ -55306,7 +55302,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Colton Parayko</t>
+          <t>Theo Lindstein</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -55321,7 +55317,7 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>Top-4 D</t>
+          <t>Top-6 F</t>
         </is>
       </c>
       <c r="E574" t="inlineStr"/>
@@ -55331,65 +55327,61 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>21.1</v>
+        <v>14.5</v>
       </c>
       <c r="H574" t="n">
         <v>0.1</v>
       </c>
       <c r="I574" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J574" t="n">
         <v>0</v>
       </c>
       <c r="K574" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L574" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M574" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="N574" t="n">
-        <v>21.1</v>
+        <v>14.5</v>
       </c>
       <c r="O574" t="n">
         <v>0.1</v>
       </c>
       <c r="P574" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Q574" t="n">
         <v>0</v>
       </c>
       <c r="R574" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S574" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T574" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="U574" t="inlineStr">
-        <is>
-          <t>4 pts vs 2.2 expected in last 10; TOI -1.1 min/gm; PP -0.1 min/gm; shots rate x1.16; goals vs shooting% -0.6</t>
-        </is>
-      </c>
+          <t>Not enough games</t>
+        </is>
+      </c>
+      <c r="U574" t="inlineStr"/>
       <c r="V574" t="n">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="W574" t="n">
-        <v>22.2</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Brandon Carlo</t>
+          <t>Colton Parayko</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -55414,10 +55406,10 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>17.3</v>
+        <v>21.1</v>
       </c>
       <c r="H575" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I575" t="n">
         <v>10</v>
@@ -55426,19 +55418,19 @@
         <v>0</v>
       </c>
       <c r="K575" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L575" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M575" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N575" t="n">
-        <v>17.3</v>
+        <v>21.1</v>
       </c>
       <c r="O575" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P575" t="n">
         <v>10</v>
@@ -55447,10 +55439,10 @@
         <v>0</v>
       </c>
       <c r="R575" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S575" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T575" t="inlineStr">
         <is>
@@ -55459,20 +55451,20 @@
       </c>
       <c r="U575" t="inlineStr">
         <is>
-          <t>1 pts vs 1.1 expected in last 10; TOI -2.1 min/gm; PP -0.0 min/gm; shots rate x0.56; goals vs shooting% +0.0</t>
+          <t>4 pts vs 2.2 expected in last 10; TOI -1.1 min/gm; PP -0.1 min/gm; shots rate x1.16; goals vs shooting% -0.6</t>
         </is>
       </c>
       <c r="V575" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="W575" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Jake Neighbours</t>
+          <t>Brandon Carlo</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -55482,12 +55474,12 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>Depth F</t>
+          <t>Top-4 D</t>
         </is>
       </c>
       <c r="E576" t="inlineStr"/>
@@ -55497,44 +55489,44 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>15</v>
+        <v>17.3</v>
       </c>
       <c r="H576" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="I576" t="n">
         <v>10</v>
       </c>
       <c r="J576" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K576" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L576" t="n">
+        <v>1</v>
+      </c>
+      <c r="M576" t="n">
         <v>6</v>
       </c>
-      <c r="M576" t="n">
-        <v>15</v>
-      </c>
       <c r="N576" t="n">
-        <v>15</v>
+        <v>17.3</v>
       </c>
       <c r="O576" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P576" t="n">
         <v>10</v>
       </c>
       <c r="Q576" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R576" t="n">
+        <v>1</v>
+      </c>
+      <c r="S576" t="n">
         <v>6</v>
       </c>
-      <c r="S576" t="n">
-        <v>15</v>
-      </c>
       <c r="T576" t="inlineStr">
         <is>
           <t>Neutral</t>
@@ -55542,20 +55534,20 @@
       </c>
       <c r="U576" t="inlineStr">
         <is>
-          <t>6 pts vs 5.1 expected in last 10; TOI -0.2 min/gm; PP +0.1 min/gm; shots rate x1.22; goals vs shooting% +0.4</t>
+          <t>1 pts vs 1.1 expected in last 10; TOI -2.1 min/gm; PP -0.0 min/gm; shots rate x0.56; goals vs shooting% +0.0</t>
         </is>
       </c>
       <c r="V576" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="W576" t="n">
-        <v>15.2</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Jonatan Berggren</t>
+          <t>Jake Neighbours</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -55565,7 +55557,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -55580,43 +55572,43 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="H577" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="I577" t="n">
         <v>10</v>
       </c>
       <c r="J577" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K577" t="n">
         <v>3</v>
       </c>
       <c r="L577" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M577" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N577" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="O577" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="P577" t="n">
         <v>10</v>
       </c>
       <c r="Q577" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R577" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S577" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T577" t="inlineStr">
         <is>
@@ -55625,20 +55617,20 @@
       </c>
       <c r="U577" t="inlineStr">
         <is>
-          <t>5 pts vs 4.6 expected in last 10; TOI +0.8 min/gm; PP -0.3 min/gm; shots rate x1.16; goals vs shooting% +0.1</t>
+          <t>6 pts vs 5.1 expected in last 10; TOI -0.2 min/gm; PP +0.1 min/gm; shots rate x1.22; goals vs shooting% +0.4</t>
         </is>
       </c>
       <c r="V577" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="W577" t="n">
-        <v>13.8</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Theo Lindstein</t>
+          <t>Jonatan Berggren</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -55648,7 +55640,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -55663,55 +55655,59 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="H578" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="I578" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J578" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K578" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L578" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M578" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N578" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="O578" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="P578" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q578" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R578" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S578" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T578" t="inlineStr">
         <is>
-          <t>Not enough games</t>
-        </is>
-      </c>
-      <c r="U578" t="inlineStr"/>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="U578" t="inlineStr">
+        <is>
+          <t>5 pts vs 4.6 expected in last 10; TOI +0.8 min/gm; PP -0.3 min/gm; shots rate x1.16; goals vs shooting% +0.1</t>
+        </is>
+      </c>
       <c r="V578" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="W578" t="n">
-        <v>15.8</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="579">

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 07:39</t>
+          <t>2026-10-25 08:40</t>
         </is>
       </c>
     </row>

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:40</t>
+          <t>2026-10-26 09:10</t>
         </is>
       </c>
     </row>
@@ -21741,7 +21741,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Martin Necas</t>
+          <t>Taylor Makar</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -21751,84 +21751,76 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Top-6 F</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Top-pair D</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>20.1</v>
+        <v>6.2</v>
       </c>
       <c r="H167" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I167" t="n">
+        <v>2</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>1</v>
+      </c>
+      <c r="N167" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="n">
+        <v>1</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Not enough games</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr"/>
+      <c r="V167" t="n">
         <v>12</v>
       </c>
-      <c r="J167" t="n">
-        <v>6</v>
-      </c>
-      <c r="K167" t="n">
-        <v>10</v>
-      </c>
-      <c r="L167" t="n">
-        <v>16</v>
-      </c>
-      <c r="M167" t="n">
-        <v>24</v>
-      </c>
-      <c r="N167" t="n">
-        <v>20</v>
-      </c>
-      <c r="O167" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P167" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q167" t="n">
-        <v>4</v>
-      </c>
-      <c r="R167" t="n">
-        <v>12</v>
-      </c>
-      <c r="S167" t="n">
-        <v>16</v>
-      </c>
-      <c r="T167" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="U167" t="inlineStr">
-        <is>
-          <t>12 pts vs 12.2 expected in last 10; TOI -1.3 min/gm; PP -0.9 min/gm; shots rate x0.64; goals vs shooting% +1.0</t>
-        </is>
-      </c>
-      <c r="V167" t="n">
-        <v>78</v>
-      </c>
       <c r="W167" t="n">
-        <v>21.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Nazem Kadri</t>
+          <t>Martin Necas</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -21857,43 +21849,43 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="H168" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="I168" t="n">
         <v>12</v>
       </c>
       <c r="J168" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K168" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L168" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="M168" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="N168" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="O168" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P168" t="n">
         <v>10</v>
       </c>
       <c r="Q168" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R168" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S168" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -21902,20 +21894,20 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>6 pts vs 6.9 expected in last 10; TOI +0.9 min/gm; PP +0.7 min/gm; shots rate x0.86; goals vs shooting% -0.8</t>
+          <t>12 pts vs 12.2 expected in last 10; TOI -1.3 min/gm; PP -0.9 min/gm; shots rate x0.64; goals vs shooting% +1.0</t>
         </is>
       </c>
       <c r="V168" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W168" t="n">
-        <v>19</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Artturi Lehkonen</t>
+          <t>Nazem Kadri</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -21925,7 +21917,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -21933,50 +21925,54 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F169" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G169" t="n">
-        <v>18.9</v>
+        <v>19.9</v>
       </c>
       <c r="H169" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="I169" t="n">
         <v>12</v>
       </c>
       <c r="J169" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K169" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L169" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M169" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="N169" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
       <c r="O169" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="P169" t="n">
         <v>10</v>
       </c>
       <c r="Q169" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R169" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S169" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -21985,20 +21981,20 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>10 pts vs 7.4 expected in last 10; TOI +0.3 min/gm; PP -0.9 min/gm; shots rate x0.76; goals vs shooting% +4.4</t>
+          <t>6 pts vs 6.9 expected in last 10; TOI +0.9 min/gm; PP +0.7 min/gm; shots rate x0.86; goals vs shooting% -0.8</t>
         </is>
       </c>
       <c r="V169" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="W169" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Brock Nelson</t>
+          <t>Artturi Lehkonen</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -22008,7 +22004,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22023,43 +22019,43 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="H170" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="I170" t="n">
         <v>12</v>
       </c>
       <c r="J170" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K170" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L170" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M170" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N170" t="n">
-        <v>18.3</v>
+        <v>19</v>
       </c>
       <c r="O170" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="P170" t="n">
         <v>10</v>
       </c>
       <c r="Q170" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R170" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S170" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -22068,20 +22064,20 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>5 pts vs 7.7 expected in last 10; TOI -1.2 min/gm; PP -1.9 min/gm; shots rate x0.89; goals vs shooting% -1.4</t>
+          <t>10 pts vs 7.4 expected in last 10; TOI +0.3 min/gm; PP -0.9 min/gm; shots rate x0.76; goals vs shooting% +4.4</t>
         </is>
       </c>
       <c r="V170" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="W170" t="n">
-        <v>19.7</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Gabriel Landeskog</t>
+          <t>Brock Nelson</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -22091,7 +22087,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22106,43 +22102,43 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>15.3</v>
+        <v>18.4</v>
       </c>
       <c r="H171" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="I171" t="n">
         <v>12</v>
       </c>
       <c r="J171" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K171" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L171" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M171" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N171" t="n">
-        <v>15.5</v>
+        <v>18.3</v>
       </c>
       <c r="O171" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="P171" t="n">
         <v>10</v>
       </c>
       <c r="Q171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R171" t="n">
         <v>5</v>
       </c>
       <c r="S171" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -22151,20 +22147,20 @@
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>5 pts vs 5.6 expected in last 10; TOI -1.1 min/gm; PP -1.0 min/gm; shots rate x0.70; goals vs shooting% +1.4</t>
+          <t>5 pts vs 7.7 expected in last 10; TOI -1.2 min/gm; PP -1.9 min/gm; shots rate x0.89; goals vs shooting% -1.4</t>
         </is>
       </c>
       <c r="V171" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="W171" t="n">
-        <v>16.4</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Taylor Makar</t>
+          <t>Gabriel Landeskog</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -22185,59 +22181,63 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>6.2</v>
+        <v>15.3</v>
       </c>
       <c r="H172" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I172" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J172" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K172" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M172" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="N172" t="n">
-        <v>6.6</v>
+        <v>15.5</v>
       </c>
       <c r="O172" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P172" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q172" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R172" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S172" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
-          <t>Not enough games</t>
-        </is>
-      </c>
-      <c r="U172" t="inlineStr"/>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>5 pts vs 5.6 expected in last 10; TOI -1.1 min/gm; PP -1.0 min/gm; shots rate x0.70; goals vs shooting% +1.4</t>
+        </is>
+      </c>
       <c r="V172" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="W172" t="n">
-        <v>6.2</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="173">
@@ -42436,7 +42436,7 @@
         <v>23</v>
       </c>
       <c r="N418" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="O418" t="n">
         <v>3.4</v>
@@ -42460,7 +42460,7 @@
       </c>
       <c r="U418" t="inlineStr">
         <is>
-          <t>9 pts vs 9.7 expected in last 10; TOI +0.3 min/gm; PP +0.3 min/gm; shots rate x0.64; goals vs shooting% -0.7</t>
+          <t>9 pts vs 9.7 expected in last 10; TOI +0.4 min/gm; PP +0.3 min/gm; shots rate x0.63; goals vs shooting% -0.7</t>
         </is>
       </c>
       <c r="V418" t="n">
@@ -42502,7 +42502,7 @@
         </is>
       </c>
       <c r="G419" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="H419" t="n">
         <v>3.6</v>
@@ -42547,7 +42547,7 @@
       </c>
       <c r="U419" t="inlineStr">
         <is>
-          <t>13 pts vs 9.2 expected in last 10; TOI -1.0 min/gm; PP +0.3 min/gm; shots rate x0.72; goals vs shooting% -1.1</t>
+          <t>13 pts vs 9.3 expected in last 10; TOI -0.9 min/gm; PP +0.3 min/gm; shots rate x0.72; goals vs shooting% -1.1</t>
         </is>
       </c>
       <c r="V419" t="n">
@@ -42585,7 +42585,7 @@
         </is>
       </c>
       <c r="G420" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="H420" t="n">
         <v>0.1</v>
@@ -42630,7 +42630,7 @@
       </c>
       <c r="U420" t="inlineStr">
         <is>
-          <t>6 pts vs 3.7 expected in last 10; TOI -2.4 min/gm; PP -0.9 min/gm; shots rate x1.42; goals vs shooting% -1.1</t>
+          <t>6 pts vs 3.7 expected in last 10; TOI -2.3 min/gm; PP -0.9 min/gm; shots rate x1.42; goals vs shooting% -1.1</t>
         </is>
       </c>
       <c r="V420" t="n">
@@ -42717,7 +42717,7 @@
       </c>
       <c r="U421" t="inlineStr">
         <is>
-          <t>15 pts vs 7.3 expected in last 10; TOI +1.6 min/gm; PP +1.1 min/gm; shots rate x1.20; goals vs shooting% +5.3</t>
+          <t>15 pts vs 7.3 expected in last 10; TOI +1.7 min/gm; PP +1.1 min/gm; shots rate x1.20; goals vs shooting% +5.3</t>
         </is>
       </c>
       <c r="V421" t="n">
@@ -42846,7 +42846,7 @@
         </is>
       </c>
       <c r="G423" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="H423" t="n">
         <v>3.2</v>
@@ -42886,7 +42886,7 @@
       </c>
       <c r="T423" t="inlineStr">
         <is>
-          <t>Cold – shots steady</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="U423" t="inlineStr">
@@ -42974,7 +42974,7 @@
       </c>
       <c r="U424" t="inlineStr">
         <is>
-          <t>5 pts vs 6.0 expected in last 10; TOI +1.3 min/gm; PP +0.3 min/gm; shots rate x1.52; goals vs shooting% -1.1</t>
+          <t>5 pts vs 6.1 expected in last 10; TOI +1.4 min/gm; PP +0.3 min/gm; shots rate x1.52; goals vs shooting% -1.1</t>
         </is>
       </c>
       <c r="V424" t="n">
@@ -43012,7 +43012,7 @@
         </is>
       </c>
       <c r="G425" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="H425" t="n">
         <v>1.3</v>
@@ -43033,7 +43033,7 @@
         <v>29</v>
       </c>
       <c r="N425" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="O425" t="n">
         <v>1.3</v>
@@ -43057,7 +43057,7 @@
       </c>
       <c r="U425" t="inlineStr">
         <is>
-          <t>7 pts vs 4.5 expected in last 10; TOI -0.3 min/gm; PP -0.1 min/gm; shots rate x1.10; goals vs shooting% +1.5</t>
+          <t>7 pts vs 4.5 expected in last 10; TOI -0.4 min/gm; PP -0.1 min/gm; shots rate x1.11; goals vs shooting% +1.5</t>
         </is>
       </c>
       <c r="V425" t="n">
@@ -43095,7 +43095,7 @@
         </is>
       </c>
       <c r="G426" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="H426" t="n">
         <v>0.1</v>
@@ -43116,7 +43116,7 @@
         <v>9</v>
       </c>
       <c r="N426" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="O426" t="n">
         <v>0.1</v>
@@ -43140,7 +43140,7 @@
       </c>
       <c r="U426" t="inlineStr">
         <is>
-          <t>2 pts vs 2.0 expected in last 10; TOI -1.4 min/gm; PP +0.0 min/gm; shots rate x0.79; goals vs shooting% -0.3</t>
+          <t>2 pts vs 2.0 expected in last 10; TOI -1.3 min/gm; PP +0.0 min/gm; shots rate x0.79; goals vs shooting% -0.3</t>
         </is>
       </c>
       <c r="V426" t="n">
@@ -43178,7 +43178,7 @@
         </is>
       </c>
       <c r="G427" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="H427" t="n">
         <v>1.2</v>
@@ -43199,7 +43199,7 @@
         <v>11</v>
       </c>
       <c r="N427" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="O427" t="n">
         <v>1.2</v>
@@ -43223,7 +43223,7 @@
       </c>
       <c r="U427" t="inlineStr">
         <is>
-          <t>3 pts vs 4.5 expected in last 10; TOI +0.5 min/gm; PP -0.1 min/gm; shots rate x0.57; goals vs shooting% +0.4</t>
+          <t>3 pts vs 4.6 expected in last 10; TOI +0.6 min/gm; PP -0.1 min/gm; shots rate x0.56; goals vs shooting% +0.4</t>
         </is>
       </c>
       <c r="V427" t="n">
@@ -43306,7 +43306,7 @@
       </c>
       <c r="U428" t="inlineStr">
         <is>
-          <t>7 pts vs 4.4 expected in last 10; TOI +3.4 min/gm; PP -0.0 min/gm; shots rate x1.65; goals vs shooting% +0.5</t>
+          <t>7 pts vs 4.4 expected in last 10; TOI +3.5 min/gm; PP -0.0 min/gm; shots rate x1.65; goals vs shooting% +0.5</t>
         </is>
       </c>
       <c r="V428" t="n">
@@ -43344,7 +43344,7 @@
         </is>
       </c>
       <c r="G429" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="H429" t="n">
         <v>0.2</v>
@@ -43365,7 +43365,7 @@
         <v>11</v>
       </c>
       <c r="N429" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="O429" t="n">
         <v>0.1</v>
@@ -43389,7 +43389,7 @@
       </c>
       <c r="U429" t="inlineStr">
         <is>
-          <t>3 pts vs 3.7 expected in last 10; TOI +2.0 min/gm; PP -0.4 min/gm; shots rate x0.80; goals vs shooting% -1.1</t>
+          <t>3 pts vs 3.7 expected in last 10; TOI +1.9 min/gm; PP -0.4 min/gm; shots rate x0.81; goals vs shooting% -1.1</t>
         </is>
       </c>
       <c r="V429" t="n">
@@ -44221,7 +44221,7 @@
         </is>
       </c>
       <c r="G440" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -44242,7 +44242,7 @@
         <v>20</v>
       </c>
       <c r="N440" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="O440" t="n">
         <v>0.1</v>
@@ -44266,7 +44266,7 @@
       </c>
       <c r="U440" t="inlineStr">
         <is>
-          <t>2 pts vs 1.8 expected in last 10; TOI -2.9 min/gm; PP -0.3 min/gm; shots rate x1.28; goals vs shooting% -0.3</t>
+          <t>2 pts vs 1.8 expected in last 10; TOI -3.1 min/gm; PP -0.3 min/gm; shots rate x1.29; goals vs shooting% -0.3</t>
         </is>
       </c>
       <c r="V440" t="n">
@@ -44379,7 +44379,7 @@
         </is>
       </c>
       <c r="G442" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="H442" t="n">
         <v>0.1</v>
@@ -44400,7 +44400,7 @@
         <v>5</v>
       </c>
       <c r="N442" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="O442" t="n">
         <v>0</v>
@@ -44649,7 +44649,7 @@
         <v>14</v>
       </c>
       <c r="N445" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="O445" t="n">
         <v>0.4</v>
@@ -44673,7 +44673,7 @@
       </c>
       <c r="U445" t="inlineStr">
         <is>
-          <t>3 pts vs 4.6 expected in last 10; TOI +2.1 min/gm; PP -0.7 min/gm; shots rate x0.67; goals vs shooting% +0.3</t>
+          <t>3 pts vs 4.6 expected in last 10; TOI +2.2 min/gm; PP -0.7 min/gm; shots rate x0.67; goals vs shooting% +0.3</t>
         </is>
       </c>
       <c r="V445" t="n">
@@ -44711,7 +44711,7 @@
         </is>
       </c>
       <c r="G446" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="H446" t="n">
         <v>2.6</v>
@@ -44732,7 +44732,7 @@
         <v>22</v>
       </c>
       <c r="N446" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="O446" t="n">
         <v>2.5</v>
@@ -44756,7 +44756,7 @@
       </c>
       <c r="U446" t="inlineStr">
         <is>
-          <t>5 pts vs 6.8 expected in last 10; TOI +1.0 min/gm; PP +0.8 min/gm; shots rate x0.69; goals vs shooting% -0.3</t>
+          <t>5 pts vs 6.9 expected in last 10; TOI +1.0 min/gm; PP +0.8 min/gm; shots rate x0.69; goals vs shooting% -0.3</t>
         </is>
       </c>
       <c r="V446" t="n">
@@ -44843,7 +44843,7 @@
       </c>
       <c r="U447" t="inlineStr">
         <is>
-          <t>5 pts vs 7.4 expected in last 10; TOI +1.0 min/gm; PP +1.4 min/gm; shots rate x0.79; goals vs shooting% -1.8</t>
+          <t>5 pts vs 7.4 expected in last 10; TOI +0.9 min/gm; PP +1.4 min/gm; shots rate x0.79; goals vs shooting% -1.8</t>
         </is>
       </c>
       <c r="V447" t="n">
@@ -44972,7 +44972,7 @@
         </is>
       </c>
       <c r="G449" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="H449" t="n">
         <v>3.5</v>
@@ -44993,7 +44993,7 @@
         <v>17</v>
       </c>
       <c r="N449" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="O449" t="n">
         <v>3.3</v>
@@ -45017,7 +45017,7 @@
       </c>
       <c r="U449" t="inlineStr">
         <is>
-          <t>6 pts vs 6.5 expected in last 10; TOI +1.1 min/gm; PP +1.3 min/gm; shots rate x0.66; goals vs shooting% +0.8</t>
+          <t>6 pts vs 6.5 expected in last 10; TOI +1.0 min/gm; PP +1.3 min/gm; shots rate x0.66; goals vs shooting% +0.8</t>
         </is>
       </c>
       <c r="V449" t="n">
@@ -45138,7 +45138,7 @@
         </is>
       </c>
       <c r="G451" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="H451" t="n">
         <v>0.2</v>
@@ -45159,7 +45159,7 @@
         <v>16</v>
       </c>
       <c r="N451" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="O451" t="n">
         <v>0.2</v>
@@ -45221,7 +45221,7 @@
         </is>
       </c>
       <c r="G452" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="H452" t="n">
         <v>3.2</v>
@@ -45242,7 +45242,7 @@
         <v>8</v>
       </c>
       <c r="N452" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="O452" t="n">
         <v>3.2</v>
@@ -45462,7 +45462,7 @@
         </is>
       </c>
       <c r="G455" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="H455" t="n">
         <v>2.1</v>
@@ -45483,7 +45483,7 @@
         <v>25</v>
       </c>
       <c r="N455" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="O455" t="n">
         <v>2</v>
@@ -45507,7 +45507,7 @@
       </c>
       <c r="U455" t="inlineStr">
         <is>
-          <t>4 pts vs 4.2 expected in last 10; TOI +0.5 min/gm; PP +0.9 min/gm; shots rate x1.32; goals vs shooting% -1.8</t>
+          <t>4 pts vs 4.2 expected in last 10; TOI +0.4 min/gm; PP +0.9 min/gm; shots rate x1.33; goals vs shooting% -1.8</t>
         </is>
       </c>
       <c r="V455" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="U457" t="inlineStr">
         <is>
-          <t>4 pts vs 2.1 expected in last 10; TOI -1.7 min/gm; PP -0.5 min/gm; shots rate x0.99; goals vs shooting% -0.6</t>
+          <t>4 pts vs 2.1 expected in last 10; TOI -1.6 min/gm; PP -0.5 min/gm; shots rate x0.98; goals vs shooting% -0.6</t>
         </is>
       </c>
       <c r="V457" t="n">
@@ -45952,7 +45952,7 @@
         </is>
       </c>
       <c r="G461" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="H461" t="n">
         <v>3.3</v>
@@ -46031,7 +46031,7 @@
         </is>
       </c>
       <c r="G462" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -46052,7 +46052,7 @@
         <v>3</v>
       </c>
       <c r="N462" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="O462" t="n">
         <v>0</v>

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 07:55</t>
+          <t>2026-10-27 08:53</t>
         </is>
       </c>
     </row>
@@ -22374,7 +22374,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Taylor Makar</t>
+          <t>Martin Necas</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -22384,76 +22384,84 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Top-pair D</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr"/>
+          <t>Top-6 F</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G168" t="n">
-        <v>6.2</v>
+        <v>20.1</v>
       </c>
       <c r="H168" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I168" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J168" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K168" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M168" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="N168" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="O168" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P168" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q168" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S168" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
-          <t>Not enough games</t>
-        </is>
-      </c>
-      <c r="U168" t="inlineStr"/>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>12 pts vs 12.2 expected in last 10; TOI -1.3 min/gm; PP -0.9 min/gm; shots rate x0.64; goals vs shooting% +1.0</t>
+        </is>
+      </c>
       <c r="V168" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="W168" t="n">
-        <v>6.2</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Martin Necas</t>
+          <t>Nazem Kadri</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -22482,43 +22490,43 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="H169" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="I169" t="n">
         <v>12</v>
       </c>
       <c r="J169" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K169" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L169" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="M169" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="N169" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="O169" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P169" t="n">
         <v>10</v>
       </c>
       <c r="Q169" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R169" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="S169" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -22527,20 +22535,20 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>12 pts vs 12.2 expected in last 10; TOI -1.3 min/gm; PP -0.9 min/gm; shots rate x0.64; goals vs shooting% +1.0</t>
+          <t>6 pts vs 6.9 expected in last 10; TOI +0.9 min/gm; PP +0.7 min/gm; shots rate x0.86; goals vs shooting% -0.8</t>
         </is>
       </c>
       <c r="V169" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="W169" t="n">
-        <v>21.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Nazem Kadri</t>
+          <t>Artturi Lehkonen</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -22550,7 +22558,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22558,54 +22566,50 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G170" t="n">
-        <v>19.9</v>
+        <v>18.9</v>
       </c>
       <c r="H170" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="I170" t="n">
         <v>12</v>
       </c>
       <c r="J170" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K170" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L170" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M170" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="N170" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="O170" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="P170" t="n">
         <v>10</v>
       </c>
       <c r="Q170" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R170" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S170" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -22614,20 +22618,20 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>6 pts vs 6.9 expected in last 10; TOI +0.9 min/gm; PP +0.7 min/gm; shots rate x0.86; goals vs shooting% -0.8</t>
+          <t>10 pts vs 7.4 expected in last 10; TOI +0.3 min/gm; PP -0.9 min/gm; shots rate x0.76; goals vs shooting% +4.4</t>
         </is>
       </c>
       <c r="V170" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="W170" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Artturi Lehkonen</t>
+          <t>Brock Nelson</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -22637,7 +22641,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22652,43 +22656,43 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="H171" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="I171" t="n">
         <v>12</v>
       </c>
       <c r="J171" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K171" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L171" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M171" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N171" t="n">
-        <v>19</v>
+        <v>18.3</v>
       </c>
       <c r="O171" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="P171" t="n">
         <v>10</v>
       </c>
       <c r="Q171" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R171" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="S171" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -22697,20 +22701,20 @@
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>10 pts vs 7.4 expected in last 10; TOI +0.3 min/gm; PP -0.9 min/gm; shots rate x0.76; goals vs shooting% +4.4</t>
+          <t>5 pts vs 7.7 expected in last 10; TOI -1.2 min/gm; PP -1.9 min/gm; shots rate x0.89; goals vs shooting% -1.4</t>
         </is>
       </c>
       <c r="V171" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="W171" t="n">
-        <v>18.5</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Brock Nelson</t>
+          <t>Gabriel Landeskog</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -22720,7 +22724,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22735,43 +22739,43 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>18.4</v>
+        <v>15.3</v>
       </c>
       <c r="H172" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="I172" t="n">
         <v>12</v>
       </c>
       <c r="J172" t="n">
+        <v>4</v>
+      </c>
+      <c r="K172" t="n">
         <v>3</v>
       </c>
-      <c r="K172" t="n">
-        <v>5</v>
-      </c>
       <c r="L172" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M172" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="N172" t="n">
-        <v>18.3</v>
+        <v>15.5</v>
       </c>
       <c r="O172" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="P172" t="n">
         <v>10</v>
       </c>
       <c r="Q172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R172" t="n">
         <v>5</v>
       </c>
       <c r="S172" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -22780,20 +22784,20 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>5 pts vs 7.7 expected in last 10; TOI -1.2 min/gm; PP -1.9 min/gm; shots rate x0.89; goals vs shooting% -1.4</t>
+          <t>5 pts vs 5.6 expected in last 10; TOI -1.1 min/gm; PP -1.0 min/gm; shots rate x0.70; goals vs shooting% +1.4</t>
         </is>
       </c>
       <c r="V172" t="n">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="W172" t="n">
-        <v>19.7</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Gabriel Landeskog</t>
+          <t>Brett Kulak</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -22803,12 +22807,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Top-6 F</t>
+          <t>Top-4 D</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -22818,43 +22822,43 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>15.3</v>
+        <v>19</v>
       </c>
       <c r="H173" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I173" t="n">
         <v>12</v>
       </c>
       <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
         <v>4</v>
       </c>
-      <c r="K173" t="n">
-        <v>3</v>
-      </c>
       <c r="L173" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M173" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N173" t="n">
-        <v>15.5</v>
+        <v>18.9</v>
       </c>
       <c r="O173" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P173" t="n">
         <v>10</v>
       </c>
       <c r="Q173" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S173" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -22863,20 +22867,20 @@
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>5 pts vs 5.6 expected in last 10; TOI -1.1 min/gm; PP -1.0 min/gm; shots rate x0.70; goals vs shooting% +1.4</t>
+          <t>4 pts vs 1.4 expected in last 10; TOI +0.0 min/gm; PP -0.1 min/gm; shots rate x0.80; goals vs shooting% -0.1</t>
         </is>
       </c>
       <c r="V173" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="W173" t="n">
-        <v>16.4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Brett Kulak</t>
+          <t>Sam Malinski</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -22901,31 +22905,31 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>19</v>
+        <v>17.2</v>
       </c>
       <c r="H174" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I174" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L174" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M174" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N174" t="n">
-        <v>18.9</v>
+        <v>17</v>
       </c>
       <c r="O174" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P174" t="n">
         <v>10</v>
@@ -22934,7 +22938,7 @@
         <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S174" t="n">
         <v>9</v>
@@ -22946,20 +22950,20 @@
       </c>
       <c r="U174" t="inlineStr">
         <is>
-          <t>4 pts vs 1.4 expected in last 10; TOI +0.0 min/gm; PP -0.1 min/gm; shots rate x0.80; goals vs shooting% -0.1</t>
+          <t>3 pts vs 4.7 expected in last 10; TOI -0.4 min/gm; PP -0.1 min/gm; shots rate x0.46; goals vs shooting% -0.4</t>
         </is>
       </c>
       <c r="V174" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W174" t="n">
-        <v>19</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Sam Malinski</t>
+          <t>T.J. Hughes</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -22969,80 +22973,80 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Top-4 D</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr"/>
+          <t>Depth F</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F175" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>17.2</v>
+        <v>14.5</v>
       </c>
       <c r="H175" t="n">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="I175" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L175" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M175" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="N175" t="n">
-        <v>17</v>
+        <v>14.9</v>
       </c>
       <c r="O175" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="P175" t="n">
         <v>10</v>
       </c>
       <c r="Q175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R175" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S175" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="U175" t="inlineStr">
-        <is>
-          <t>3 pts vs 4.7 expected in last 10; TOI -0.4 min/gm; PP -0.1 min/gm; shots rate x0.46; goals vs shooting% -0.4</t>
-        </is>
-      </c>
+          <t>Not enough baseline</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr"/>
       <c r="V175" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="W175" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>T.J. Hughes</t>
+          <t>Jaden Schwartz</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -23052,7 +23056,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23060,72 +23064,72 @@
           <t>Depth F</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H176" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="I176" t="n">
         <v>12</v>
       </c>
       <c r="J176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K176" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L176" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M176" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="N176" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="O176" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="P176" t="n">
         <v>10</v>
       </c>
       <c r="Q176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R176" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S176" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
-          <t>Not enough baseline</t>
-        </is>
-      </c>
-      <c r="U176" t="inlineStr"/>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>5 pts vs 4.8 expected in last 10; TOI -1.9 min/gm; PP +0.6 min/gm; shots rate x0.95; goals vs shooting% +1.2</t>
+        </is>
+      </c>
       <c r="V176" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W176" t="n">
-        <v>0</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Jaden Schwartz</t>
+          <t>Fedor Svechkov</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -23135,7 +23139,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23150,65 +23154,65 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>14.2</v>
+        <v>13.1</v>
       </c>
       <c r="H177" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="I177" t="n">
         <v>12</v>
       </c>
       <c r="J177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K177" t="n">
         <v>4</v>
       </c>
       <c r="L177" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M177" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="N177" t="n">
-        <v>14.1</v>
+        <v>13.5</v>
       </c>
       <c r="O177" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="P177" t="n">
         <v>10</v>
       </c>
       <c r="Q177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R177" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S177" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Hot – mixed</t>
         </is>
       </c>
       <c r="U177" t="inlineStr">
         <is>
-          <t>5 pts vs 4.8 expected in last 10; TOI -1.9 min/gm; PP +0.6 min/gm; shots rate x0.95; goals vs shooting% +1.2</t>
+          <t>6 pts vs 2.5 expected in last 10; TOI +0.9 min/gm; PP -0.1 min/gm; shots rate x0.84; goals vs shooting% +1.5</t>
         </is>
       </c>
       <c r="V177" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="W177" t="n">
-        <v>16.1</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Fedor Svechkov</t>
+          <t>Parker Kelly</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -23233,65 +23237,65 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>13.1</v>
+        <v>12.7</v>
       </c>
       <c r="H178" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I178" t="n">
         <v>12</v>
       </c>
       <c r="J178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K178" t="n">
         <v>4</v>
       </c>
       <c r="L178" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M178" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N178" t="n">
-        <v>13.5</v>
+        <v>12.9</v>
       </c>
       <c r="O178" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P178" t="n">
         <v>10</v>
       </c>
       <c r="Q178" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S178" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
-          <t>Hot – mixed</t>
+          <t>Cold – shots down</t>
         </is>
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>6 pts vs 2.5 expected in last 10; TOI +0.9 min/gm; PP -0.1 min/gm; shots rate x0.84; goals vs shooting% +1.5</t>
+          <t>1 pts vs 4.6 expected in last 10; TOI -0.1 min/gm; PP -0.0 min/gm; shots rate x0.80; goals vs shooting% -2.1</t>
         </is>
       </c>
       <c r="V178" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="W178" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Parker Kelly</t>
+          <t>Nicolas Roy</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -23316,65 +23320,61 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>12.7</v>
+        <v>11.7</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
       </c>
       <c r="I179" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K179" t="n">
+        <v>2</v>
+      </c>
+      <c r="L179" t="n">
         <v>4</v>
       </c>
-      <c r="L179" t="n">
-        <v>5</v>
-      </c>
       <c r="M179" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N179" t="n">
-        <v>12.9</v>
+        <v>11.7</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
       </c>
       <c r="P179" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R179" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
-          <t>Cold – shots down</t>
-        </is>
-      </c>
-      <c r="U179" t="inlineStr">
-        <is>
-          <t>1 pts vs 4.6 expected in last 10; TOI -0.1 min/gm; PP -0.0 min/gm; shots rate x0.80; goals vs shooting% -2.1</t>
-        </is>
-      </c>
+          <t>Not enough games</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr"/>
       <c r="V179" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="W179" t="n">
-        <v>12.7</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Nicolas Roy</t>
+          <t>Logan O'Connor</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -23384,7 +23384,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23395,47 +23395,47 @@
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
       </c>
       <c r="I180" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
+        <v>4</v>
+      </c>
+      <c r="N180" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
         <v>2</v>
       </c>
-      <c r="K180" t="n">
-        <v>2</v>
-      </c>
-      <c r="L180" t="n">
+      <c r="Q180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R180" t="n">
+        <v>0</v>
+      </c>
+      <c r="S180" t="n">
         <v>4</v>
-      </c>
-      <c r="M180" t="n">
-        <v>10</v>
-      </c>
-      <c r="N180" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="O180" t="n">
-        <v>0</v>
-      </c>
-      <c r="P180" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q180" t="n">
-        <v>2</v>
-      </c>
-      <c r="R180" t="n">
-        <v>4</v>
-      </c>
-      <c r="S180" t="n">
-        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -23444,16 +23444,16 @@
       </c>
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="n">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="W180" t="n">
-        <v>14.5</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Logan O'Connor</t>
+          <t>Zachary L'Heureux</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -23463,7 +23463,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23474,47 +23474,47 @@
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>11.4</v>
+        <v>9.1</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N181" t="n">
-        <v>13.3</v>
+        <v>9.1</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
       </c>
       <c r="P181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q181" t="n">
         <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S181" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -23523,16 +23523,16 @@
       </c>
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="W181" t="n">
-        <v>11.4</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Zachary L'Heureux</t>
+          <t>Gavin Brindley</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -23542,7 +23542,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23557,43 +23557,43 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
       </c>
       <c r="I182" t="n">
+        <v>4</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>1</v>
+      </c>
+      <c r="L182" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" t="n">
         <v>3</v>
       </c>
-      <c r="J182" t="n">
-        <v>0</v>
-      </c>
-      <c r="K182" t="n">
-        <v>1</v>
-      </c>
-      <c r="L182" t="n">
-        <v>1</v>
-      </c>
-      <c r="M182" t="n">
-        <v>6</v>
-      </c>
       <c r="N182" t="n">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
       </c>
       <c r="P182" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>0</v>
+      </c>
+      <c r="R182" t="n">
+        <v>1</v>
+      </c>
+      <c r="S182" t="n">
         <v>3</v>
-      </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
-      <c r="R182" t="n">
-        <v>1</v>
-      </c>
-      <c r="S182" t="n">
-        <v>6</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -23602,16 +23602,16 @@
       </c>
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="n">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="W182" t="n">
-        <v>13.4</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Gavin Brindley</t>
+          <t>Taylor Makar</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -23621,7 +23621,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23632,47 +23632,47 @@
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>8.1</v>
+        <v>6.2</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
       </c>
       <c r="I183" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
       </c>
       <c r="K183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N183" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
       </c>
       <c r="P183" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q183" t="n">
         <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -23681,10 +23681,10 @@
       </c>
       <c r="U183" t="inlineStr"/>
       <c r="V183" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="W183" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="184">
@@ -26215,7 +26215,7 @@
         <v>11</v>
       </c>
       <c r="M214" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N214" t="n">
         <v>20.6</v>
@@ -26233,7 +26233,7 @@
         <v>11</v>
       </c>
       <c r="S214" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>11 pts vs 10.0 expected in last 10; TOI +1.5 min/gm; PP +0.7 min/gm; shots rate x1.46; goals vs shooting% -1.8</t>
+          <t>11 pts vs 10.0 expected in last 10; TOI +1.5 min/gm; PP +0.7 min/gm; shots rate x1.42; goals vs shooting% -1.7</t>
         </is>
       </c>
       <c r="V214" t="n">
@@ -29878,7 +29878,7 @@
         <v>1</v>
       </c>
       <c r="M259" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N259" t="n">
         <v>11.8</v>
@@ -29896,7 +29896,7 @@
         <v>1</v>
       </c>
       <c r="S259" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>1 pts vs 1.3 expected in last 10; TOI -3.7 min/gm; PP -0.0 min/gm; shots rate x1.64; goals vs shooting% -0.3</t>
+          <t>1 pts vs 1.3 expected in last 10; TOI -3.7 min/gm; PP -0.0 min/gm; shots rate x1.44; goals vs shooting% -0.3</t>
         </is>
       </c>
       <c r="V259" t="n">

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 08:00</t>
+          <t>2026-10-28 08:58</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
         <v>21</v>
       </c>
       <c r="P3" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>21</v>
       </c>
       <c r="P5" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>33</v>
       </c>
       <c r="P6" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>28</v>
       </c>
       <c r="P22" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>6</v>
       </c>
       <c r="M40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N40" t="n">
         <v>11.3</v>
@@ -11403,7 +11403,7 @@
         <v>3</v>
       </c>
       <c r="S40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>3 pts vs 2.7 expected in last 10; TOI -1.2 min/gm; PP +0.1 min/gm; shots rate x1.19; goals vs shooting% -0.6</t>
+          <t>3 pts vs 2.7 expected in last 10; TOI -1.2 min/gm; PP +0.1 min/gm; shots rate x1.28; goals vs shooting% -0.8</t>
         </is>
       </c>
       <c r="V40" t="n">
@@ -46878,7 +46878,7 @@
         <v>5</v>
       </c>
       <c r="M471" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N471" t="n">
         <v>17.7</v>
@@ -46896,7 +46896,7 @@
         <v>4</v>
       </c>
       <c r="S471" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T471" t="inlineStr">
         <is>
@@ -46905,7 +46905,7 @@
       </c>
       <c r="U471" t="inlineStr">
         <is>
-          <t>4 pts vs 6.2 expected in last 10; TOI +0.0 min/gm; PP -0.1 min/gm; shots rate x0.65; goals vs shooting% +0.6</t>
+          <t>4 pts vs 6.2 expected in last 10; TOI +0.0 min/gm; PP -0.1 min/gm; shots rate x0.70; goals vs shooting% +0.5</t>
         </is>
       </c>
       <c r="V471" t="n">

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 12:37</t>
+          <t>2026-10-29 13:16</t>
         </is>
       </c>
     </row>
@@ -22513,7 +22513,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Brock Nelson</t>
+          <t>Gabriel Landeskog</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -22523,7 +22523,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22538,43 +22538,43 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>18.4</v>
+        <v>15</v>
       </c>
       <c r="H171" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="I171" t="n">
         <v>13</v>
       </c>
       <c r="J171" t="n">
+        <v>5</v>
+      </c>
+      <c r="K171" t="n">
         <v>3</v>
-      </c>
-      <c r="K171" t="n">
-        <v>5</v>
       </c>
       <c r="L171" t="n">
         <v>8</v>
       </c>
       <c r="M171" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N171" t="n">
-        <v>18.2</v>
+        <v>15.2</v>
       </c>
       <c r="O171" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="P171" t="n">
         <v>10</v>
       </c>
       <c r="Q171" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R171" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S171" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -22583,20 +22583,20 @@
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>5 pts vs 7.6 expected in last 10; TOI -1.1 min/gm; PP -1.8 min/gm; shots rate x1.05; goals vs shooting% -2.0</t>
+          <t>6 pts vs 5.4 expected in last 10; TOI -1.4 min/gm; PP -0.9 min/gm; shots rate x0.61; goals vs shooting% +2.7</t>
         </is>
       </c>
       <c r="V171" t="n">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="W171" t="n">
-        <v>19.7</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Gabriel Landeskog</t>
+          <t>Brett Kulak</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -22606,12 +22606,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Top-6 F</t>
+          <t>Top-4 D</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -22621,43 +22621,43 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="H172" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I172" t="n">
         <v>13</v>
       </c>
       <c r="J172" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L172" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M172" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N172" t="n">
-        <v>15.2</v>
+        <v>19.2</v>
       </c>
       <c r="O172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P172" t="n">
         <v>10</v>
       </c>
       <c r="Q172" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S172" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -22666,20 +22666,20 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>6 pts vs 5.4 expected in last 10; TOI -1.4 min/gm; PP -0.9 min/gm; shots rate x0.61; goals vs shooting% +2.7</t>
+          <t>3 pts vs 1.6 expected in last 10; TOI +0.6 min/gm; PP -0.1 min/gm; shots rate x0.86; goals vs shooting% -0.1</t>
         </is>
       </c>
       <c r="V172" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="W172" t="n">
-        <v>16.4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Brett Kulak</t>
+          <t>Sam Malinski</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -22704,31 +22704,31 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>19.5</v>
+        <v>17.8</v>
       </c>
       <c r="H173" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I173" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L173" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M173" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N173" t="n">
-        <v>19.2</v>
+        <v>17.3</v>
       </c>
       <c r="O173" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P173" t="n">
         <v>10</v>
@@ -22737,10 +22737,10 @@
         <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -22749,20 +22749,20 @@
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>3 pts vs 1.6 expected in last 10; TOI +0.6 min/gm; PP -0.1 min/gm; shots rate x0.86; goals vs shooting% -0.1</t>
+          <t>5 pts vs 4.8 expected in last 10; TOI +0.2 min/gm; PP -0.1 min/gm; shots rate x0.55; goals vs shooting% -0.5</t>
         </is>
       </c>
       <c r="V173" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W173" t="n">
-        <v>19</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Sam Malinski</t>
+          <t>Brock Nelson</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -22772,12 +22772,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Top-4 D</t>
+          <t>Depth F</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -22787,43 +22787,43 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>17.8</v>
+        <v>18.4</v>
       </c>
       <c r="H174" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="I174" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J174" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K174" t="n">
         <v>5</v>
       </c>
       <c r="L174" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M174" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="N174" t="n">
-        <v>17.3</v>
+        <v>18.2</v>
       </c>
       <c r="O174" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="P174" t="n">
         <v>10</v>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R174" t="n">
         <v>5</v>
       </c>
       <c r="S174" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -22832,14 +22832,14 @@
       </c>
       <c r="U174" t="inlineStr">
         <is>
-          <t>5 pts vs 4.8 expected in last 10; TOI +0.2 min/gm; PP -0.1 min/gm; shots rate x0.55; goals vs shooting% -0.5</t>
+          <t>5 pts vs 7.6 expected in last 10; TOI -1.1 min/gm; PP -1.8 min/gm; shots rate x1.05; goals vs shooting% -2.0</t>
         </is>
       </c>
       <c r="V174" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="W174" t="n">
-        <v>17.6</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="175">
@@ -25736,11 +25736,7 @@
           <t>Depth (no NHL data)</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
           <t>no NHL data</t>
@@ -36135,7 +36131,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Juraj Slafkovský</t>
+          <t>Cole Caufield</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -36145,7 +36141,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -36164,7 +36160,7 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
       <c r="H337" t="n">
         <v>3.5</v>
@@ -36173,19 +36169,19 @@
         <v>12</v>
       </c>
       <c r="J337" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K337" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L337" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M337" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="N337" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="O337" t="n">
         <v>3.3</v>
@@ -36194,13 +36190,13 @@
         <v>10</v>
       </c>
       <c r="Q337" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R337" t="n">
         <v>8</v>
       </c>
       <c r="S337" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="T337" t="inlineStr">
         <is>
@@ -36209,20 +36205,20 @@
       </c>
       <c r="U337" t="inlineStr">
         <is>
-          <t>8 pts vs 8.6 expected in last 10; TOI -0.2 min/gm; PP +0.2 min/gm; shots rate x1.34; goals vs shooting% -2.7</t>
+          <t>8 pts vs 11.1 expected in last 10; TOI +0.5 min/gm; PP +0.1 min/gm; shots rate x1.01; goals vs shooting% -2.6</t>
         </is>
       </c>
       <c r="V337" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="W337" t="n">
-        <v>18.5</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Phillip Danault</t>
+          <t>Juraj Slafkovský</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -36232,7 +36228,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -36240,50 +36236,54 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E338" t="inlineStr"/>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F338" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G338" t="n">
-        <v>17.2</v>
+        <v>18.4</v>
       </c>
       <c r="H338" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="I338" t="n">
         <v>12</v>
       </c>
       <c r="J338" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K338" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L338" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M338" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N338" t="n">
-        <v>16.6</v>
+        <v>18.3</v>
       </c>
       <c r="O338" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="P338" t="n">
         <v>10</v>
       </c>
       <c r="Q338" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R338" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S338" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -36292,20 +36292,20 @@
       </c>
       <c r="U338" t="inlineStr">
         <is>
-          <t>3 pts vs 2.4 expected in last 10; TOI +1.7 min/gm; PP -0.4 min/gm; shots rate x1.37; goals vs shooting% -1.2</t>
+          <t>8 pts vs 8.6 expected in last 10; TOI -0.2 min/gm; PP +0.2 min/gm; shots rate x1.34; goals vs shooting% -2.7</t>
         </is>
       </c>
       <c r="V338" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="W338" t="n">
-        <v>15.6</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Alex Newhook</t>
+          <t>Phillip Danault</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -36330,43 +36330,43 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>16.2</v>
+        <v>17.2</v>
       </c>
       <c r="H339" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="I339" t="n">
         <v>12</v>
       </c>
       <c r="J339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K339" t="n">
         <v>3</v>
       </c>
       <c r="L339" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M339" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N339" t="n">
-        <v>16.2</v>
+        <v>16.6</v>
       </c>
       <c r="O339" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="P339" t="n">
         <v>10</v>
       </c>
       <c r="Q339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R339" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S339" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="T339" t="inlineStr">
         <is>
@@ -36375,20 +36375,20 @@
       </c>
       <c r="U339" t="inlineStr">
         <is>
-          <t>4 pts vs 6.3 expected in last 10; TOI +1.7 min/gm; PP +0.2 min/gm; shots rate x0.55; goals vs shooting% -0.8</t>
+          <t>3 pts vs 2.4 expected in last 10; TOI +1.7 min/gm; PP -0.4 min/gm; shots rate x1.37; goals vs shooting% -1.2</t>
         </is>
       </c>
       <c r="V339" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="W339" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Ivan Demidov</t>
+          <t>Alex Newhook</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -36398,7 +36398,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -36406,72 +36406,72 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr">
         <is>
-          <t>last season</t>
+          <t>last games</t>
         </is>
       </c>
       <c r="G340" t="n">
-        <v>15.5</v>
+        <v>16.2</v>
       </c>
       <c r="H340" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I340" t="n">
+        <v>12</v>
+      </c>
+      <c r="J340" t="n">
+        <v>1</v>
+      </c>
+      <c r="K340" t="n">
         <v>3</v>
       </c>
-      <c r="I340" t="n">
-        <v>2</v>
-      </c>
-      <c r="J340" t="n">
-        <v>1</v>
-      </c>
-      <c r="K340" t="n">
-        <v>1</v>
-      </c>
       <c r="L340" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M340" t="n">
+        <v>12</v>
+      </c>
+      <c r="N340" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="O340" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P340" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>1</v>
+      </c>
+      <c r="R340" t="n">
         <v>4</v>
       </c>
-      <c r="N340" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="O340" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P340" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q340" t="n">
-        <v>1</v>
-      </c>
-      <c r="R340" t="n">
-        <v>2</v>
-      </c>
       <c r="S340" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T340" t="inlineStr">
         <is>
-          <t>Not enough games</t>
-        </is>
-      </c>
-      <c r="U340" t="inlineStr"/>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>4 pts vs 6.3 expected in last 10; TOI +1.7 min/gm; PP +0.2 min/gm; shots rate x0.55; goals vs shooting% -0.8</t>
+        </is>
+      </c>
       <c r="V340" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="W340" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Kaiden Guhle</t>
+          <t>Ivan Demidov</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -36481,80 +36481,80 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Top-4 D</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr"/>
+          <t>Top-6 F</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>last games</t>
+          <t>last season</t>
         </is>
       </c>
       <c r="G341" t="n">
-        <v>22.4</v>
+        <v>15.5</v>
       </c>
       <c r="H341" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="I341" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J341" t="n">
+        <v>1</v>
+      </c>
+      <c r="K341" t="n">
+        <v>1</v>
+      </c>
+      <c r="L341" t="n">
         <v>2</v>
       </c>
-      <c r="K341" t="n">
+      <c r="M341" t="n">
+        <v>4</v>
+      </c>
+      <c r="N341" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="O341" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P341" t="n">
         <v>2</v>
       </c>
-      <c r="L341" t="n">
+      <c r="Q341" t="n">
+        <v>1</v>
+      </c>
+      <c r="R341" t="n">
+        <v>2</v>
+      </c>
+      <c r="S341" t="n">
         <v>4</v>
       </c>
-      <c r="M341" t="n">
-        <v>11</v>
-      </c>
-      <c r="N341" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="O341" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="P341" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q341" t="n">
-        <v>2</v>
-      </c>
-      <c r="R341" t="n">
-        <v>4</v>
-      </c>
-      <c r="S341" t="n">
-        <v>11</v>
-      </c>
       <c r="T341" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="U341" t="inlineStr">
-        <is>
-          <t>4 pts vs 2.6 expected in last 8; TOI +2.9 min/gm; PP +0.1 min/gm; shots rate x1.17; goals vs shooting% +1.4</t>
-        </is>
-      </c>
+          <t>Not enough games</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr"/>
       <c r="V341" t="n">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="W341" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Alexandre Carrier</t>
+          <t>Kaiden Guhle</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -36579,43 +36579,43 @@
         </is>
       </c>
       <c r="G342" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="H342" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I342" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J342" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K342" t="n">
+        <v>2</v>
+      </c>
+      <c r="L342" t="n">
         <v>4</v>
       </c>
-      <c r="L342" t="n">
-        <v>5</v>
-      </c>
       <c r="M342" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N342" t="n">
-        <v>19.9</v>
+        <v>22.4</v>
       </c>
       <c r="O342" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P342" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q342" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R342" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S342" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -36624,20 +36624,20 @@
       </c>
       <c r="U342" t="inlineStr">
         <is>
-          <t>3 pts vs 3.5 expected in last 10; TOI +1.9 min/gm; PP +0.0 min/gm; shots rate x1.04; goals vs shooting% -1.2</t>
+          <t>4 pts vs 2.6 expected in last 8; TOI +2.9 min/gm; PP +0.1 min/gm; shots rate x1.17; goals vs shooting% +1.4</t>
         </is>
       </c>
       <c r="V342" t="n">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="W342" t="n">
-        <v>19.1</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Cole Caufield</t>
+          <t>Alexandre Carrier</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -36647,62 +36647,58 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Depth F</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Top-4 D</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>18.7</v>
+        <v>20.9</v>
       </c>
       <c r="H343" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="I343" t="n">
         <v>12</v>
       </c>
       <c r="J343" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K343" t="n">
         <v>4</v>
       </c>
       <c r="L343" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M343" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="N343" t="n">
-        <v>18.8</v>
+        <v>19.9</v>
       </c>
       <c r="O343" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P343" t="n">
         <v>10</v>
       </c>
       <c r="Q343" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R343" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S343" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="T343" t="inlineStr">
         <is>
@@ -36711,14 +36707,14 @@
       </c>
       <c r="U343" t="inlineStr">
         <is>
-          <t>8 pts vs 11.1 expected in last 10; TOI +0.5 min/gm; PP +0.1 min/gm; shots rate x1.01; goals vs shooting% -2.6</t>
+          <t>3 pts vs 3.5 expected in last 10; TOI +1.9 min/gm; PP +0.0 min/gm; shots rate x1.04; goals vs shooting% -1.2</t>
         </is>
       </c>
       <c r="V343" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="W343" t="n">
-        <v>18.2</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="344">
@@ -51159,11 +51155,7 @@
           <t>Depth F</t>
         </is>
       </c>
-      <c r="E519" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E519" t="inlineStr"/>
       <c r="F519" t="inlineStr">
         <is>
           <t>last season</t>

--- a/output/nhl_daily_data.xlsx
+++ b/output/nhl_daily_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 12:20</t>
+          <t>2026-10-30 12:55</t>
         </is>
       </c>
     </row>
@@ -20222,7 +20222,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Tyler Bertuzzi</t>
+          <t>Patrick Kane</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -20251,7 +20251,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="H148" t="n">
         <v>3.8</v>
@@ -20260,19 +20260,19 @@
         <v>13</v>
       </c>
       <c r="J148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K148" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L148" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M148" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="N148" t="n">
-        <v>17.4</v>
+        <v>18.9</v>
       </c>
       <c r="O148" t="n">
         <v>3.5</v>
@@ -20281,13 +20281,13 @@
         <v>10</v>
       </c>
       <c r="Q148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S148" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -20296,20 +20296,20 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>4 pts vs 6.8 expected in last 10; TOI -0.9 min/gm; PP +0.6 min/gm; shots rate x0.62; goals vs shooting% -1.4</t>
+          <t>7 pts vs 8.6 expected in last 10; TOI +0.7 min/gm; PP +0.6 min/gm; shots rate x0.74; goals vs shooting% -1.9</t>
         </is>
       </c>
       <c r="V148" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="W148" t="n">
-        <v>18.4</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Frank Nazar</t>
+          <t>Tyler Bertuzzi</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -20319,7 +20319,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -20327,50 +20327,54 @@
           <t>Top-6 F</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="H149" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="I149" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J149" t="n">
+        <v>2</v>
+      </c>
+      <c r="K149" t="n">
         <v>3</v>
-      </c>
-      <c r="K149" t="n">
-        <v>2</v>
       </c>
       <c r="L149" t="n">
         <v>5</v>
       </c>
       <c r="M149" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N149" t="n">
         <v>17.4</v>
       </c>
       <c r="O149" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="P149" t="n">
         <v>10</v>
       </c>
       <c r="Q149" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R149" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S149" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -20379,20 +20383,20 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>5 pts vs 5.8 expected in last 10; TOI -0.9 min/gm; PP -1.6 min/gm; shots rate x0.70; goals vs shooting% +1.5</t>
+          <t>4 pts vs 6.8 expected in last 10; TOI -0.9 min/gm; PP +0.6 min/gm; shots rate x0.62; goals vs shooting% -1.4</t>
         </is>
       </c>
       <c r="V149" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="W149" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Anton Frondell</t>
+          <t>Frank Nazar</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -20417,61 +20421,65 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>16.3</v>
+        <v>17.4</v>
       </c>
       <c r="H150" t="n">
         <v>1.5</v>
       </c>
       <c r="I150" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K150" t="n">
+        <v>2</v>
+      </c>
+      <c r="L150" t="n">
         <v>5</v>
       </c>
-      <c r="L150" t="n">
-        <v>6</v>
-      </c>
       <c r="M150" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N150" t="n">
-        <v>16.5</v>
+        <v>17.4</v>
       </c>
       <c r="O150" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="P150" t="n">
         <v>10</v>
       </c>
       <c r="Q150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R150" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S150" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>Not enough baseline</t>
-        </is>
-      </c>
-      <c r="U150" t="inlineStr"/>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>5 pts vs 5.8 expected in last 10; TOI -0.9 min/gm; PP -1.6 min/gm; shots rate x0.70; goals vs shooting% +1.5</t>
+        </is>
+      </c>
       <c r="V150" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="W150" t="n">
-        <v>17.7</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Alex Vlasic</t>
+          <t>Anton Frondell</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -20481,12 +20489,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Top-4 D</t>
+          <t>Top-6 F</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -20496,65 +20504,61 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>20.3</v>
+        <v>16.3</v>
       </c>
       <c r="H151" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="I151" t="n">
         <v>13</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K151" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L151" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M151" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N151" t="n">
-        <v>20.3</v>
+        <v>16.5</v>
       </c>
       <c r="O151" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="P151" t="n">
         <v>10</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S151" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>0 pts vs 2.6 expected in last 10; TOI -0.8 min/gm; PP +0.1 min/gm; shots rate x0.91; goals vs shooting% -0.2</t>
-        </is>
-      </c>
+          <t>Not enough baseline</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr"/>
       <c r="V151" t="n">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="W151" t="n">
-        <v>21.1</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Wyatt Kaiser</t>
+          <t>Alex Vlasic</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -20579,7 +20583,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>18.9</v>
+        <v>20.3</v>
       </c>
       <c r="H152" t="n">
         <v>0.1</v>
@@ -20588,19 +20592,19 @@
         <v>13</v>
       </c>
       <c r="J152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L152" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M152" t="n">
         <v>10</v>
       </c>
       <c r="N152" t="n">
-        <v>19.4</v>
+        <v>20.3</v>
       </c>
       <c r="O152" t="n">
         <v>0.1</v>
@@ -20609,10 +20613,10 @@
         <v>10</v>
       </c>
       <c r="Q152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
         <v>9</v>
@@ -20624,20 +20628,20 @@
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>4 pts vs 2.2 expected in last 10; TOI -0.8 min/gm; PP +0.1 min/gm; shots rate x0.99; goals vs shooting% +0.3</t>
+          <t>0 pts vs 2.6 expected in last 10; TOI -0.8 min/gm; PP +0.1 min/gm; shots rate x0.91; goals vs shooting% -0.2</t>
         </is>
       </c>
       <c r="V152" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="W152" t="n">
-        <v>19.6</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Patrick Kane</t>
+          <t>Wyatt Kaiser</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -20647,29 +20651,25 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Depth F</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Top-4 D</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>last games</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="H153" t="n">
-        <v>3.8</v>
+        <v>0.1</v>
       </c>
       <c r="I153" t="n">
         <v>13</v>
@@ -20678,31 +20678,31 @@
         <v>1</v>
       </c>
       <c r="K153" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L153" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M153" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="N153" t="n">
-        <v>18.9</v>
+        <v>19.4</v>
       </c>
       <c r="O153" t="n">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="P153" t="n">
         <v>10</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R153" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S153" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -20711,14 +20711,14 @@
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>7 pts vs 8.6 expected in last 10; TOI +0.7 min/gm; PP +0.6 min/gm; shots rate x0.74; goals vs shooting% -1.9</t>
+          <t>4 pts vs 2.2 expected in last 10; TOI -0.8 min/gm; PP +0.1 min/gm; shots rate x0.99; goals vs shooting% +0.3</t>
         </is>
       </c>
       <c r="V153" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="W153" t="n">
-        <v>17.7</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="154">
@@ -25196,11 +25196,7 @@
           <t>Depth F</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
           <t>last games</t>
